--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="H2" t="n">
         <v>5.5</v>
@@ -769,7 +769,7 @@
         <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H4" t="n">
         <v>2.52</v>
@@ -1160,7 +1160,7 @@
         <v>2.52</v>
       </c>
       <c r="K4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>1.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J5" t="n">
         <v>3.9</v>
@@ -1363,13 +1363,13 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
         <v>1.97</v>
@@ -1414,7 +1414,7 @@
         <v>10.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF5" t="n">
         <v>40</v>
@@ -1465,7 +1465,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>16</v>
@@ -1480,7 +1480,7 @@
         <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
@@ -1492,7 +1492,7 @@
         <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF5" t="n">
         <v>34</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G6" t="n">
         <v>2.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
         <v>5.9</v>
@@ -1548,7 +1548,7 @@
         <v>2.56</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G7" t="n">
         <v>1.32</v>
@@ -1736,13 +1736,13 @@
         <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K7" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H8" t="n">
         <v>2.56</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J8" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>3.8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
         <v>4.5</v>
@@ -2414,7 +2414,7 @@
         <v>25</v>
       </c>
       <c r="AO10" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
         <v>9.6</v>
@@ -2462,7 +2462,7 @@
         <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF10" t="n">
         <v>18.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
         <v>2.02</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.89</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H12" t="n">
         <v>4.2</v>
@@ -2709,7 +2709,7 @@
         <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -2721,22 +2721,22 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
         <v>1.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T12" t="n">
         <v>1.61</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
         <v>22</v>
@@ -2760,7 +2760,7 @@
         <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
         <v>12.5</v>
@@ -2772,7 +2772,7 @@
         <v>17</v>
       </c>
       <c r="AE12" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
         <v>13.5</v>
@@ -2784,7 +2784,7 @@
         <v>15.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
         <v>22</v>
@@ -2811,10 +2811,10 @@
         <v>18.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT12" t="n">
         <v>11.5</v>
@@ -2835,10 +2835,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>3.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="H15" t="n">
         <v>2.92</v>
@@ -3291,7 +3291,7 @@
         <v>3.35</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>3.8</v>
@@ -3303,7 +3303,7 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
         <v>1.48</v>
@@ -3315,22 +3315,22 @@
         <v>2.42</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
         <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
         <v>11.5</v>
@@ -3360,7 +3360,7 @@
         <v>21</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH15" t="n">
         <v>25</v>
@@ -3387,13 +3387,13 @@
         <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AS15" t="n">
         <v>4.1</v>
@@ -3402,13 +3402,13 @@
         <v>3.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AV15" t="n">
         <v>3.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX15" t="n">
         <v>3.65</v>
@@ -3420,7 +3420,7 @@
         <v>3.75</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
         <v>4.1</v>
@@ -3429,7 +3429,7 @@
         <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
         <v>4.3</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-25 00:39:18</t>
+          <t>2026-04-25 03:12:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.74</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>1.94</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>1.94</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="I3" t="n">
         <v>3.15</v>
@@ -966,7 +966,7 @@
         <v>2.14</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>1.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J5" t="n">
         <v>3.9</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="G6" t="n">
         <v>2.26</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
         <v>2.56</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
         <v>2.08</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
         <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
         <v>1.91</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
         <v>2.02</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
         <v>1.91</v>
@@ -2712,7 +2712,7 @@
         <v>4.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2721,19 +2721,19 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q12" t="n">
         <v>1.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S12" t="n">
         <v>2.58</v>
@@ -2772,7 +2772,7 @@
         <v>17</v>
       </c>
       <c r="AE12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
         <v>13.5</v>
@@ -2808,10 +2808,10 @@
         <v>20</v>
       </c>
       <c r="AQ12" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AS12" t="n">
         <v>36</v>
@@ -2820,7 +2820,7 @@
         <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
         <v>15.5</v>
@@ -2835,10 +2835,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -2847,20 +2847,20 @@
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H15" t="n">
         <v>2.92</v>
@@ -3291,7 +3291,7 @@
         <v>3.35</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
         <v>3.8</v>
@@ -3303,28 +3303,28 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P15" t="n">
         <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V15" t="n">
         <v>1.43</v>
@@ -3351,7 +3351,7 @@
         <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
         <v>55</v>
@@ -3366,16 +3366,16 @@
         <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK15" t="n">
         <v>46</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -3384,65 +3384,65 @@
         <v>50</v>
       </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AR15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX15" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AY15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC15" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA15" t="n">
+      <c r="BD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF15" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD15" t="n">
+      <c r="BG15" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="K18" t="n">
         <v>6.6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-25 03:12:17</t>
+          <t>2026-04-25 05:45:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="G2" t="n">
         <v>2.06</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>1.83</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1369,19 +1369,19 @@
         <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
         <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
         <v>2.04</v>
@@ -1420,7 +1420,7 @@
         <v>40</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>21</v>
@@ -1432,7 +1432,7 @@
         <v>140</v>
       </c>
       <c r="AK5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL5" t="n">
         <v>75</v>
@@ -1444,7 +1444,7 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP5" t="n">
         <v>13</v>
@@ -1471,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="AX5" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AY5" t="n">
         <v>17</v>
@@ -1483,26 +1483,26 @@
         <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="BE5" t="n">
         <v>12</v>
       </c>
       <c r="BF5" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BG5" t="n">
         <v>10.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="G7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Q7" t="n">
         <v>1.54</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="H8" t="n">
         <v>2.56</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
         <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2333,16 +2333,16 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
         <v>1.26</v>
@@ -2381,10 +2381,10 @@
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2426,10 +2426,10 @@
         <v>26</v>
       </c>
       <c r="AS10" t="n">
-        <v>38</v>
+        <v>12.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
@@ -2453,16 +2453,16 @@
         <v>36</v>
       </c>
       <c r="BB10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF10" t="n">
         <v>18.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
         <v>22</v>
@@ -2760,7 +2760,7 @@
         <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB12" t="n">
         <v>12.5</v>
@@ -2769,7 +2769,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
         <v>42</v>
@@ -2805,13 +2805,13 @@
         <v>34</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>36</v>
@@ -2820,7 +2820,7 @@
         <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>15.5</v>
@@ -2838,7 +2838,7 @@
         <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -2853,14 +2853,14 @@
         <v>46</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -3279,46 +3279,46 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H15" t="n">
         <v>2.62</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.92</v>
-      </c>
       <c r="I15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>110</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="O15" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
         <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
         <v>1.98</v>
@@ -3327,7 +3327,7 @@
         <v>1.73</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
         <v>1.52</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-25 05:45:13</t>
+          <t>2026-04-25 08:18:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G2" t="n">
         <v>2.06</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="I3" t="n">
         <v>3.15</v>
@@ -966,7 +966,7 @@
         <v>2.14</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A.E.L.</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.98</v>
+        <v>4.8</v>
       </c>
       <c r="H4" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="J4" t="n">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,66 +1325,66 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>A.E.L.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>2.98</v>
       </c>
       <c r="H5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.8</v>
       </c>
-      <c r="I5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1393,123 +1393,123 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>1.91</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2.56</v>
+        <v>1.91</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.33</v>
       </c>
-      <c r="H7" t="n">
+      <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
         <v>10</v>
       </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>1.88</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>2.56</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.15</v>
       </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>1.35</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,66 +2295,66 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>2.14</v>
+        <v>3.95</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,66 +2683,66 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.91</v>
       </c>
-      <c r="H12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>1.91</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.52</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2751,123 +2751,123 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:45:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>2.54</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.07</v>
+        <v>1.61</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.45</v>
       </c>
-      <c r="J15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K15" t="n">
-        <v>110</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AR15" t="n">
-        <v>3.85</v>
+        <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.98</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.55</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.85</v>
+        <v>18.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.3</v>
+        <v>28</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>19</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,66 +3459,66 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.76</v>
+        <v>1.89</v>
       </c>
       <c r="G16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I16" t="n">
         <v>4.3</v>
       </c>
-      <c r="H16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.96</v>
-      </c>
       <c r="J16" t="n">
-        <v>2.32</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,201 +3830,1559 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 08:18:13</t>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-25 10:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-25 10:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-25 10:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>18:45:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Union Santa Fe</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-25 10:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K22" t="n">
+        <v>110</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-25 10:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Union Magdalena</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-25 10:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SER Caxias do Sul</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ypiranga RS</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-25 10:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Ferroviaria</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Guarani</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F25" t="n">
         <v>2.66</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G25" t="n">
         <v>4.1</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H25" t="n">
         <v>2.12</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I25" t="n">
         <v>3</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J25" t="n">
         <v>2.46</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K25" t="n">
         <v>6.6</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q25" t="n">
         <v>2.32</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-04-25 08:18:13</t>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-25 10:51:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH25"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1.94</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
@@ -954,31 +954,31 @@
         <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="I3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>110</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
         <v>1.39</v>
@@ -987,134 +987,134 @@
         <v>2.48</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
@@ -1145,34 +1145,34 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
-        <v>1.26</v>
+        <v>2.28</v>
       </c>
       <c r="I4" t="n">
         <v>2.92</v>
       </c>
       <c r="J4" t="n">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
         <v>1.48</v>
@@ -1181,141 +1181,141 @@
         <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A.E.L.</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="I5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.7</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Radnicki Nis</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,66 +1713,66 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>A.E.L.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>2.56</v>
       </c>
       <c r="I7" t="n">
-        <v>1.83</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,123 +1781,123 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>1.91</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>1.91</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>FK Javor Ivanjica</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.35</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>2.74</v>
+        <v>1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,33 +2295,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
@@ -2330,31 +2330,31 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Chaves</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.61</v>
+        <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,66 +3265,66 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>1.32</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3333,123 +3333,123 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,66 +3459,66 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.52</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.07</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="H20" t="n">
-        <v>1.71</v>
+        <v>2.54</v>
       </c>
       <c r="I20" t="n">
-        <v>2.18</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
         <v>2.12</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,66 +4429,66 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:45:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="H21" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.07</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
         <v>2.38</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,123 +4497,123 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="G22" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>110</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>1.66</v>
+        <v>5.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.66</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>2.58</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Santiago City</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="G23" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="K23" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,201 +5188,1559 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-25 10:51:15</t>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>18:45:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Union Santa Fe</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Union Magdalena</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SER Caxias do Sul</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ypiranga RS</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Ferroviaria</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Guarani</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F32" t="n">
         <v>2.66</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G32" t="n">
         <v>4.1</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H32" t="n">
         <v>2.12</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J32" t="n">
         <v>2.46</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K32" t="n">
         <v>6.6</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q32" t="n">
         <v>2.32</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2026-04-25 10:51:15</t>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:24:05</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,16 +775,16 @@
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
         <v>1.61</v>
@@ -793,134 +793,134 @@
         <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="I3" t="n">
         <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="K3" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
         <v>1.54</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>2.92</v>
       </c>
       <c r="J4" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
@@ -1172,7 +1172,7 @@
         <v>1.48</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="P4" t="n">
         <v>1.48</v>
@@ -1184,7 +1184,7 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1196,7 +1196,7 @@
         <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
         <v>11.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H5" t="n">
         <v>2.32</v>
@@ -1351,7 +1351,7 @@
         <v>2.58</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.7</v>
@@ -1360,7 +1360,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
         <v>3.3</v>
@@ -1390,7 +1390,7 @@
         <v>1.63</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
@@ -1408,28 +1408,28 @@
         <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG5" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
         <v>55</v>
@@ -1447,7 +1447,7 @@
         <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1468,41 +1468,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
         <v>17</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="G7" t="n">
         <v>2.98</v>
@@ -1739,22 +1739,22 @@
         <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
         <v>1.81</v>
@@ -1763,134 +1763,134 @@
         <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -2318,16 +2318,16 @@
         <v>1.82</v>
       </c>
       <c r="I10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2339,7 +2339,7 @@
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>1.96</v>
@@ -2357,19 +2357,19 @@
         <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
         <v>8.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
         <v>19</v>
@@ -2378,7 +2378,7 @@
         <v>17.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>10</v>
@@ -2387,31 +2387,31 @@
         <v>19</v>
       </c>
       <c r="AF10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH10" t="n">
         <v>19.5</v>
       </c>
-      <c r="AH10" t="n">
-        <v>21</v>
-      </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
         <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="n">
         <v>12</v>
@@ -2420,37 +2420,37 @@
         <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA10" t="n">
         <v>32</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>30</v>
       </c>
       <c r="BB10" t="n">
         <v>40</v>
@@ -2465,21 +2465,21 @@
         <v>40</v>
       </c>
       <c r="BF10" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BG10" t="n">
         <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chaves</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>3.65</v>
       </c>
       <c r="H12" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="J12" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.84</v>
+        <v>2.64</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.84</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW13" t="n">
         <v>6.6</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FK Backa Topola</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.07</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>1.32</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>2.74</v>
+        <v>1.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.87</v>
+        <v>2.74</v>
       </c>
       <c r="G16" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>2.68</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>1.29</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="H17" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.5</v>
+        <v>1.84</v>
       </c>
       <c r="G18" t="n">
-        <v>5.9</v>
+        <v>2.08</v>
       </c>
       <c r="H18" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="I18" t="n">
-        <v>2.26</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.44</v>
+        <v>1.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>1.31</v>
       </c>
       <c r="H20" t="n">
-        <v>2.54</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>2.94</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="G21" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y21" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA21" t="n">
         <v>120</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM21" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="AR21" t="n">
-        <v>26</v>
+        <v>4.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>36</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>30</v>
+        <v>4.3</v>
       </c>
       <c r="AX21" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AY21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF21" t="n">
         <v>10</v>
       </c>
-      <c r="AZ21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>19</v>
-      </c>
       <c r="BG21" t="n">
-        <v>36</v>
+        <v>4.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Chaves</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="G22" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>5.5</v>
+        <v>1.81</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="R22" t="n">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>2.58</v>
+        <v>1.27</v>
       </c>
       <c r="T22" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,184 +4817,184 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Provincial Ovalle FC</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Santiago City</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
@@ -5011,17 +5011,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -5043,159 +5043,159 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="P24" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
         <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.07</v>
+        <v>1.69</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="G26" t="n">
-        <v>1.66</v>
+        <v>3.25</v>
       </c>
       <c r="H26" t="n">
-        <v>6.8</v>
+        <v>2.58</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>2.94</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.95</v>
+        <v>2.12</v>
       </c>
       <c r="G27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU27" t="n">
         <v>6.8</v>
       </c>
-      <c r="H27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,66 +5787,66 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G28" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5855,123 +5855,123 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Santiago City</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="G29" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K29" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,66 +6175,66 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.76</v>
+        <v>1.9</v>
       </c>
       <c r="G30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H30" t="n">
         <v>4.3</v>
       </c>
-      <c r="H30" t="n">
-        <v>2.12</v>
-      </c>
       <c r="I30" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P30" t="n">
-        <v>1.68</v>
+        <v>2.48</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6243,123 +6243,123 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,36 +6369,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,201 +6546,1559 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-25 13:24:05</t>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>18:45:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Union Santa Fe</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Union Magdalena</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SER Caxias do Sul</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ypiranga RS</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Ferroviaria</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Guarani</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F39" t="n">
         <v>2.66</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G39" t="n">
         <v>4.1</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H39" t="n">
         <v>2.12</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I39" t="n">
         <v>3</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J39" t="n">
         <v>2.46</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K39" t="n">
         <v>6.6</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q39" t="n">
         <v>2.32</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-04-25 13:24:05</t>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:56:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH45"/>
+  <dimension ref="A1:BH46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H2" t="n">
         <v>3.65</v>
@@ -799,7 +799,7 @@
         <v>3.85</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
         <v>1.84</v>
@@ -808,7 +808,7 @@
         <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X2" t="n">
         <v>14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -969,16 +969,16 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
         <v>1.77</v>
@@ -987,19 +987,19 @@
         <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
         <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
         <v>1.96</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>110</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J5" t="n">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="K5" t="n">
-        <v>110</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.54</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
@@ -1578,13 +1578,13 @@
         <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X6" t="n">
         <v>14.5</v>
@@ -1638,7 +1638,7 @@
         <v>30</v>
       </c>
       <c r="AO6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
@@ -1647,7 +1647,7 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
         <v>7.8</v>
@@ -1677,7 +1677,7 @@
         <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
         <v>19.5</v>
@@ -1686,7 +1686,7 @@
         <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
         <v>17.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="n">
         <v>2.28</v>
@@ -1739,7 +1739,7 @@
         <v>2.92</v>
       </c>
       <c r="J7" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.8</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
         <v>1.49</v>
@@ -1766,7 +1766,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1778,7 +1778,7 @@
         <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
         <v>11.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1990,7 +1990,7 @@
         <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
@@ -2017,7 +2017,7 @@
         <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
         <v>130</v>
@@ -2029,7 +2029,7 @@
         <v>29</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" t="n">
         <v>8</v>
@@ -2038,7 +2038,7 @@
         <v>12.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2050,41 +2050,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AY8" t="n">
         <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
         <v>17</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="G11" t="n">
         <v>2.98</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
         <v>40</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BD13" t="n">
         <v>34</v>
@@ -3047,14 +3047,14 @@
         <v>40</v>
       </c>
       <c r="BF13" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -3515,10 +3515,10 @@
         <v>2.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
         <v>1.1</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="G18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.65</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW18" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH18" t="n">
+      <c r="AX18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC18" t="n">
         <v>21</v>
       </c>
-      <c r="AI18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>44</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
         <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="R19" t="n">
         <v>1.32</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="I20" t="n">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>1.46</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V20" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT20" t="n">
         <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
         <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>25</v>
+        <v>3.95</v>
       </c>
       <c r="BB20" t="n">
-        <v>32</v>
+        <v>4.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="BD20" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="BE20" t="n">
-        <v>44</v>
+        <v>4.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -4476,13 +4476,13 @@
         <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="R21" t="n">
         <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>1.81</v>
+        <v>1.02</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G23" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="H23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4882,7 +4882,7 @@
         <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
         <v>1.43</v>
       </c>
       <c r="P24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q24" t="n">
         <v>2.26</v>
@@ -5064,13 +5064,13 @@
         <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="U24" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="V24" t="n">
         <v>1.53</v>
@@ -5133,10 +5133,10 @@
         <v>44</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AR24" t="n">
         <v>12.5</v>
@@ -5145,13 +5145,13 @@
         <v>4</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
         <v>3.95</v>
@@ -5163,7 +5163,7 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BA24" t="n">
         <v>4</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -5231,13 +5231,13 @@
         <v>15</v>
       </c>
       <c r="J25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K25" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
@@ -5252,7 +5252,7 @@
         <v>2.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="R25" t="n">
         <v>1.75</v>
@@ -5309,7 +5309,7 @@
         <v>160</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
         <v>14</v>
@@ -5327,16 +5327,16 @@
         <v>240</v>
       </c>
       <c r="AP25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>9.800000000000001</v>
@@ -5345,10 +5345,10 @@
         <v>13</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
@@ -5357,10 +5357,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB25" t="n">
         <v>9.199999999999999</v>
@@ -5369,20 +5369,20 @@
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF25" t="n">
         <v>3.45</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>5.9</v>
       </c>
       <c r="H28" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I28" t="n">
         <v>2.18</v>
@@ -5825,16 +5825,16 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O28" t="n">
-        <v>1.51</v>
+        <v>1.02</v>
       </c>
       <c r="P28" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R28" t="n">
         <v>1.14</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
         <v>15.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB30" t="n">
         <v>10.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -6407,10 +6407,10 @@
         <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P31" t="n">
         <v>1.73</v>
@@ -6419,16 +6419,16 @@
         <v>2.18</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V31" t="n">
         <v>1.53</v>
@@ -6437,116 +6437,116 @@
         <v>1.49</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY31" t="n">
         <v>11</v>
       </c>
-      <c r="AS31" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BC31" t="n">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>40</v>
+        <v>7.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -6595,16 +6595,16 @@
         <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
         <v>1.7</v>
@@ -6616,7 +6616,7 @@
         <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T32" t="n">
         <v>2.04</v>
@@ -6706,7 +6706,7 @@
         <v>16</v>
       </c>
       <c r="AW32" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -6774,10 +6774,10 @@
         <v>2.14</v>
       </c>
       <c r="G33" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H33" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I33" t="n">
         <v>4.1</v>
@@ -6786,22 +6786,22 @@
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O33" t="n">
         <v>1.34</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q33" t="n">
         <v>2</v>
@@ -6819,10 +6819,10 @@
         <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W33" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X33" t="n">
         <v>13</v>
@@ -6891,7 +6891,7 @@
         <v>34</v>
       </c>
       <c r="AT33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU33" t="n">
         <v>7.4</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
         <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
         <v>1.02</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G35" t="n">
         <v>1.91</v>
@@ -7213,7 +7213,7 @@
         <v>2.08</v>
       </c>
       <c r="X35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y35" t="n">
         <v>21</v>
@@ -7228,7 +7228,7 @@
         <v>12.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
         <v>16.5</v>
@@ -7240,7 +7240,7 @@
         <v>13.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH35" t="n">
         <v>15.5</v>
@@ -7252,7 +7252,7 @@
         <v>22</v>
       </c>
       <c r="AK35" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL35" t="n">
         <v>26</v>
@@ -7276,7 +7276,7 @@
         <v>32</v>
       </c>
       <c r="AS35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT35" t="n">
         <v>12</v>
@@ -7312,7 +7312,7 @@
         <v>24</v>
       </c>
       <c r="BE35" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF35" t="n">
         <v>8.4</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -7938,167 +7938,167 @@
         <v>3.95</v>
       </c>
       <c r="G39" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H39" t="n">
         <v>1.71</v>
       </c>
       <c r="I39" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J39" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="K39" t="n">
         <v>6.2</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P39" t="n">
         <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -8147,152 +8147,152 @@
         <v>3.4</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P40" t="n">
         <v>1.52</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -8529,165 +8529,165 @@
         <v>2.96</v>
       </c>
       <c r="J42" t="n">
-        <v>2.32</v>
+        <v>2.84</v>
       </c>
       <c r="K42" t="n">
         <v>6.2</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P42" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8697,191 +8697,191 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="G43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q43" t="n">
         <v>2.28</v>
       </c>
-      <c r="H43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I43" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="K43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8891,184 +8891,184 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="G44" t="n">
         <v>2.28</v>
       </c>
       <c r="H44" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.78</v>
       </c>
-      <c r="I44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-25 18:29:41</t>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>
@@ -9090,179 +9090,373 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>SER Caxias do Sul</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ypiranga RS</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>Ferroviaria</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Guarani</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F46" t="n">
         <v>3.25</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G46" t="n">
         <v>3.85</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H46" t="n">
         <v>2.34</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I46" t="n">
         <v>2.9</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J46" t="n">
         <v>2.88</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K46" t="n">
         <v>3.75</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
+      <c r="L46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N46" t="n">
         <v>1.51</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="O46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q46" t="n">
         <v>2.54</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH45" t="inlineStr">
-        <is>
-          <t>2026-04-25 18:29:41</t>
+      <c r="R46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:02:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H2" t="n">
         <v>3.65</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -808,13 +808,13 @@
         <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X2" t="n">
         <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
         <v>34</v>
@@ -826,10 +826,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -862,7 +862,7 @@
         <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
         <v>9.199999999999999</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -978,31 +978,31 @@
         <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="X3" t="n">
         <v>15</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H4" t="n">
         <v>5.5</v>
@@ -1157,7 +1157,7 @@
         <v>6.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
@@ -1169,7 +1169,7 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O4" t="n">
         <v>1.47</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -1339,91 +1339,91 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
-        <v>2.08</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
         <v>1.54</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1444,65 +1444,65 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.11</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.11</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.11</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.11</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.11</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.11</v>
+        <v>18.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.11</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.11</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.11</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.11</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1557,7 +1557,7 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
@@ -1575,7 +1575,7 @@
         <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
         <v>2.08</v>
@@ -1596,7 +1596,7 @@
         <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
         <v>9.6</v>
@@ -1620,7 +1620,7 @@
         <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
         <v>36</v>
@@ -1632,10 +1632,10 @@
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
         <v>44</v>
@@ -1650,7 +1650,7 @@
         <v>6.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -1662,7 +1662,7 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
         <v>19.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
         <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
         <v>2.28</v>
       </c>
       <c r="I7" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="K7" t="n">
         <v>3.8</v>
@@ -1748,25 +1748,25 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
         <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
         <v>11.5</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>2.64</v>
       </c>
       <c r="G14" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I14" t="n">
         <v>3.2</v>
@@ -3100,7 +3100,7 @@
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3115,7 +3115,7 @@
         <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
         <v>2.24</v>
@@ -3136,7 +3136,7 @@
         <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
         <v>13.5</v>
@@ -3160,7 +3160,7 @@
         <v>14.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
         <v>18</v>
@@ -3172,7 +3172,7 @@
         <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
         <v>46</v>
@@ -3184,13 +3184,13 @@
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
         <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP14" t="n">
         <v>9.4</v>
@@ -3202,7 +3202,7 @@
         <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -3214,7 +3214,7 @@
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
         <v>14.5</v>
@@ -3223,32 +3223,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB14" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BC14" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC14" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG14" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -3321,13 +3321,13 @@
         <v>2.92</v>
       </c>
       <c r="T15" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W15" t="n">
         <v>1.42</v>
@@ -3381,10 +3381,10 @@
         <v>75</v>
       </c>
       <c r="AN15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
         <v>15.5</v>
@@ -3420,19 +3420,19 @@
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC15" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC15" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD15" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>20</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G16" t="n">
         <v>1.39</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I16" t="n">
         <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K16" t="n">
         <v>6.4</v>
@@ -3497,13 +3497,13 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q16" t="n">
         <v>1.5</v>
@@ -3515,10 +3515,10 @@
         <v>2.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="V16" t="n">
         <v>1.1</v>
@@ -3569,7 +3569,7 @@
         <v>15</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
         <v>150</v>
@@ -3602,7 +3602,7 @@
         <v>7</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>7.8</v>
@@ -3614,7 +3614,7 @@
         <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16" t="n">
         <v>9.800000000000001</v>
@@ -3626,7 +3626,7 @@
         <v>6.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>2.4</v>
       </c>
       <c r="I18" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
@@ -3885,146 +3885,146 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
         <v>1.56</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
         <v>1.59</v>
       </c>
       <c r="W18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR18" t="n">
         <v>15.5</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AS18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV18" t="n">
         <v>10</v>
       </c>
-      <c r="AR18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AW18" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG18" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -4148,19 +4148,19 @@
         <v>46</v>
       </c>
       <c r="AK19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP19" t="n">
         <v>11.5</v>
@@ -4172,7 +4172,7 @@
         <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
         <v>9.199999999999999</v>
@@ -4184,7 +4184,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX19" t="n">
         <v>14.5</v>
@@ -4196,29 +4196,29 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC19" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF19" t="n">
         <v>19.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
         <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
@@ -4285,7 +4285,7 @@
         <v>1.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
         <v>3.35</v>
@@ -4303,7 +4303,7 @@
         <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y20" t="n">
         <v>12.5</v>
@@ -4390,29 +4390,29 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC20" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC20" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF20" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.95</v>
       </c>
       <c r="BG20" t="n">
         <v>13</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="G21" t="n">
         <v>1.87</v>
@@ -4458,7 +4458,7 @@
         <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
       <c r="G22" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4745,52 +4745,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G23" t="n">
         <v>2.26</v>
@@ -4846,7 +4846,7 @@
         <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -5028,13 +5028,13 @@
         <v>2.92</v>
       </c>
       <c r="G24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J24" t="n">
         <v>3</v>
@@ -5049,7 +5049,7 @@
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
         <v>1.43</v>
@@ -5058,13 +5058,13 @@
         <v>1.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R24" t="n">
         <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
         <v>1.76</v>
@@ -5076,13 +5076,13 @@
         <v>1.53</v>
       </c>
       <c r="W24" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z24" t="n">
         <v>21</v>
@@ -5103,10 +5103,10 @@
         <v>44</v>
       </c>
       <c r="AF24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
@@ -5142,7 +5142,7 @@
         <v>12.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT24" t="n">
         <v>8.6</v>
@@ -5154,7 +5154,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX24" t="n">
         <v>14.5</v>
@@ -5172,23 +5172,23 @@
         <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BD24" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE24" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF24" t="n">
-        <v>32</v>
+        <v>3.95</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -5234,10 +5234,10 @@
         <v>6.8</v>
       </c>
       <c r="K25" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
@@ -5255,10 +5255,10 @@
         <v>1.47</v>
       </c>
       <c r="R25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S25" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="T25" t="n">
         <v>1.91</v>
@@ -5273,7 +5273,7 @@
         <v>4.4</v>
       </c>
       <c r="X25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Y25" t="n">
         <v>50</v>
@@ -5333,10 +5333,10 @@
         <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT25" t="n">
         <v>9.800000000000001</v>
@@ -5345,10 +5345,10 @@
         <v>13</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
@@ -5360,7 +5360,7 @@
         <v>7.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB25" t="n">
         <v>9.199999999999999</v>
@@ -5369,20 +5369,20 @@
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BG25" t="n">
         <v>9.6</v>
       </c>
-      <c r="BF25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1.94</v>
       </c>
       <c r="G26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H26" t="n">
         <v>4.1</v>
@@ -5425,37 +5425,37 @@
         <v>4.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.31</v>
       </c>
       <c r="P26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U26" t="n">
         <v>1.88</v>
@@ -5464,16 +5464,16 @@
         <v>1.29</v>
       </c>
       <c r="W26" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y26" t="n">
         <v>19</v>
       </c>
       <c r="Z26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA26" t="n">
         <v>120</v>
@@ -5482,16 +5482,16 @@
         <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD26" t="n">
         <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
@@ -5500,7 +5500,7 @@
         <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="n">
         <v>28</v>
@@ -5515,22 +5515,22 @@
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO26" t="n">
         <v>80</v>
       </c>
       <c r="AP26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>3.85</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT26" t="n">
         <v>6.8</v>
@@ -5539,13 +5539,13 @@
         <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY26" t="n">
         <v>7.6</v>
@@ -5554,29 +5554,29 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BC26" t="n">
         <v>15</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>1.93</v>
       </c>
       <c r="I28" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="J28" t="n">
         <v>3.05</v>
@@ -5822,73 +5822,73 @@
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.51</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="W28" t="n">
         <v>1.2</v>
       </c>
       <c r="X28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z28" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>15</v>
-      </c>
       <c r="AA28" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AB28" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AC28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AF28" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AG28" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AH28" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AI28" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ28" t="n">
         <v>1000</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.08</v>
+        <v>5.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.52</v>
+        <v>6.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.14</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.32</v>
+        <v>5</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.54</v>
+        <v>6.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>2.58</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.52</v>
+        <v>6.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.64</v>
+        <v>7.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>2.72</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.72</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.72</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.72</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.72</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.72</v>
+        <v>6.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G31" t="n">
         <v>3.15</v>
@@ -6392,7 +6392,7 @@
         <v>2.62</v>
       </c>
       <c r="I31" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J31" t="n">
         <v>3.15</v>
@@ -6425,19 +6425,19 @@
         <v>3.6</v>
       </c>
       <c r="T31" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U31" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
         <v>10.5</v>
@@ -6500,7 +6500,7 @@
         <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>9</v>
@@ -6512,7 +6512,7 @@
         <v>10.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX31" t="n">
         <v>16.5</v>
@@ -6524,29 +6524,29 @@
         <v>16.5</v>
       </c>
       <c r="BA31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC31" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -6604,13 +6604,13 @@
         <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
         <v>1.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R32" t="n">
         <v>1.26</v>
@@ -6628,7 +6628,7 @@
         <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X32" t="n">
         <v>10.5</v>
@@ -6736,11 +6736,11 @@
         <v>19.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.42</v>
@@ -6915,7 +6915,7 @@
         <v>29</v>
       </c>
       <c r="BB33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC33" t="n">
         <v>21</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>1.89</v>
       </c>
       <c r="G35" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H35" t="n">
         <v>4.3</v>
@@ -7171,7 +7171,7 @@
         <v>4.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K35" t="n">
         <v>4.2</v>
@@ -7210,7 +7210,7 @@
         <v>1.29</v>
       </c>
       <c r="W35" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X35" t="n">
         <v>22</v>
@@ -7261,7 +7261,7 @@
         <v>60</v>
       </c>
       <c r="AN35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO35" t="n">
         <v>34</v>
@@ -7312,17 +7312,17 @@
         <v>24</v>
       </c>
       <c r="BE35" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF35" t="n">
         <v>8.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -7383,13 +7383,13 @@
         <v>1.07</v>
       </c>
       <c r="P36" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q36" t="n">
         <v>1.07</v>
       </c>
       <c r="R36" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
         <v>1.07</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
         <v>1.84</v>
       </c>
       <c r="V38" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W38" t="n">
         <v>2.5</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -7935,170 +7935,170 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="G39" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="H39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.71</v>
       </c>
-      <c r="I39" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="R39" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S39" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V39" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ39" t="n">
         <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ39" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AS39" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY39" t="n">
         <v>17</v>
       </c>
-      <c r="AX39" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ39" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="BB39" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BC39" t="n">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="BD39" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -8150,13 +8150,13 @@
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N40" t="n">
         <v>2.62</v>
       </c>
       <c r="O40" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P40" t="n">
         <v>1.52</v>
@@ -8165,134 +8165,134 @@
         <v>2.52</v>
       </c>
       <c r="R40" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S40" t="n">
-        <v>2.52</v>
+        <v>5.1</v>
       </c>
       <c r="T40" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="U40" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="V40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W40" t="n">
         <v>1.7</v>
       </c>
       <c r="X40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX40" t="n">
         <v>11</v>
       </c>
-      <c r="Y40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AY40" t="n">
         <v>10</v>
       </c>
-      <c r="AC40" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AZ40" t="n">
-        <v>2.42</v>
+        <v>19.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB40" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="BD40" t="n">
-        <v>2.52</v>
+        <v>4.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -8326,13 +8326,13 @@
         <v>2.62</v>
       </c>
       <c r="G41" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="H41" t="n">
         <v>2.92</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J41" t="n">
         <v>3.05</v>
@@ -8344,7 +8344,7 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N41" t="n">
         <v>2.8</v>
@@ -8428,65 +8428,65 @@
         <v>55</v>
       </c>
       <c r="AO41" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP41" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR41" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="AS41" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT41" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU41" t="n">
         <v>6</v>
       </c>
       <c r="AV41" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BC41" t="n">
         <v>1.82</v>
       </c>
-      <c r="AX41" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BC41" t="n">
+      <c r="BD41" t="n">
         <v>1.83</v>
       </c>
-      <c r="BD41" t="n">
-        <v>1.84</v>
-      </c>
       <c r="BE41" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BF41" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="BG41" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
         <v>1.56</v>
       </c>
       <c r="O42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P42" t="n">
         <v>1.56</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O44" t="n">
         <v>1.44</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -9105,19 +9105,19 @@
         <v>2.28</v>
       </c>
       <c r="H45" t="n">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
-        <v>1.78</v>
+        <v>2.68</v>
       </c>
       <c r="K45" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
         <v>1.01</v>
@@ -9147,7 +9147,7 @@
         <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W45" t="n">
         <v>1.78</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
         <v>2.34</v>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="J46" t="n">
         <v>2.88</v>
@@ -9311,16 +9311,16 @@
         <v>3.75</v>
       </c>
       <c r="L46" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="O46" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P46" t="n">
         <v>1.51</v>
@@ -9329,43 +9329,43 @@
         <v>2.54</v>
       </c>
       <c r="R46" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V46" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W46" t="n">
         <v>1.35</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC46" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
@@ -9374,7 +9374,7 @@
         <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH46" t="n">
         <v>1000</v>
@@ -9401,62 +9401,62 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-25 21:02:12</t>
+          <t>2026-04-25 23:33:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH46"/>
+  <dimension ref="A1:BH50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,16 +760,16 @@
         <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -778,97 +778,97 @@
         <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>1.58</v>
       </c>
       <c r="O2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.8</v>
-      </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
         <v>1.01</v>
@@ -877,22 +877,22 @@
         <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
         <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -954,55 +954,55 @@
         <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
         <v>15</v>
@@ -1017,16 +1017,16 @@
         <v>140</v>
       </c>
       <c r="AB3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC3" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -1038,10 +1038,10 @@
         <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>28</v>
@@ -1053,22 +1053,22 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>80</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -1080,41 +1080,41 @@
         <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY3" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC3" t="n">
         <v>16.5</v>
       </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
       <c r="BD3" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>90</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>60</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -1178,19 +1178,19 @@
         <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
         <v>1.17</v>
@@ -1199,55 +1199,55 @@
         <v>2.12</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
         <v>230</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>130</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
         <v>140</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>240</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>220</v>
@@ -1256,13 +1256,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
         <v>5.6</v>
@@ -1271,44 +1271,44 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -1339,91 +1339,91 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I5" t="n">
         <v>3.25</v>
       </c>
-      <c r="G5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.86</v>
-      </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.54</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1444,65 +1444,65 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.4</v>
+        <v>1.11</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>1.11</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.4</v>
+        <v>1.11</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.8</v>
+        <v>1.11</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>1.11</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>1.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>1.11</v>
       </c>
       <c r="AX5" t="n">
-        <v>18.5</v>
+        <v>1.11</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.5</v>
+        <v>1.11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>1.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>1.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.5</v>
+        <v>1.11</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>1.11</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>1.11</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>1.11</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.4</v>
+        <v>1.11</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -1545,91 +1545,91 @@
         <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
         <v>3.35</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
         <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
@@ -1638,65 +1638,65 @@
         <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
         <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>26</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -1730,43 +1730,43 @@
         <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J7" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="P7" t="n">
         <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
         <v>11.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
         <v>3.7</v>
@@ -1930,58 +1930,58 @@
         <v>2.32</v>
       </c>
       <c r="I8" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W8" t="n">
         <v>1.37</v>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
         <v>42</v>
@@ -1990,19 +1990,19 @@
         <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
@@ -2011,13 +2011,13 @@
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL8" t="n">
         <v>55</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>60</v>
       </c>
       <c r="AM8" t="n">
         <v>130</v>
@@ -2029,16 +2029,16 @@
         <v>29</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
         <v>4.5</v>
@@ -2059,32 +2059,32 @@
         <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC8" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF8" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
         <v>17</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -2142,19 +2142,19 @@
         <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
         <v>1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
         <v>1.07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.33</v>
@@ -2930,13 +2930,13 @@
         <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
         <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
         <v>2.18</v>
@@ -2963,7 +2963,7 @@
         <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE13" t="n">
         <v>19</v>
@@ -2987,10 +2987,10 @@
         <v>65</v>
       </c>
       <c r="AL13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
         <v>80</v>
@@ -3014,13 +3014,13 @@
         <v>15.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX13" t="n">
         <v>34</v>
@@ -3038,7 +3038,7 @@
         <v>40</v>
       </c>
       <c r="BC13" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BD13" t="n">
         <v>34</v>
@@ -3047,14 +3047,14 @@
         <v>40</v>
       </c>
       <c r="BF13" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -3088,22 +3088,22 @@
         <v>2.64</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="H14" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3112,37 +3112,37 @@
         <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P14" t="n">
         <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
         <v>21</v>
@@ -3151,34 +3151,34 @@
         <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>55</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>46</v>
-      </c>
       <c r="AK14" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
@@ -3193,28 +3193,28 @@
         <v>40</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="AX14" t="n">
         <v>14.5</v>
@@ -3223,32 +3223,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.8</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>3.35</v>
       </c>
       <c r="H15" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="I15" t="n">
         <v>2.44</v>
@@ -3303,28 +3303,28 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
         <v>1.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T15" t="n">
         <v>1.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
         <v>1.69</v>
@@ -3336,10 +3336,10 @@
         <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
         <v>34</v>
@@ -3357,19 +3357,19 @@
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
         <v>36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="n">
         <v>36</v>
@@ -3378,10 +3378,10 @@
         <v>42</v>
       </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO15" t="n">
         <v>17</v>
@@ -3420,19 +3420,19 @@
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
         <v>20</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fatih Karagumruk Istanbul</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="G16" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="H16" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="I16" t="n">
         <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.46</v>
+        <v>1.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="X16" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
         <v>15</v>
       </c>
-      <c r="AL16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>21</v>
-      </c>
       <c r="AQ16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX16" t="n">
         <v>7</v>
       </c>
-      <c r="AR16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BB16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.46</v>
+        <v>3.35</v>
       </c>
       <c r="G17" t="n">
-        <v>1.51</v>
+        <v>3.65</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="I17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X17" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>350</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AR17" t="n">
         <v>13</v>
       </c>
-      <c r="AD17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AS17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I18" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,146 +3885,146 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>1.46</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA18" t="n">
         <v>25</v>
       </c>
-      <c r="Y18" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="BB18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE18" t="n">
         <v>44</v>
       </c>
-      <c r="AB18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4</v>
-      </c>
       <c r="BF18" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G19" t="n">
         <v>2.82</v>
       </c>
       <c r="H19" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4082,40 +4082,40 @@
         <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.96</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="T19" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
         <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
         <v>55</v>
@@ -4127,7 +4127,7 @@
         <v>9</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE19" t="n">
         <v>40</v>
@@ -4148,31 +4148,31 @@
         <v>46</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP19" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
         <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT19" t="n">
         <v>9.199999999999999</v>
@@ -4184,7 +4184,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX19" t="n">
         <v>14.5</v>
@@ -4193,39 +4193,39 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BF19" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fatih Karagumruk Istanbul</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.35</v>
+        <v>1.32</v>
       </c>
       <c r="G20" t="n">
-        <v>3.65</v>
+        <v>1.39</v>
       </c>
       <c r="H20" t="n">
-        <v>2.24</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.34</v>
+        <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="P20" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="T20" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="U20" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.74</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>3.55</v>
       </c>
       <c r="X20" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC20" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK20" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>50</v>
-      </c>
       <c r="AL20" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AN20" t="n">
-        <v>48</v>
+        <v>5.3</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="AP20" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY20" t="n">
         <v>9</v>
       </c>
-      <c r="AR20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG20" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="G22" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W22" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G23" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H23" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I23" t="n">
         <v>5.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="K23" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,16 +4855,16 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O23" t="n">
         <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R23" t="n">
         <v>1.51</v>
@@ -4882,7 +4882,7 @@
         <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -5028,13 +5028,13 @@
         <v>2.92</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="H24" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I24" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>3</v>
@@ -5043,13 +5043,13 @@
         <v>3.45</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
         <v>1.43</v>
@@ -5058,31 +5058,31 @@
         <v>1.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R24" t="n">
         <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="V24" t="n">
         <v>1.53</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
         <v>21</v>
@@ -5091,7 +5091,7 @@
         <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
         <v>8.800000000000001</v>
@@ -5103,10 +5103,10 @@
         <v>44</v>
       </c>
       <c r="AF24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
@@ -5145,13 +5145,13 @@
         <v>3.95</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW24" t="n">
         <v>3.9</v>
@@ -5172,23 +5172,23 @@
         <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
         <v>4.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG24" t="n">
         <v>3.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -5219,25 +5219,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G25" t="n">
         <v>1.29</v>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J25" t="n">
         <v>6.8</v>
       </c>
       <c r="K25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
@@ -5246,13 +5246,13 @@
         <v>6.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="R25" t="n">
         <v>1.76</v>
@@ -5261,135 +5261,135 @@
         <v>2.08</v>
       </c>
       <c r="T25" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="V25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
         <v>4.4</v>
       </c>
       <c r="X25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y25" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z25" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA25" t="n">
-        <v>530</v>
+        <v>620</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AD25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AE25" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI25" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ25" t="n">
         <v>11</v>
       </c>
       <c r="AK25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU25" t="n">
         <v>14</v>
       </c>
-      <c r="AL25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AV25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX25" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8</v>
-      </c>
       <c r="AY25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC25" t="n">
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.07</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q26" t="n">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FK Backa Topola</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.07</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="R27" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="H28" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I28" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
         <v>3.5</v>
@@ -5825,10 +5825,10 @@
         <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O28" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="P28" t="n">
         <v>1.5</v>
@@ -5837,58 +5837,58 @@
         <v>2.62</v>
       </c>
       <c r="R28" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="V28" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AB28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD28" t="n">
         <v>13</v>
       </c>
-      <c r="AC28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>12</v>
-      </c>
       <c r="AE28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH28" t="n">
         <v>30</v>
       </c>
-      <c r="AF28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>27</v>
-      </c>
       <c r="AI28" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ28" t="n">
         <v>1000</v>
@@ -5909,7 +5909,7 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ28" t="n">
         <v>5.6</v>
@@ -5918,53 +5918,53 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AU28" t="n">
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA28" t="n">
         <v>5</v>
       </c>
-      <c r="AW28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BB28" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I30" t="n">
         <v>2.24</v>
@@ -6207,10 +6207,10 @@
         <v>3.35</v>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
         <v>3.2</v>
@@ -6219,10 +6219,10 @@
         <v>1.39</v>
       </c>
       <c r="P30" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R30" t="n">
         <v>1.27</v>
@@ -6231,22 +6231,22 @@
         <v>3.9</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U30" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V30" t="n">
         <v>1.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="n">
         <v>13.5</v>
@@ -6309,7 +6309,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU30" t="n">
         <v>6.6</v>
@@ -6330,29 +6330,29 @@
         <v>15.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC30" t="n">
         <v>10</v>
       </c>
       <c r="BD30" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="BE30" t="n">
         <v>10.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="BG30" t="n">
         <v>18.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -6383,170 +6383,170 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H31" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I31" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J31" t="n">
         <v>3.15</v>
       </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W31" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X31" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR31" t="n">
         <v>11</v>
       </c>
-      <c r="AC31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="AS31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX31" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AY31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD31" t="n">
         <v>36</v>
       </c>
-      <c r="AF31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE31" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF31" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
         <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X32" t="n">
         <v>10.5</v>
@@ -6640,7 +6640,7 @@
         <v>29</v>
       </c>
       <c r="AA32" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB32" t="n">
         <v>7.8</v>
@@ -6709,7 +6709,7 @@
         <v>30</v>
       </c>
       <c r="AX32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY32" t="n">
         <v>10</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,186 +6762,186 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="G33" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="H33" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="I33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J33" t="n">
         <v>4.1</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="O33" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>1.93</v>
+        <v>2.54</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="S33" t="n">
-        <v>3.55</v>
+        <v>2.58</v>
       </c>
       <c r="T33" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="U33" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="V33" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="X33" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Y33" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AA33" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AF33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG33" t="n">
         <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM33" t="n">
         <v>60</v>
       </c>
-      <c r="AJ33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>100</v>
-      </c>
       <c r="AN33" t="n">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE33" t="n">
         <v>50</v>
       </c>
-      <c r="AP33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>38</v>
-      </c>
       <c r="BF33" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Provincial Ovalle FC</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santiago City</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H34" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>3.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="R34" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>1.31</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7150,179 +7150,179 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Santiago City</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.89</v>
+        <v>1.02</v>
       </c>
       <c r="G35" t="n">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="H35" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="K35" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S35" t="n">
         <v>1.31</v>
       </c>
-      <c r="M35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T35" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
         <v>1.07</v>
       </c>
       <c r="R36" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
         <v>1.07</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G38" t="n">
         <v>1.66</v>
@@ -7750,13 +7750,13 @@
         <v>6.8</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7771,7 +7771,7 @@
         <v>1.37</v>
       </c>
       <c r="P38" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
         <v>2.08</v>
@@ -7783,10 +7783,10 @@
         <v>3.85</v>
       </c>
       <c r="T38" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U38" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V38" t="n">
         <v>1.16</v>
@@ -7795,16 +7795,16 @@
         <v>2.5</v>
       </c>
       <c r="X38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Z38" t="n">
         <v>55</v>
       </c>
       <c r="AA38" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB38" t="n">
         <v>7.4</v>
@@ -7813,10 +7813,10 @@
         <v>9</v>
       </c>
       <c r="AD38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE38" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF38" t="n">
         <v>9.4</v>
@@ -7831,7 +7831,7 @@
         <v>130</v>
       </c>
       <c r="AJ38" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AK38" t="n">
         <v>19.5</v>
@@ -7843,34 +7843,34 @@
         <v>200</v>
       </c>
       <c r="AN38" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AO38" t="n">
         <v>200</v>
       </c>
       <c r="AP38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="AS38" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT38" t="n">
         <v>6.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV38" t="n">
         <v>18.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX38" t="n">
         <v>8.199999999999999</v>
@@ -7882,7 +7882,7 @@
         <v>21</v>
       </c>
       <c r="BA38" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BB38" t="n">
         <v>14.5</v>
@@ -7891,20 +7891,20 @@
         <v>17</v>
       </c>
       <c r="BD38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF38" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>9</v>
-      </c>
       <c r="BG38" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -7935,170 +7935,170 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G39" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="H39" t="n">
         <v>1.82</v>
       </c>
       <c r="I39" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="J39" t="n">
         <v>3.35</v>
       </c>
       <c r="K39" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>3.05</v>
+        <v>1.58</v>
       </c>
       <c r="O39" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P39" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="R39" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>1.97</v>
       </c>
       <c r="T39" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="W39" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X39" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
         <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -8129,19 +8129,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G40" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H40" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I40" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K40" t="n">
         <v>3.4</v>
@@ -8153,7 +8153,7 @@
         <v>1.12</v>
       </c>
       <c r="N40" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O40" t="n">
         <v>1.52</v>
@@ -8162,31 +8162,31 @@
         <v>1.52</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R40" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S40" t="n">
         <v>5.1</v>
       </c>
       <c r="T40" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="U40" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="V40" t="n">
         <v>1.3</v>
       </c>
       <c r="W40" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X40" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y40" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z40" t="n">
         <v>34</v>
@@ -8195,58 +8195,58 @@
         <v>120</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC40" t="n">
         <v>8.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE40" t="n">
         <v>80</v>
       </c>
       <c r="AF40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG40" t="n">
         <v>14.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI40" t="n">
         <v>110</v>
       </c>
       <c r="AJ40" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AK40" t="n">
         <v>40</v>
       </c>
       <c r="AL40" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM40" t="n">
         <v>230</v>
       </c>
       <c r="AN40" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO40" t="n">
         <v>120</v>
       </c>
       <c r="AP40" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT40" t="n">
         <v>6.2</v>
@@ -8258,7 +8258,7 @@
         <v>14.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AX40" t="n">
         <v>11</v>
@@ -8270,29 +8270,29 @@
         <v>19.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE40" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF40" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G41" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H41" t="n">
         <v>2.92</v>
       </c>
       <c r="I41" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J41" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="K41" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8347,7 +8347,7 @@
         <v>1.11</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="O41" t="n">
         <v>1.47</v>
@@ -8359,28 +8359,28 @@
         <v>2.4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S41" t="n">
         <v>4.7</v>
       </c>
       <c r="T41" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="U41" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V41" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W41" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X41" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z41" t="n">
         <v>970</v>
@@ -8398,95 +8398,95 @@
         <v>970</v>
       </c>
       <c r="AE41" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF41" t="n">
         <v>970</v>
       </c>
       <c r="AG41" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH41" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI41" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL41" t="n">
         <v>65</v>
       </c>
-      <c r="AJ41" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>60</v>
-      </c>
       <c r="AM41" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN41" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO41" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AQ41" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS41" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT41" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AU41" t="n">
         <v>6</v>
       </c>
       <c r="AV41" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.81</v>
+        <v>5.7</v>
       </c>
       <c r="AX41" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BE41" t="n">
         <v>6</v>
       </c>
-      <c r="AZ41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.87</v>
-      </c>
       <c r="BF41" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="G42" t="n">
         <v>4.3</v>
@@ -8526,13 +8526,13 @@
         <v>2.12</v>
       </c>
       <c r="I42" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J42" t="n">
         <v>2.84</v>
       </c>
       <c r="K42" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8565,7 +8565,7 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W42" t="n">
         <v>1.3</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -8905,16 +8905,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G44" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H44" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I44" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
         <v>2.96</v>
@@ -8929,7 +8929,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O44" t="n">
         <v>1.44</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
         <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J45" t="n">
         <v>2.68</v>
@@ -9123,13 +9123,13 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q45" t="n">
         <v>2.4</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="G46" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H46" t="n">
         <v>2.34</v>
       </c>
       <c r="I46" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J46" t="n">
         <v>2.88</v>
@@ -9317,7 +9317,7 @@
         <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="O46" t="n">
         <v>1.52</v>
@@ -9326,13 +9326,13 @@
         <v>1.51</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.54</v>
+        <v>1.52</v>
       </c>
       <c r="R46" t="n">
         <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="T46" t="n">
         <v>1.91</v>
@@ -9341,7 +9341,7 @@
         <v>1.64</v>
       </c>
       <c r="V46" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W46" t="n">
         <v>1.35</v>
@@ -9410,7 +9410,7 @@
         <v>10.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
         <v>7.2</v>
@@ -9434,29 +9434,805 @@
         <v>17</v>
       </c>
       <c r="BA46" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>130</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-25 23:33:07</t>
+          <t>2026-04-26 02:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K47" t="n">
+        <v>12</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>2026-04-26 02:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K48" t="n">
+        <v>950</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X48" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>2026-04-26 02:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>2026-04-26 02:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H50" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I50" t="n">
+        <v>10</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>2026-04-26 02:03:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -760,31 +760,31 @@
         <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
         <v>1.58</v>
       </c>
       <c r="O2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P2" t="n">
         <v>1.58</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.37</v>
@@ -975,34 +975,34 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
         <v>15</v>
@@ -1017,16 +1017,16 @@
         <v>140</v>
       </c>
       <c r="AB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC3" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
         <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -1038,10 +1038,10 @@
         <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>28</v>
@@ -1053,22 +1053,22 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -1080,41 +1080,41 @@
         <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY3" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1175,22 +1175,22 @@
         <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R4" t="n">
         <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
         <v>1.17</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I5" t="n">
         <v>3.05</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.25</v>
       </c>
       <c r="J5" t="n">
         <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>110</v>
       </c>
       <c r="L5" t="n">
         <v>1.54</v>
@@ -1366,16 +1366,16 @@
         <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1.51</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
         <v>4.8</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
         <v>3.55</v>
@@ -1548,46 +1548,46 @@
         <v>3.2</v>
       </c>
       <c r="K6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.35</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
         <v>15</v>
@@ -1599,7 +1599,7 @@
         <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
         <v>8.6</v>
@@ -1641,7 +1641,7 @@
         <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
@@ -1650,7 +1650,7 @@
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT6" t="n">
         <v>8.6</v>
@@ -1662,7 +1662,7 @@
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -1674,29 +1674,29 @@
         <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF6" t="n">
         <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="G7" t="n">
-        <v>970</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,22 +1751,22 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.49</v>
       </c>
       <c r="P7" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,13 +1775,13 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1930,16 +1930,16 @@
         <v>2.32</v>
       </c>
       <c r="I8" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1960,7 +1960,7 @@
         <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
         <v>1.67</v>
@@ -1969,16 +1969,16 @@
         <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
         <v>1.37</v>
       </c>
       <c r="X8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
         <v>16</v>
@@ -2038,7 +2038,7 @@
         <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2050,41 +2050,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY8" t="n">
         <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC8" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG8" t="n">
         <v>17</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -2142,19 +2142,19 @@
         <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
         <v>1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="R9" t="n">
         <v>1.07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -2891,25 +2891,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I13" t="n">
         <v>1.84</v>
       </c>
       <c r="J13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.95</v>
       </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -2924,25 +2924,25 @@
         <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
         <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
         <v>2.18</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X13" t="n">
         <v>14</v>
@@ -2951,7 +2951,7 @@
         <v>8.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
         <v>19</v>
@@ -3017,7 +3017,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW13" t="n">
         <v>17.5</v>
@@ -3038,23 +3038,23 @@
         <v>40</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE13" t="n">
         <v>40</v>
       </c>
       <c r="BF13" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -3085,49 +3085,49 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="I14" t="n">
         <v>3.15</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -3136,43 +3136,43 @@
         <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
         <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
         <v>46</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
         <v>55</v>
@@ -3193,62 +3193,62 @@
         <v>40</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="AX14" t="n">
         <v>14.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
         <v>3.35</v>
       </c>
       <c r="H15" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3315,7 +3315,7 @@
         <v>1.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
         <v>2.94</v>
@@ -3324,13 +3324,13 @@
         <v>1.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3500,16 +3500,16 @@
         <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
         <v>2.84</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>15</v>
+        <v>1.36</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>44</v>
+        <v>1.36</v>
       </c>
       <c r="AS16" t="n">
-        <v>100</v>
+        <v>1.37</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>1.23</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="AV16" t="n">
-        <v>22</v>
+        <v>1.36</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.4</v>
+        <v>1.37</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>1.24</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>1.36</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18.5</v>
+        <v>1.36</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.4</v>
+        <v>1.37</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>1.36</v>
       </c>
       <c r="BD16" t="n">
-        <v>26</v>
+        <v>1.36</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>1.37</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>1.36</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I17" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J17" t="n">
         <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
         <v>1.33</v>
@@ -3694,37 +3694,37 @@
         <v>3.85</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W17" t="n">
         <v>1.38</v>
       </c>
       <c r="X17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
         <v>18</v>
@@ -3736,7 +3736,7 @@
         <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>11.5</v>
@@ -3778,28 +3778,28 @@
         <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR17" t="n">
         <v>13</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="AT17" t="n">
         <v>12</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
         <v>13</v>
@@ -3808,29 +3808,29 @@
         <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF17" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF17" t="n">
-        <v>6</v>
-      </c>
       <c r="BG17" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G18" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,34 +3885,34 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.46</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.45</v>
       </c>
       <c r="S18" t="n">
         <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3930,7 +3930,7 @@
         <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>15.5</v>
+        <v>1.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>14</v>
+        <v>1.1</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>1.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>1.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>18.5</v>
+        <v>1.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>1.1</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>1.1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>1.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>25</v>
+        <v>1.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>32</v>
+        <v>1.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>21</v>
+        <v>1.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>25</v>
+        <v>1.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>44</v>
+        <v>1.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G19" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H19" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,40 +4079,40 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P19" t="n">
         <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
         <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X19" t="n">
         <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z19" t="n">
         <v>24</v>
@@ -4121,13 +4121,13 @@
         <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>40</v>
@@ -4136,7 +4136,7 @@
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>20</v>
@@ -4172,53 +4172,53 @@
         <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU19" t="n">
         <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AX19" t="n">
         <v>14.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
         <v>18.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>1.32</v>
       </c>
       <c r="G20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H20" t="n">
         <v>9.4</v>
@@ -4261,7 +4261,7 @@
         <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K20" t="n">
         <v>6.6</v>
@@ -4273,25 +4273,25 @@
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S20" t="n">
         <v>2.44</v>
       </c>
       <c r="T20" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
         <v>1.81</v>
@@ -4300,7 +4300,7 @@
         <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X20" t="n">
         <v>28</v>
@@ -4312,7 +4312,7 @@
         <v>110</v>
       </c>
       <c r="AA20" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AB20" t="n">
         <v>10.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H21" t="n">
         <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,13 +4467,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O21" t="n">
         <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
         <v>1.27</v>
@@ -4491,10 +4491,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G22" t="n">
         <v>2.1</v>
@@ -4661,22 +4661,22 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
         <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>1.78</v>
       </c>
       <c r="G23" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I23" t="n">
         <v>5.1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="K23" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,19 +4855,19 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
         <v>1.47</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S23" t="n">
         <v>2.12</v>
@@ -4882,7 +4882,7 @@
         <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>2.92</v>
       </c>
       <c r="G24" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I24" t="n">
         <v>2.9</v>
@@ -5043,13 +5043,13 @@
         <v>3.45</v>
       </c>
       <c r="L24" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
         <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
         <v>1.43</v>
@@ -5067,16 +5067,16 @@
         <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U24" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V24" t="n">
         <v>1.53</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X24" t="n">
         <v>12.5</v>
@@ -5103,10 +5103,10 @@
         <v>44</v>
       </c>
       <c r="AF24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
@@ -5118,7 +5118,7 @@
         <v>70</v>
       </c>
       <c r="AK24" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL24" t="n">
         <v>75</v>
@@ -5133,25 +5133,25 @@
         <v>44</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AR24" t="n">
         <v>12.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.95</v>
+        <v>30</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
         <v>3.9</v>
@@ -5172,13 +5172,13 @@
         <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD24" t="n">
         <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF24" t="n">
         <v>4</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -5219,61 +5219,61 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G25" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="H25" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="I25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P25" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="R25" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S25" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="U25" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V25" t="n">
         <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="X25" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Y25" t="n">
         <v>55</v>
@@ -5282,13 +5282,13 @@
         <v>160</v>
       </c>
       <c r="AA25" t="n">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD25" t="n">
         <v>60</v>
@@ -5315,7 +5315,7 @@
         <v>16</v>
       </c>
       <c r="AL25" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
         <v>170</v>
@@ -5324,19 +5324,19 @@
         <v>4.2</v>
       </c>
       <c r="AO25" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT25" t="n">
         <v>10</v>
@@ -5345,10 +5345,10 @@
         <v>14</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX25" t="n">
         <v>7.8</v>
@@ -5357,10 +5357,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB25" t="n">
         <v>9</v>
@@ -5369,20 +5369,20 @@
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF25" t="n">
         <v>3.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -5440,19 +5440,19 @@
         <v>1.01</v>
       </c>
       <c r="O26" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="P26" t="n">
         <v>1.07</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
         <v>1.07</v>
       </c>
       <c r="S26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -5607,40 +5607,40 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="G27" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H27" t="n">
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
         <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R27" t="n">
         <v>1.33</v>
@@ -5649,22 +5649,22 @@
         <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="V27" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="X27" t="n">
         <v>17</v>
       </c>
       <c r="Y27" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z27" t="n">
         <v>40</v>
@@ -5685,19 +5685,19 @@
         <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
         <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK27" t="n">
         <v>26</v>
@@ -5709,7 +5709,7 @@
         <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO27" t="n">
         <v>80</v>
@@ -5718,59 +5718,59 @@
         <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.6</v>
+        <v>3.25</v>
       </c>
       <c r="AU27" t="n">
         <v>6.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY27" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13.5</v>
+        <v>3.85</v>
       </c>
       <c r="BA27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="BC27" t="n">
-        <v>15.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H28" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I28" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J28" t="n">
         <v>3.1</v>
@@ -5819,37 +5819,37 @@
         <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M28" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O28" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R28" t="n">
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W28" t="n">
         <v>1.21</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I30" t="n">
         <v>2.24</v>
@@ -6216,31 +6216,31 @@
         <v>3.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U30" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
         <v>1.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X30" t="n">
         <v>11</v>
@@ -6258,10 +6258,10 @@
         <v>14</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>27</v>
@@ -6306,13 +6306,13 @@
         <v>11.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT30" t="n">
         <v>12</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
         <v>10</v>
@@ -6330,29 +6330,29 @@
         <v>15.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG30" t="n">
         <v>18.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G31" t="n">
         <v>3.1</v>
@@ -6392,13 +6392,13 @@
         <v>2.64</v>
       </c>
       <c r="I31" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6431,10 +6431,10 @@
         <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W31" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6491,52 +6491,52 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -6604,10 +6604,10 @@
         <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
         <v>2.36</v>
@@ -6622,7 +6622,7 @@
         <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V32" t="n">
         <v>1.3</v>
@@ -6691,10 +6691,10 @@
         <v>11.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT32" t="n">
         <v>7.4</v>
@@ -6706,7 +6706,7 @@
         <v>16</v>
       </c>
       <c r="AW32" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6718,7 +6718,7 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB32" t="n">
         <v>24</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
         <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q33" t="n">
         <v>1.63</v>
@@ -6828,7 +6828,7 @@
         <v>22</v>
       </c>
       <c r="Y33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z33" t="n">
         <v>36</v>
@@ -6852,7 +6852,7 @@
         <v>13.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH33" t="n">
         <v>15.5</v>
@@ -6888,7 +6888,7 @@
         <v>32</v>
       </c>
       <c r="AS33" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT33" t="n">
         <v>12</v>
@@ -6900,7 +6900,7 @@
         <v>16</v>
       </c>
       <c r="AW33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX33" t="n">
         <v>12.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -6971,16 +6971,16 @@
         <v>2.18</v>
       </c>
       <c r="H34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
         <v>4.1</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
         <v>1.42</v>
@@ -6998,7 +6998,7 @@
         <v>1.93</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
         <v>1.36</v>
@@ -7016,7 +7016,7 @@
         <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
         <v>13</v>
@@ -7034,7 +7034,7 @@
         <v>9.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD34" t="n">
         <v>16</v>
@@ -7085,7 +7085,7 @@
         <v>34</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU34" t="n">
         <v>7.4</v>
@@ -7094,13 +7094,13 @@
         <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AX34" t="n">
         <v>12</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ34" t="n">
         <v>16</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G38" t="n">
         <v>1.66</v>
@@ -7756,7 +7756,7 @@
         <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7771,7 +7771,7 @@
         <v>1.37</v>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q38" t="n">
         <v>2.08</v>
@@ -7783,10 +7783,10 @@
         <v>3.85</v>
       </c>
       <c r="T38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U38" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V38" t="n">
         <v>1.16</v>
@@ -7804,10 +7804,10 @@
         <v>55</v>
       </c>
       <c r="AA38" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC38" t="n">
         <v>9</v>
@@ -7816,7 +7816,7 @@
         <v>26</v>
       </c>
       <c r="AE38" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF38" t="n">
         <v>9.4</v>
@@ -7855,10 +7855,10 @@
         <v>16.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS38" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT38" t="n">
         <v>6.4</v>
@@ -7870,7 +7870,7 @@
         <v>18.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX38" t="n">
         <v>8.199999999999999</v>
@@ -7882,7 +7882,7 @@
         <v>21</v>
       </c>
       <c r="BA38" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB38" t="n">
         <v>14.5</v>
@@ -7891,20 +7891,20 @@
         <v>17</v>
       </c>
       <c r="BD38" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF38" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG38" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -7941,22 +7941,22 @@
         <v>6.4</v>
       </c>
       <c r="H39" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I39" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>3.35</v>
       </c>
       <c r="K39" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N39" t="n">
         <v>1.58</v>
@@ -7983,10 +7983,10 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G40" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H40" t="n">
         <v>3.65</v>
       </c>
       <c r="I40" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J40" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8153,13 +8153,13 @@
         <v>1.12</v>
       </c>
       <c r="N40" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O40" t="n">
         <v>1.52</v>
       </c>
       <c r="P40" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q40" t="n">
         <v>2.56</v>
@@ -8174,25 +8174,25 @@
         <v>2.06</v>
       </c>
       <c r="U40" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V40" t="n">
         <v>1.3</v>
       </c>
       <c r="W40" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y40" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA40" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB40" t="n">
         <v>8.800000000000001</v>
@@ -8234,19 +8234,19 @@
         <v>42</v>
       </c>
       <c r="AO40" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP40" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ40" t="n">
         <v>9</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT40" t="n">
         <v>6.2</v>
@@ -8258,7 +8258,7 @@
         <v>14.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX40" t="n">
         <v>11</v>
@@ -8270,29 +8270,29 @@
         <v>19.5</v>
       </c>
       <c r="BA40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD40" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG40" t="n">
         <v>4.6</v>
       </c>
-      <c r="BF40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G41" t="n">
         <v>2.96</v>
@@ -8332,13 +8332,13 @@
         <v>2.92</v>
       </c>
       <c r="I41" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8347,7 +8347,7 @@
         <v>1.11</v>
       </c>
       <c r="N41" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="O41" t="n">
         <v>1.47</v>
@@ -8359,7 +8359,7 @@
         <v>2.4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S41" t="n">
         <v>4.7</v>
@@ -8404,16 +8404,16 @@
         <v>970</v>
       </c>
       <c r="AG41" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI41" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK41" t="n">
         <v>40</v>
@@ -8422,71 +8422,71 @@
         <v>65</v>
       </c>
       <c r="AM41" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN41" t="n">
         <v>44</v>
       </c>
       <c r="AO41" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="AU41" t="n">
         <v>6</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC41" t="n">
         <v>5.7</v>
       </c>
-      <c r="AX41" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA41" t="n">
+      <c r="BD41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF41" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB41" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BE41" t="n">
+      <c r="BG41" t="n">
         <v>6</v>
       </c>
-      <c r="BF41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G42" t="n">
         <v>4.3</v>
@@ -8532,7 +8532,7 @@
         <v>2.84</v>
       </c>
       <c r="K42" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8550,13 +8550,13 @@
         <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R42" t="n">
         <v>1.13</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
         <v>1.47</v>
       </c>
       <c r="O44" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P44" t="n">
         <v>1.47</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.37</v>
+        <v>2.48</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="G46" t="n">
         <v>3.9</v>
       </c>
       <c r="H46" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I46" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>2.88</v>
@@ -9317,31 +9317,31 @@
         <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="O46" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P46" t="n">
         <v>1.51</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.52</v>
+        <v>2.52</v>
       </c>
       <c r="R46" t="n">
         <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="T46" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="U46" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="V46" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W46" t="n">
         <v>1.35</v>
@@ -9374,7 +9374,7 @@
         <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH46" t="n">
         <v>1000</v>
@@ -9404,7 +9404,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ46" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR46" t="n">
         <v>10.5</v>
@@ -9422,7 +9422,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW46" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX46" t="n">
         <v>16.5</v>
@@ -9431,7 +9431,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA46" t="n">
         <v>1.01</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="G47" t="n">
         <v>2.44</v>
@@ -9502,7 +9502,7 @@
         <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9520,13 +9520,13 @@
         <v>1.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="R47" t="n">
         <v>1.18</v>
       </c>
       <c r="S47" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="G48" t="n">
         <v>3.8</v>
@@ -9789,62 +9789,62 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="I49" t="n">
         <v>1000</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -10069,22 +10069,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="G50" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="H50" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J50" t="n">
-        <v>2.78</v>
+        <v>3.65</v>
       </c>
       <c r="K50" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10093,16 +10093,16 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="O50" t="n">
         <v>1.41</v>
       </c>
       <c r="P50" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="R50" t="n">
         <v>1.2</v>
@@ -10117,10 +10117,10 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W50" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH53"/>
+  <dimension ref="A1:BH54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -781,7 +781,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.37</v>
@@ -790,25 +790,25 @@
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
         <v>2.06</v>
@@ -966,7 +966,7 @@
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.37</v>
@@ -987,16 +987,16 @@
         <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
         <v>3.8</v>
       </c>
       <c r="T3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.91</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.92</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1145,46 +1145,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
         <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P4" t="n">
         <v>1.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,100 +1363,100 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.47</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
         <v>130</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="n">
         <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
         <v>140</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP5" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
         <v>5.6</v>
@@ -1465,44 +1465,44 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AX5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="n">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="I6" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
         <v>1.54</v>
@@ -1560,64 +1560,64 @@
         <v>2.44</v>
       </c>
       <c r="O6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
         <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1638,65 +1638,65 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.11</v>
+        <v>6.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.11</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.11</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.11</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.11</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.11</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.11</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.11</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.11</v>
+        <v>4.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
         <v>2.52</v>
       </c>
       <c r="I8" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
         <v>3.3</v>
@@ -1942,13 +1942,13 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P8" t="n">
         <v>1.51</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I9" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.43</v>
@@ -2163,7 +2163,7 @@
         <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
         <v>1.37</v>
@@ -2175,7 +2175,7 @@
         <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
         <v>42</v>
@@ -2196,7 +2196,7 @@
         <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
         <v>22</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -2554,7 +2554,7 @@
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -2709,22 +2709,22 @@
         <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
         <v>1.81</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P12" t="n">
         <v>1.81</v>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
         <v>1.53</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G15" t="n">
         <v>2.78</v>
@@ -3294,7 +3294,7 @@
         <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.4</v>
@@ -3303,7 +3303,7 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
         <v>1.42</v>
@@ -3321,7 +3321,7 @@
         <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
         <v>2</v>
@@ -3339,7 +3339,7 @@
         <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
         <v>55</v>
@@ -3348,7 +3348,7 @@
         <v>9.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
         <v>14</v>
@@ -3423,7 +3423,7 @@
         <v>29</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC15" t="n">
         <v>21</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -3488,13 +3488,13 @@
         <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
         <v>4.2</v>
@@ -3503,19 +3503,19 @@
         <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
         <v>1.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.94</v>
+        <v>1.02</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U16" t="n">
         <v>2.34</v>
@@ -3524,10 +3524,10 @@
         <v>1.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
         <v>12.5</v>
@@ -3590,7 +3590,7 @@
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
@@ -3614,19 +3614,19 @@
         <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
         <v>42</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD16" t="n">
         <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
         <v>20</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fatih Karagumruk Istanbul</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>1.36</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N17" t="n">
         <v>1.29</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.4</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.52</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.32</v>
@@ -3888,13 +3888,13 @@
         <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
         <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
         <v>1.39</v>
@@ -3909,10 +3909,10 @@
         <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -4109,7 +4109,7 @@
         <v>1.38</v>
       </c>
       <c r="X19" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y19" t="n">
         <v>12.5</v>
@@ -4196,19 +4196,19 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
         <v>26</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>3.05</v>
       </c>
       <c r="H20" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I20" t="n">
         <v>2.58</v>
@@ -4279,7 +4279,7 @@
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
         <v>1.63</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -4467,10 +4467,10 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="P21" t="n">
         <v>1.8</v>
@@ -4491,7 +4491,7 @@
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
         <v>1.56</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Fatih Karagumruk Istanbul</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>1.36</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>5.9</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>5.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -4831,28 +4831,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="G23" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I23" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J23" t="n">
         <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
         <v>1.83</v>
@@ -4864,13 +4864,13 @@
         <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R23" t="n">
         <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4879,16 +4879,16 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,34 +4897,34 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4933,68 +4933,68 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.7</v>
       </c>
-      <c r="I24" t="n">
+      <c r="T24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR24" t="n">
         <v>6.6</v>
       </c>
-      <c r="J24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -5228,31 +5228,31 @@
         <v>3.35</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R25" t="n">
         <v>1.53</v>
@@ -5267,7 +5267,7 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
         <v>1.92</v>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>2.6</v>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>3</v>
@@ -5431,7 +5431,7 @@
         <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
@@ -5455,13 +5455,13 @@
         <v>4.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U26" t="n">
         <v>1.92</v>
       </c>
       <c r="V26" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
         <v>1.44</v>
@@ -5530,10 +5530,10 @@
         <v>12.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU26" t="n">
         <v>6.4</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FK Backa Topola</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="G27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>16</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.87</v>
       </c>
-      <c r="H27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="H28" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="K28" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="L28" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="O28" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>2.78</v>
+        <v>1.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="R28" t="n">
-        <v>1.75</v>
+        <v>1.07</v>
       </c>
       <c r="S28" t="n">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="T28" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
         <v>16.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
         <v>40</v>
@@ -6073,7 +6073,7 @@
         <v>70</v>
       </c>
       <c r="AF29" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG29" t="n">
         <v>12.5</v>
@@ -6097,7 +6097,7 @@
         <v>130</v>
       </c>
       <c r="AN29" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AO29" t="n">
         <v>80</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G30" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H30" t="n">
         <v>1.94</v>
       </c>
       <c r="I30" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="J30" t="n">
         <v>3.1</v>
@@ -6219,10 +6219,10 @@
         <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -6231,16 +6231,16 @@
         <v>5.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U30" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="V30" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="W30" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X30" t="n">
         <v>9.800000000000001</v>
@@ -6306,7 +6306,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT30" t="n">
         <v>4</v>
@@ -6315,44 +6315,44 @@
         <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BA30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC30" t="n">
         <v>5.3</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG30" t="n">
         <v>4.7</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -6491,52 +6491,52 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -6586,10 +6586,10 @@
         <v>2.96</v>
       </c>
       <c r="I32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K32" t="n">
         <v>6.2</v>
@@ -6598,10 +6598,10 @@
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O32" t="n">
         <v>1.14</v>
@@ -6625,10 +6625,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W32" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6685,52 +6685,52 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -6774,10 +6774,10 @@
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I33" t="n">
         <v>2.24</v>
@@ -6807,10 +6807,10 @@
         <v>2.22</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T33" t="n">
         <v>1.88</v>
@@ -6900,7 +6900,7 @@
         <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX33" t="n">
         <v>21</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="G34" t="n">
         <v>3.05</v>
@@ -6974,10 +6974,10 @@
         <v>2.64</v>
       </c>
       <c r="I34" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
         <v>3.45</v>
@@ -7013,7 +7013,7 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W34" t="n">
         <v>1.48</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G35" t="n">
         <v>2.14</v>
@@ -7177,7 +7177,7 @@
         <v>3.45</v>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M35" t="n">
         <v>1.1</v>
@@ -7192,7 +7192,7 @@
         <v>1.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R35" t="n">
         <v>1.26</v>
@@ -7318,11 +7318,11 @@
         <v>19.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
         <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L36" t="n">
         <v>1.31</v>
@@ -7398,7 +7398,7 @@
         <v>1.61</v>
       </c>
       <c r="U36" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V36" t="n">
         <v>1.29</v>
@@ -7413,19 +7413,19 @@
         <v>22</v>
       </c>
       <c r="Z36" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA36" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB36" t="n">
         <v>12.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD36" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE36" t="n">
         <v>40</v>
@@ -7446,7 +7446,7 @@
         <v>22</v>
       </c>
       <c r="AK36" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL36" t="n">
         <v>25</v>
@@ -7464,7 +7464,7 @@
         <v>21</v>
       </c>
       <c r="AQ36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR36" t="n">
         <v>32</v>
@@ -7479,7 +7479,7 @@
         <v>9</v>
       </c>
       <c r="AV36" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW36" t="n">
         <v>36</v>
@@ -7491,7 +7491,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA36" t="n">
         <v>40</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.14</v>
       </c>
       <c r="G37" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H37" t="n">
         <v>4</v>
@@ -7559,61 +7559,61 @@
         <v>4.1</v>
       </c>
       <c r="J37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K37" t="n">
         <v>3.5</v>
       </c>
-      <c r="K37" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L37" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O37" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P37" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="T37" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U37" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V37" t="n">
         <v>1.32</v>
       </c>
       <c r="W37" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X37" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z37" t="n">
         <v>28</v>
       </c>
       <c r="AA37" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB37" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC37" t="n">
         <v>7.6</v>
@@ -7622,61 +7622,61 @@
         <v>16</v>
       </c>
       <c r="AE37" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF37" t="n">
         <v>13</v>
       </c>
       <c r="AG37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH37" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ37" t="n">
         <v>26</v>
       </c>
       <c r="AK37" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL37" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM37" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN37" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AO37" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ37" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR37" t="n">
         <v>25</v>
       </c>
       <c r="AS37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT37" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU37" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV37" t="n">
         <v>14.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AX37" t="n">
         <v>12</v>
@@ -7688,13 +7688,13 @@
         <v>16</v>
       </c>
       <c r="BA37" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BB37" t="n">
         <v>24</v>
       </c>
       <c r="BC37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD37" t="n">
         <v>34</v>
@@ -7706,11 +7706,11 @@
         <v>15</v>
       </c>
       <c r="BG37" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -7849,52 +7849,52 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -8043,52 +8043,52 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF39" t="n">
         <v>1.01</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -8150,25 +8150,25 @@
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
         <v>1.01</v>
       </c>
       <c r="O40" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="P40" t="n">
         <v>1.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="R40" t="n">
         <v>1.24</v>
       </c>
       <c r="S40" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -8237,52 +8237,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8314,186 +8314,186 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N41" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="O41" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="P41" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.08</v>
+        <v>1.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>3.85</v>
+        <v>1.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z41" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA41" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC41" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD41" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI41" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL41" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM41" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU41" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW41" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BA41" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD41" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF41" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8503,191 +8503,191 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="G42" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT42" t="n">
         <v>6.4</v>
       </c>
-      <c r="H42" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V42" t="n">
-        <v>2</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8697,191 +8697,191 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18:45:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.28</v>
+        <v>4.6</v>
       </c>
       <c r="G43" t="n">
-        <v>2.44</v>
+        <v>5.7</v>
       </c>
       <c r="H43" t="n">
-        <v>3.65</v>
+        <v>1.84</v>
       </c>
       <c r="I43" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K43" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M43" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>2.62</v>
+        <v>1.58</v>
       </c>
       <c r="O43" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="P43" t="n">
         <v>1.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.56</v>
+        <v>1.97</v>
       </c>
       <c r="R43" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>5.1</v>
+        <v>1.97</v>
       </c>
       <c r="T43" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.3</v>
+        <v>2.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="X43" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8891,184 +8891,184 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:45:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F44" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N44" t="n">
         <v>2.62</v>
       </c>
-      <c r="G44" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2.82</v>
-      </c>
       <c r="O44" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="P44" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R44" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S44" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T44" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="U44" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="V44" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="W44" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="X44" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y44" t="n">
         <v>11.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AA44" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AB44" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE44" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF44" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG44" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH44" t="n">
         <v>25</v>
       </c>
       <c r="AI44" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AJ44" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AK44" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN44" t="n">
         <v>40</v>
       </c>
-      <c r="AL44" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>44</v>
-      </c>
       <c r="AO44" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AP44" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ44" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AR44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS44" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE44" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU44" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BE44" t="n">
+      <c r="BF44" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF44" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG44" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -9262,14 +9262,14 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9284,186 +9284,186 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="G46" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="H46" t="n">
-        <v>2.46</v>
+        <v>2.94</v>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="K46" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>1.41</v>
+        <v>2.86</v>
       </c>
       <c r="O46" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="P46" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R46" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V46" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9473,191 +9473,191 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="F47" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.78</v>
       </c>
-      <c r="G47" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H47" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I47" t="n">
+      <c r="V47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ47" t="n">
         <v>6.4</v>
       </c>
-      <c r="J47" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K47" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9667,75 +9667,75 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="I48" t="n">
         <v>6.4</v>
       </c>
       <c r="J48" t="n">
-        <v>2.96</v>
+        <v>1.09</v>
       </c>
       <c r="K48" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M48" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.48</v>
+        <v>1.47</v>
       </c>
       <c r="O48" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="P48" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="R48" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S48" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="T48" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
         <v>1.19</v>
       </c>
       <c r="W48" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="X48" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
         <v>1000</v>
@@ -9747,10 +9747,10 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
         <v>1000</v>
@@ -9759,7 +9759,7 @@
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
         <v>1000</v>
@@ -9789,52 +9789,52 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ48" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT48" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX48" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY48" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF48" t="n">
         <v>1.01</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -9866,154 +9866,154 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="G49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K49" t="n">
         <v>3.9</v>
       </c>
-      <c r="H49" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L49" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O49" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="P49" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R49" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S49" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X49" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT49" t="n">
         <v>4.6</v>
       </c>
-      <c r="T49" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X49" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ49" t="n">
+      <c r="AU49" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR49" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AV49" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW49" t="n">
         <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY49" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ49" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA49" t="n">
         <v>1.01</v>
@@ -10038,14 +10038,14 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10055,93 +10055,93 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="G50" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="H50" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="K50" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="O50" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P50" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.75</v>
+        <v>2.52</v>
       </c>
       <c r="R50" t="n">
         <v>1.18</v>
       </c>
       <c r="S50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U50" t="n">
         <v>1.75</v>
       </c>
-      <c r="T50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V50" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="W50" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
         <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC50" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE50" t="n">
         <v>1000</v>
@@ -10150,7 +10150,7 @@
         <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH50" t="n">
         <v>1000</v>
@@ -10177,37 +10177,37 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS50" t="n">
         <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW50" t="n">
         <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA50" t="n">
         <v>1.01</v>
@@ -10232,14 +10232,14 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10254,55 +10254,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="G51" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="H51" t="n">
-        <v>2.48</v>
+        <v>1.76</v>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="K51" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="O51" t="n">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="P51" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>1.05</v>
       </c>
       <c r="R51" t="n">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>1.05</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -10311,13 +10311,13 @@
         <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="X51" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y51" t="n">
         <v>1000</v>
@@ -10374,66 +10374,66 @@
         <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10448,31 +10448,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="G52" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H52" t="n">
-        <v>1.76</v>
+        <v>3.05</v>
       </c>
       <c r="I52" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10481,22 +10481,22 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="P52" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="R52" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="S52" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -10505,10 +10505,10 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W52" t="n">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,201 +10620,395 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X53" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>2026-04-26 09:30:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Aucas</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Delfin</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="F54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G54" t="n">
         <v>1.7</v>
       </c>
-      <c r="H53" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="H54" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I54" t="n">
         <v>9.4</v>
       </c>
-      <c r="J53" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K53" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N53" t="n">
+      <c r="J54" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N54" t="n">
         <v>2.72</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O54" t="n">
         <v>1.41</v>
       </c>
-      <c r="P53" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R53" t="n">
+      <c r="P54" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R54" t="n">
         <v>1.2</v>
       </c>
-      <c r="S53" t="n">
+      <c r="S54" t="n">
         <v>3.5</v>
       </c>
-      <c r="T53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH53" t="inlineStr">
-        <is>
-          <t>2026-04-26 07:03:13</t>
+      <c r="T54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
         <v>2.24</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
         <v>4.3</v>
@@ -772,22 +772,22 @@
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
         <v>2.1</v>
@@ -802,7 +802,7 @@
         <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.31</v>
@@ -811,10 +811,10 @@
         <v>1.8</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -871,13 +871,13 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
         <v>6</v>
@@ -886,41 +886,41 @@
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AY2" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
         <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
         <v>5.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1065,22 +1065,22 @@
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AS3" t="n">
         <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
@@ -1092,7 +1092,7 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
         <v>16.5</v>
@@ -1101,7 +1101,7 @@
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
         <v>4.2</v>
@@ -1110,11 +1110,11 @@
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1145,55 +1145,55 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
         <v>1.65</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.58</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.78</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.22</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.18</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.14</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.77</v>
+        <v>5.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1366,31 +1366,31 @@
         <v>2.86</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
         <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
         <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
         <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1399,16 +1399,16 @@
         <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>27</v>
@@ -1417,10 +1417,10 @@
         <v>130</v>
       </c>
       <c r="AF5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG5" t="n">
         <v>11</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>27</v>
@@ -1429,34 +1429,34 @@
         <v>140</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>230</v>
       </c>
       <c r="AN5" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AP5" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>5.6</v>
@@ -1465,44 +1465,44 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1533,91 +1533,91 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="H6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O6" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1641,19 +1641,19 @@
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
@@ -1665,38 +1665,38 @@
         <v>32</v>
       </c>
       <c r="AX6" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
         <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>44</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BG6" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.45</v>
@@ -1760,52 +1760,52 @@
         <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
         <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
@@ -1814,83 +1814,83 @@
         <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
         <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
         <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>27</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.6</v>
+        <v>29</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>2.76</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
         <v>3.25</v>
@@ -1978,7 +1978,7 @@
         <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1990,7 +1990,7 @@
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2002,7 +2002,7 @@
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AQ8" t="n">
         <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
         <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -2133,13 +2133,13 @@
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.36</v>
@@ -2163,13 +2163,13 @@
         <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
         <v>1.38</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
         <v>11.5</v>
@@ -2178,13 +2178,13 @@
         <v>970</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>12.5</v>
@@ -2202,7 +2202,7 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
         <v>65</v>
@@ -2232,7 +2232,7 @@
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2244,41 +2244,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.8</v>
+        <v>42</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
         <v>17</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
@@ -2339,10 +2339,10 @@
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R10" t="n">
         <v>1.31</v>
@@ -2351,16 +2351,16 @@
         <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2420,59 +2420,59 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>3.75</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT10" t="n">
         <v>6.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
         <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.6</v>
+        <v>3.35</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>3.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>15</v>
+        <v>3.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>3.85</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -2503,73 +2503,73 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.33</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>7</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.28</v>
-      </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
         <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
         <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z11" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
         <v>1000</v>
@@ -2578,10 +2578,10 @@
         <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
         <v>1000</v>
@@ -2590,13 +2590,13 @@
         <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -2700,28 +2700,28 @@
         <v>1.48</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.31</v>
@@ -2742,10 +2742,10 @@
         <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
         <v>2.66</v>
@@ -2769,7 +2769,7 @@
         <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB12" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR12" t="n">
+      <c r="BC12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD12" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="BE12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3.2</v>
       </c>
-      <c r="AV12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H13" t="n">
         <v>1.47</v>
       </c>
       <c r="I13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="J13" t="n">
         <v>3.95</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.26</v>
@@ -2915,7 +2915,7 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.2</v>
@@ -2939,7 +2939,7 @@
         <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="W13" t="n">
         <v>1.13</v>
@@ -2948,25 +2948,25 @@
         <v>27</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AB13" t="n">
         <v>32</v>
       </c>
       <c r="AC13" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AF13" t="n">
         <v>1000</v>
@@ -2975,7 +2975,7 @@
         <v>30</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
         <v>36</v>
@@ -2984,7 +2984,7 @@
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
@@ -2996,65 +2996,65 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AP13" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY13" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.4</v>
       </c>
       <c r="AZ13" t="n">
         <v>4.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
         <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
         <v>3.05</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
-        <v>1.96</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.7</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
@@ -3312,10 +3312,10 @@
         <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
@@ -3327,7 +3327,7 @@
         <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
         <v>1.55</v>
@@ -3381,7 +3381,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
         <v>30</v>
@@ -3390,13 +3390,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR15" t="n">
         <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT15" t="n">
         <v>8.800000000000001</v>
@@ -3411,7 +3411,7 @@
         <v>3.85</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
@@ -3423,13 +3423,13 @@
         <v>3.95</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BE15" t="n">
         <v>4.1</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G16" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H16" t="n">
         <v>2.62</v>
       </c>
       <c r="I16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
         <v>4.4</v>
@@ -3506,13 +3506,13 @@
         <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R16" t="n">
         <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T16" t="n">
         <v>1.53</v>
@@ -3521,10 +3521,10 @@
         <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X16" t="n">
         <v>29</v>
@@ -3557,7 +3557,7 @@
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
         <v>40</v>
@@ -3581,37 +3581,37 @@
         <v>21</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.7</v>
+        <v>17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
         <v>3.95</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.8</v>
+        <v>19.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
         <v>3.85</v>
@@ -3620,10 +3620,10 @@
         <v>3.85</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.7</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
         <v>4</v>
@@ -3632,11 +3632,11 @@
         <v>3.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -3667,46 +3667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="G17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="H17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
         <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="R17" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="T17" t="n">
         <v>1.81</v>
@@ -3718,13 +3718,13 @@
         <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
         <v>36</v>
       </c>
       <c r="Y17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z17" t="n">
         <v>110</v>
@@ -3733,10 +3733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3745,10 +3745,10 @@
         <v>140</v>
       </c>
       <c r="AF17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
         <v>28</v>
@@ -3760,7 +3760,7 @@
         <v>13.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AL17" t="n">
         <v>36</v>
@@ -3775,62 +3775,62 @@
         <v>150</v>
       </c>
       <c r="AP17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -3870,10 +3870,10 @@
         <v>1.83</v>
       </c>
       <c r="I18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
@@ -3882,40 +3882,40 @@
         <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
         <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
         <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W18" t="n">
         <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
         <v>9.199999999999999</v>
@@ -3924,13 +3924,13 @@
         <v>11.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>9.800000000000001</v>
@@ -3942,13 +3942,13 @@
         <v>38</v>
       </c>
       <c r="AG18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH18" t="n">
         <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
         <v>120</v>
@@ -3975,13 +3975,13 @@
         <v>8.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
@@ -3996,10 +3996,10 @@
         <v>34</v>
       </c>
       <c r="AY18" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>30</v>
@@ -4008,13 +4008,13 @@
         <v>38</v>
       </c>
       <c r="BC18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD18" t="n">
         <v>55</v>
       </c>
-      <c r="BD18" t="n">
-        <v>50</v>
-      </c>
       <c r="BE18" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BF18" t="n">
         <v>55</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I19" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="J19" t="n">
         <v>3.65</v>
@@ -4091,25 +4091,25 @@
         <v>1.78</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
         <v>2.98</v>
       </c>
       <c r="T19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W19" t="n">
         <v>1.43</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="n">
         <v>12.5</v>
@@ -4157,7 +4157,7 @@
         <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO19" t="n">
         <v>17</v>
@@ -4196,19 +4196,19 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
         <v>42</v>
       </c>
       <c r="BC19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF19" t="n">
         <v>20</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>1.34</v>
       </c>
       <c r="G20" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
         <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="K20" t="n">
         <v>6.4</v>
@@ -4279,10 +4279,10 @@
         <v>1.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R20" t="n">
         <v>1.58</v>
@@ -4300,7 +4300,7 @@
         <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="X20" t="n">
         <v>28</v>
@@ -4324,10 +4324,10 @@
         <v>42</v>
       </c>
       <c r="AE20" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -4360,13 +4360,13 @@
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR20" t="n">
         <v>6.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT20" t="n">
         <v>8.800000000000001</v>
@@ -4375,10 +4375,10 @@
         <v>11.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX20" t="n">
         <v>7.8</v>
@@ -4387,10 +4387,10 @@
         <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB20" t="n">
         <v>9.6</v>
@@ -4399,20 +4399,20 @@
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG20" t="n">
         <v>7</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -4443,58 +4443,58 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="O21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>1.33</v>
+        <v>2.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="S21" t="n">
-        <v>1.18</v>
+        <v>2.12</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4536,7 +4536,7 @@
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>3.6</v>
       </c>
       <c r="H22" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I22" t="n">
         <v>2.34</v>
@@ -4655,7 +4655,7 @@
         <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -4667,13 +4667,13 @@
         <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
         <v>3.4</v>
@@ -4688,10 +4688,10 @@
         <v>1.74</v>
       </c>
       <c r="W22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
         <v>12.5</v>
@@ -4703,7 +4703,7 @@
         <v>30</v>
       </c>
       <c r="AB22" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC22" t="n">
         <v>8.199999999999999</v>
@@ -4781,16 +4781,16 @@
         <v>30</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC22" t="n">
         <v>28</v>
       </c>
       <c r="BD22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE22" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8</v>
       </c>
       <c r="BF22" t="n">
         <v>26</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -4837,10 +4837,10 @@
         <v>3.05</v>
       </c>
       <c r="H23" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I23" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
@@ -4891,7 +4891,7 @@
         <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
         <v>42</v>
@@ -4900,10 +4900,10 @@
         <v>15.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
         <v>30</v>
@@ -4912,22 +4912,22 @@
         <v>27</v>
       </c>
       <c r="AG23" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>40</v>
       </c>
       <c r="AJ23" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK23" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4936,7 +4936,7 @@
         <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP23" t="n">
         <v>16.5</v>
@@ -4948,7 +4948,7 @@
         <v>15.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT23" t="n">
         <v>13</v>
@@ -4972,19 +4972,19 @@
         <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF23" t="n">
         <v>18</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -5028,13 +5028,13 @@
         <v>2.68</v>
       </c>
       <c r="G24" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H24" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
         <v>3.2</v>
@@ -5055,22 +5055,22 @@
         <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T24" t="n">
         <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
@@ -5091,16 +5091,16 @@
         <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD24" t="n">
         <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF24" t="n">
         <v>17</v>
@@ -5118,25 +5118,25 @@
         <v>46</v>
       </c>
       <c r="AK24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL24" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM24" t="n">
         <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AP24" t="n">
         <v>10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR24" t="n">
         <v>16.5</v>
@@ -5160,19 +5160,19 @@
         <v>14.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
         <v>28</v>
       </c>
       <c r="BB24" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BC24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
         <v>40</v>
@@ -5181,14 +5181,14 @@
         <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG24" t="n">
         <v>22</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>2.74</v>
       </c>
       <c r="H25" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I25" t="n">
         <v>3.1</v>
@@ -5237,7 +5237,7 @@
         <v>3.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
@@ -5249,16 +5249,16 @@
         <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
         <v>1.78</v>
@@ -5321,7 +5321,7 @@
         <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO25" t="n">
         <v>36</v>
@@ -5336,7 +5336,7 @@
         <v>17</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT25" t="n">
         <v>9.6</v>
@@ -5348,7 +5348,7 @@
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX25" t="n">
         <v>14.5</v>
@@ -5360,7 +5360,7 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB25" t="n">
         <v>7.4</v>
@@ -5369,7 +5369,7 @@
         <v>7</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE25" t="n">
         <v>8</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G26" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="H26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I26" t="n">
         <v>8.4</v>
@@ -5431,7 +5431,7 @@
         <v>4.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -5443,76 +5443,76 @@
         <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
         <v>1.81</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
         <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V26" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG26" t="n">
         <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN26" t="n">
         <v>7.6</v>
@@ -5521,28 +5521,28 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>21</v>
       </c>
       <c r="AR26" t="n">
-        <v>3.95</v>
+        <v>30</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.1</v>
+        <v>48</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU26" t="n">
         <v>9.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.8</v>
+        <v>25</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="AX26" t="n">
         <v>8</v>
@@ -5551,32 +5551,32 @@
         <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC26" t="n">
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.1</v>
+        <v>24</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.1</v>
+        <v>44</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.1</v>
+        <v>44</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G27" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I27" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.32</v>
@@ -5631,7 +5631,7 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O27" t="n">
         <v>1.3</v>
@@ -5640,31 +5640,31 @@
         <v>1.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="R27" t="n">
         <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U27" t="n">
         <v>1.94</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5703,7 +5703,7 @@
         <v>22</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
@@ -5715,62 +5715,62 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>14.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT27" t="n">
         <v>6.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
         <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX27" t="n">
         <v>7.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ27" t="n">
         <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BC27" t="n">
         <v>13</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G28" t="n">
         <v>2.04</v>
@@ -5831,10 +5831,10 @@
         <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
         <v>1.31</v>
@@ -5843,7 +5843,7 @@
         <v>3.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -5995,58 +5995,58 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H29" t="n">
         <v>3.5</v>
       </c>
       <c r="I29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J29" t="n">
         <v>3.9</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.95</v>
       </c>
       <c r="K29" t="n">
         <v>4.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M29" t="n">
         <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O29" t="n">
         <v>1.19</v>
       </c>
       <c r="P29" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="R29" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S29" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
         <v>1.56</v>
       </c>
       <c r="U29" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="X29" t="n">
         <v>30</v>
@@ -6064,10 +6064,10 @@
         <v>17</v>
       </c>
       <c r="AC29" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE29" t="n">
         <v>44</v>
@@ -6079,10 +6079,10 @@
         <v>13.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ29" t="n">
         <v>30</v>
@@ -6097,10 +6097,10 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP29" t="n">
         <v>18</v>
@@ -6109,22 +6109,22 @@
         <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AT29" t="n">
         <v>10</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV29" t="n">
         <v>11.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX29" t="n">
         <v>11.5</v>
@@ -6136,7 +6136,7 @@
         <v>11</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BB29" t="n">
         <v>18</v>
@@ -6148,7 +6148,7 @@
         <v>19</v>
       </c>
       <c r="BE29" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BF29" t="n">
         <v>7</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -6192,22 +6192,22 @@
         <v>1.63</v>
       </c>
       <c r="G30" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I30" t="n">
         <v>7.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
         <v>5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -6219,7 +6219,7 @@
         <v>1.3</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="Q30" t="n">
         <v>1.86</v>
@@ -6228,19 +6228,19 @@
         <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="T30" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U30" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V30" t="n">
         <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6303,7 +6303,7 @@
         <v>3.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS30" t="n">
         <v>4.1</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -6386,34 +6386,34 @@
         <v>2.74</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H31" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I31" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L31" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="n">
         <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q31" t="n">
         <v>2.3</v>
@@ -6425,31 +6425,31 @@
         <v>4.3</v>
       </c>
       <c r="T31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.92</v>
       </c>
-      <c r="U31" t="n">
-        <v>1.9</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X31" t="n">
         <v>10.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC31" t="n">
         <v>7.4</v>
@@ -6476,7 +6476,7 @@
         <v>50</v>
       </c>
       <c r="AK31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL31" t="n">
         <v>60</v>
@@ -6488,10 +6488,10 @@
         <v>42</v>
       </c>
       <c r="AO31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ31" t="n">
         <v>8.4</v>
@@ -6500,7 +6500,7 @@
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT31" t="n">
         <v>8.199999999999999</v>
@@ -6512,7 +6512,7 @@
         <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX31" t="n">
         <v>15.5</v>
@@ -6524,29 +6524,29 @@
         <v>16.5</v>
       </c>
       <c r="BA31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC31" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB31" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG31" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>7</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -6586,13 +6586,13 @@
         <v>13</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J32" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="K32" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L32" t="n">
         <v>1.21</v>
@@ -6607,16 +6607,16 @@
         <v>1.16</v>
       </c>
       <c r="P32" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q32" t="n">
         <v>1.49</v>
       </c>
       <c r="R32" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="S32" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T32" t="n">
         <v>2</v>
@@ -6628,85 +6628,85 @@
         <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X32" t="n">
         <v>34</v>
       </c>
       <c r="Y32" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z32" t="n">
         <v>160</v>
       </c>
       <c r="AA32" t="n">
-        <v>640</v>
+        <v>820</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AD32" t="n">
         <v>55</v>
       </c>
       <c r="AE32" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AF32" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AG32" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
         <v>34</v>
       </c>
       <c r="AI32" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL32" t="n">
         <v>36</v>
       </c>
       <c r="AM32" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN32" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AO32" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.2</v>
+        <v>26</v>
       </c>
       <c r="AQ32" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AT32" t="n">
         <v>10</v>
       </c>
       <c r="AU32" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX32" t="n">
         <v>7.8</v>
@@ -6715,32 +6715,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BG32" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G33" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H33" t="n">
         <v>3.95</v>
@@ -6783,28 +6783,28 @@
         <v>4.3</v>
       </c>
       <c r="J33" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
         <v>1.34</v>
       </c>
       <c r="M33" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P33" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
         <v>1.32</v>
@@ -6813,7 +6813,7 @@
         <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U33" t="n">
         <v>1.86</v>
@@ -6822,10 +6822,10 @@
         <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="X33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y33" t="n">
         <v>970</v>
@@ -6849,7 +6849,7 @@
         <v>65</v>
       </c>
       <c r="AF33" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG33" t="n">
         <v>970</v>
@@ -6876,46 +6876,46 @@
         <v>970</v>
       </c>
       <c r="AO33" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ33" t="n">
         <v>11.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AU33" t="n">
         <v>7</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC33" t="n">
         <v>4.6</v>
@@ -6924,24 +6924,24 @@
         <v>27</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I34" t="n">
         <v>4.5</v>
       </c>
-      <c r="G34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.16</v>
-      </c>
       <c r="J34" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="M34" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>5.8</v>
       </c>
       <c r="O34" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>1.53</v>
+        <v>2.64</v>
       </c>
       <c r="Q34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U34" t="n">
         <v>2.58</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.68</v>
-      </c>
       <c r="V34" t="n">
-        <v>1.86</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y34" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.6</v>
+        <v>20</v>
       </c>
       <c r="AQ34" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="AR34" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AS34" t="n">
         <v>4.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.5</v>
+        <v>38</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,108 +7145,108 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>14:50:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Al-Jndal</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="G35" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H35" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I35" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K35" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N35" t="n">
-        <v>1.78</v>
+        <v>2.58</v>
       </c>
       <c r="O35" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P35" t="n">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.81</v>
+        <v>2.58</v>
       </c>
       <c r="R35" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.81</v>
+        <v>5.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V35" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="W35" t="n">
         <v>1.21</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ35" t="n">
         <v>1000</v>
@@ -7267,69 +7267,69 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,184 +7339,184 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Al-Jndal</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.54</v>
+        <v>5.2</v>
       </c>
       <c r="G36" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I36" t="n">
         <v>1.76</v>
       </c>
-      <c r="H36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I36" t="n">
-        <v>6.2</v>
-      </c>
       <c r="J36" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD36" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="O36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X36" t="n">
+      <c r="AE36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN36" t="n">
         <v>90</v>
       </c>
-      <c r="Y36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AO36" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AU36" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="AZ36" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.1</v>
+        <v>28</v>
       </c>
       <c r="BB36" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BC36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE36" t="n">
         <v>11</v>
       </c>
-      <c r="BD36" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF36" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -7538,179 +7538,179 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="G37" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="H37" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
+        <v>11</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X37" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
         <v>4.5</v>
       </c>
-      <c r="J37" t="n">
+      <c r="AO37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA37" t="n">
         <v>4.1</v>
       </c>
-      <c r="K37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ37" t="n">
+      <c r="BB37" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC37" t="n">
         <v>11</v>
       </c>
-      <c r="BA37" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>13</v>
-      </c>
       <c r="BD37" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BE37" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="BG37" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -7747,34 +7747,34 @@
         <v>4.2</v>
       </c>
       <c r="H38" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="I38" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J38" t="n">
         <v>3.3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L38" t="n">
         <v>1.45</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N38" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
         <v>1.4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
         <v>1.29</v>
@@ -7786,16 +7786,16 @@
         <v>1.89</v>
       </c>
       <c r="U38" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V38" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="W38" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y38" t="n">
         <v>8.6</v>
@@ -7804,7 +7804,7 @@
         <v>13.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB38" t="n">
         <v>14</v>
@@ -7816,7 +7816,7 @@
         <v>11</v>
       </c>
       <c r="AE38" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF38" t="n">
         <v>30</v>
@@ -7825,13 +7825,13 @@
         <v>18</v>
       </c>
       <c r="AH38" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI38" t="n">
         <v>46</v>
       </c>
       <c r="AJ38" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AK38" t="n">
         <v>60</v>
@@ -7840,25 +7840,25 @@
         <v>70</v>
       </c>
       <c r="AM38" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN38" t="n">
         <v>70</v>
       </c>
       <c r="AO38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ38" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR38" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS38" t="n">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="AT38" t="n">
         <v>12</v>
@@ -7873,22 +7873,22 @@
         <v>22</v>
       </c>
       <c r="AX38" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AY38" t="n">
         <v>15</v>
       </c>
       <c r="AZ38" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA38" t="n">
         <v>10.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD38" t="n">
         <v>11.5</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -7944,16 +7944,16 @@
         <v>2.66</v>
       </c>
       <c r="I39" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K39" t="n">
         <v>3.45</v>
       </c>
       <c r="L39" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
         <v>1.09</v>
@@ -7962,28 +7962,28 @@
         <v>3.15</v>
       </c>
       <c r="O39" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P39" t="n">
         <v>1.73</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R39" t="n">
         <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T39" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U39" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W39" t="n">
         <v>1.48</v>
@@ -8094,11 +8094,11 @@
         <v>6.6</v>
       </c>
       <c r="BG39" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -8129,16 +8129,16 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G40" t="n">
         <v>2.12</v>
       </c>
-      <c r="G40" t="n">
-        <v>2.16</v>
-      </c>
       <c r="H40" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J40" t="n">
         <v>3.4</v>
@@ -8159,28 +8159,28 @@
         <v>1.44</v>
       </c>
       <c r="P40" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R40" t="n">
         <v>1.26</v>
       </c>
       <c r="S40" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U40" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W40" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X40" t="n">
         <v>10.5</v>
@@ -8207,7 +8207,7 @@
         <v>65</v>
       </c>
       <c r="AF40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG40" t="n">
         <v>11</v>
@@ -8216,13 +8216,13 @@
         <v>21</v>
       </c>
       <c r="AI40" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ40" t="n">
         <v>26</v>
       </c>
       <c r="AK40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL40" t="n">
         <v>48</v>
@@ -8246,7 +8246,7 @@
         <v>27</v>
       </c>
       <c r="AS40" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT40" t="n">
         <v>7.4</v>
@@ -8270,7 +8270,7 @@
         <v>19.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB40" t="n">
         <v>24</v>
@@ -8288,11 +8288,11 @@
         <v>19.5</v>
       </c>
       <c r="BG40" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G41" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" t="n">
         <v>4.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>4.2</v>
       </c>
       <c r="J41" t="n">
         <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.31</v>
@@ -8356,7 +8356,7 @@
         <v>2.52</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R41" t="n">
         <v>1.61</v>
@@ -8368,19 +8368,19 @@
         <v>1.6</v>
       </c>
       <c r="U41" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V41" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X41" t="n">
         <v>22</v>
       </c>
       <c r="Y41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="n">
         <v>34</v>
@@ -8401,7 +8401,7 @@
         <v>40</v>
       </c>
       <c r="AF41" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG41" t="n">
         <v>10</v>
@@ -8416,7 +8416,7 @@
         <v>23</v>
       </c>
       <c r="AK41" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL41" t="n">
         <v>25</v>
@@ -8428,7 +8428,7 @@
         <v>9</v>
       </c>
       <c r="AO41" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP41" t="n">
         <v>21</v>
@@ -8437,13 +8437,13 @@
         <v>20</v>
       </c>
       <c r="AR41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS41" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT41" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU41" t="n">
         <v>9</v>
@@ -8452,10 +8452,10 @@
         <v>15.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX41" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY41" t="n">
         <v>9.800000000000001</v>
@@ -8470,7 +8470,7 @@
         <v>21</v>
       </c>
       <c r="BC41" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD41" t="n">
         <v>24</v>
@@ -8482,11 +8482,11 @@
         <v>8.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -8523,13 +8523,13 @@
         <v>2.18</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I42" t="n">
         <v>4.1</v>
       </c>
       <c r="J42" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K42" t="n">
         <v>3.5</v>
@@ -8541,13 +8541,13 @@
         <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
         <v>1.38</v>
       </c>
       <c r="P42" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q42" t="n">
         <v>2.16</v>
@@ -8562,13 +8562,13 @@
         <v>1.9</v>
       </c>
       <c r="U42" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V42" t="n">
         <v>1.32</v>
       </c>
       <c r="W42" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X42" t="n">
         <v>12</v>
@@ -8577,7 +8577,7 @@
         <v>13.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA42" t="n">
         <v>85</v>
@@ -8589,7 +8589,7 @@
         <v>7.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE42" t="n">
         <v>55</v>
@@ -8601,7 +8601,7 @@
         <v>11</v>
       </c>
       <c r="AH42" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI42" t="n">
         <v>65</v>
@@ -8634,13 +8634,13 @@
         <v>25</v>
       </c>
       <c r="AS42" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AT42" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
         <v>14.5</v>
@@ -8667,10 +8667,10 @@
         <v>21</v>
       </c>
       <c r="BD42" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE42" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BF42" t="n">
         <v>16.5</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -8735,16 +8735,16 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O43" t="n">
         <v>1.01</v>
       </c>
       <c r="P43" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="R43" t="n">
         <v>1.16</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -8929,25 +8929,25 @@
         <v>1.02</v>
       </c>
       <c r="N44" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="O44" t="n">
         <v>1.07</v>
       </c>
       <c r="P44" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q44" t="n">
         <v>1.07</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="S44" t="n">
-        <v>1.07</v>
+        <v>1.52</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="U44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -9123,22 +9123,22 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O45" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P45" t="n">
         <v>1.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R45" t="n">
         <v>1.24</v>
       </c>
       <c r="S45" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -9317,28 +9317,28 @@
         <v>1.02</v>
       </c>
       <c r="N46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O46" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P46" t="n">
         <v>1.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S46" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -9487,16 +9487,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="G47" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H47" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I47" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J47" t="n">
         <v>4</v>
@@ -9505,7 +9505,7 @@
         <v>4.1</v>
       </c>
       <c r="L47" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="M47" t="n">
         <v>1.08</v>
@@ -9535,37 +9535,37 @@
         <v>1.84</v>
       </c>
       <c r="V47" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W47" t="n">
         <v>2.48</v>
       </c>
       <c r="X47" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z47" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA47" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB47" t="n">
         <v>7.2</v>
       </c>
       <c r="AC47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF47" t="n">
         <v>9</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AG47" t="n">
         <v>10</v>
@@ -9574,61 +9574,61 @@
         <v>24</v>
       </c>
       <c r="AI47" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ47" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK47" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL47" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM47" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN47" t="n">
         <v>12</v>
       </c>
       <c r="AO47" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP47" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR47" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AS47" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT47" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU47" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV47" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AW47" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX47" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY47" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ47" t="n">
         <v>21</v>
       </c>
       <c r="BA47" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB47" t="n">
         <v>14.5</v>
@@ -9637,20 +9637,20 @@
         <v>17</v>
       </c>
       <c r="BD47" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BE47" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF47" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF47" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG47" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -9684,10 +9684,10 @@
         <v>4.7</v>
       </c>
       <c r="G48" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H48" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I48" t="n">
         <v>1.97</v>
@@ -9699,7 +9699,7 @@
         <v>3.75</v>
       </c>
       <c r="L48" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M48" t="n">
         <v>1.09</v>
@@ -9732,7 +9732,7 @@
         <v>2.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X48" t="n">
         <v>14</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
         <v>2.06</v>
       </c>
       <c r="U49" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V49" t="n">
         <v>1.32</v>
@@ -10013,7 +10013,7 @@
         <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA49" t="n">
         <v>8.6</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="G50" t="n">
         <v>3.7</v>
@@ -10081,40 +10081,40 @@
         <v>2.62</v>
       </c>
       <c r="J50" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K50" t="n">
         <v>3.6</v>
       </c>
       <c r="L50" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M50" t="n">
         <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O50" t="n">
         <v>1.39</v>
       </c>
       <c r="P50" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q50" t="n">
         <v>2.16</v>
       </c>
       <c r="R50" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S50" t="n">
-        <v>2.16</v>
+        <v>3.55</v>
       </c>
       <c r="T50" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U50" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V50" t="n">
         <v>1.61</v>
@@ -10123,7 +10123,7 @@
         <v>1.37</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y50" t="n">
         <v>10.5</v>
@@ -10132,7 +10132,7 @@
         <v>17.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB50" t="n">
         <v>13</v>
@@ -10141,7 +10141,7 @@
         <v>8.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE50" t="n">
         <v>36</v>
@@ -10150,89 +10150,89 @@
         <v>27</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI50" t="n">
         <v>55</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK50" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -10263,58 +10263,58 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G51" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H51" t="n">
         <v>2.94</v>
       </c>
       <c r="I51" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J51" t="n">
         <v>3.1</v>
       </c>
-      <c r="J51" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K51" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L51" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M51" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N51" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O51" t="n">
         <v>1.47</v>
       </c>
       <c r="P51" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R51" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S51" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T51" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U51" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V51" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W51" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X51" t="n">
         <v>11.5</v>
@@ -10329,7 +10329,7 @@
         <v>60</v>
       </c>
       <c r="AB51" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC51" t="n">
         <v>970</v>
@@ -10338,7 +10338,7 @@
         <v>970</v>
       </c>
       <c r="AE51" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF51" t="n">
         <v>970</v>
@@ -10350,7 +10350,7 @@
         <v>25</v>
       </c>
       <c r="AI51" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AJ51" t="n">
         <v>55</v>
@@ -10362,25 +10362,25 @@
         <v>65</v>
       </c>
       <c r="AM51" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN51" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO51" t="n">
         <v>60</v>
       </c>
       <c r="AP51" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR51" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AS51" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT51" t="n">
         <v>7.6</v>
@@ -10389,44 +10389,44 @@
         <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AY51" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AZ51" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA51" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG51" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -10469,13 +10469,13 @@
         <v>3.15</v>
       </c>
       <c r="J52" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K52" t="n">
         <v>3.3</v>
       </c>
       <c r="L52" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="M52" t="n">
         <v>1.12</v>
@@ -10502,7 +10502,7 @@
         <v>2.04</v>
       </c>
       <c r="U52" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V52" t="n">
         <v>1.47</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -10660,16 +10660,16 @@
         <v>4.7</v>
       </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K53" t="n">
         <v>3.6</v>
       </c>
       <c r="L53" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M53" t="n">
         <v>1.09</v>
@@ -10699,10 +10699,10 @@
         <v>1.79</v>
       </c>
       <c r="V53" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W53" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X53" t="n">
         <v>12</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G54" t="n">
         <v>2.12</v>
@@ -10860,7 +10860,7 @@
         <v>2.96</v>
       </c>
       <c r="K54" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L54" t="n">
         <v>1.5</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
         <v>1000</v>
       </c>
       <c r="H56" t="n">
-        <v>1.76</v>
+        <v>1.09</v>
       </c>
       <c r="I56" t="n">
         <v>1000</v>
@@ -11284,7 +11284,7 @@
         <v>1.01</v>
       </c>
       <c r="W56" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -11436,10 +11436,10 @@
         <v>3.55</v>
       </c>
       <c r="I57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K57" t="n">
         <v>4.1</v>
@@ -11451,16 +11451,16 @@
         <v>1.06</v>
       </c>
       <c r="N57" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O57" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R57" t="n">
         <v>1.39</v>
@@ -11469,13 +11469,13 @@
         <v>3.05</v>
       </c>
       <c r="T57" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U57" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V57" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W57" t="n">
         <v>1.84</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -11815,58 +11815,58 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G59" t="n">
         <v>1.66</v>
       </c>
       <c r="H59" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I59" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="J59" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K59" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L59" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M59" t="n">
         <v>1.09</v>
       </c>
       <c r="N59" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="O59" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P59" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="R59" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T59" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="U59" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V59" t="n">
         <v>1.13</v>
       </c>
       <c r="W59" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11905,7 +11905,7 @@
         <v>1000</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK59" t="n">
         <v>1000</v>
@@ -11923,62 +11923,62 @@
         <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.79</v>
+        <v>5.9</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AT59" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="AU59" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="AX59" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY59" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.21</v>
+        <v>2.04</v>
       </c>
       <c r="BB59" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="BF59" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
@@ -796,7 +796,7 @@
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T2" t="n">
         <v>1.87</v>
@@ -808,13 +808,13 @@
         <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -838,7 +838,7 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -871,10 +871,10 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -886,41 +886,41 @@
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BC2" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.89</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
         <v>4.4</v>
@@ -969,7 +969,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1002,7 +1002,7 @@
         <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
         <v>15</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>2.22</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.55</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.48</v>
@@ -1178,16 +1178,16 @@
         <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
         <v>1.75</v>
@@ -1196,7 +1196,7 @@
         <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>2.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.42</v>
+        <v>2.26</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>1.96</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.63</v>
+        <v>3.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.5</v>
+        <v>1.87</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>2.86</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>2.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.7</v>
+        <v>1.68</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.57</v>
+        <v>2.68</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.57</v>
+        <v>2.66</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.59</v>
+        <v>2.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.57</v>
+        <v>2.68</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
         <v>3.75</v>
@@ -1369,7 +1369,7 @@
         <v>1.47</v>
       </c>
       <c r="P5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q5" t="n">
         <v>2.4</v>
@@ -1381,7 +1381,7 @@
         <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
         <v>1.71</v>
@@ -1390,7 +1390,7 @@
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1411,19 +1411,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>130</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>140</v>
@@ -1453,10 +1453,10 @@
         <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
         <v>5.6</v>
@@ -1465,10 +1465,10 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX5" t="n">
         <v>7.6</v>
@@ -1480,7 +1480,7 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB5" t="n">
         <v>16</v>
@@ -1489,20 +1489,20 @@
         <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5" t="n">
         <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
@@ -1575,7 +1575,7 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.74</v>
@@ -1671,19 +1671,19 @@
         <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA6" t="n">
         <v>7.8</v>
       </c>
       <c r="BB6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD6" t="n">
         <v>8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
         <v>8.4</v>
@@ -1692,11 +1692,11 @@
         <v>8</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>2.48</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I9" t="n">
         <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
@@ -2139,7 +2139,7 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>1.34</v>
@@ -2157,22 +2157,22 @@
         <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
@@ -2205,10 +2205,10 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
         <v>46</v>
@@ -2217,10 +2217,10 @@
         <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AP9" t="n">
         <v>12</v>
@@ -2229,22 +2229,22 @@
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT9" t="n">
         <v>9.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX9" t="n">
         <v>13.5</v>
@@ -2253,32 +2253,32 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BF9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
         <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
@@ -2345,19 +2345,19 @@
         <v>2.46</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
         <v>1.41</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>3.25</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
         <v>3.55</v>
@@ -2551,10 +2551,10 @@
         <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
         <v>15</v>
@@ -2575,7 +2575,7 @@
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>29</v>
@@ -2584,13 +2584,13 @@
         <v>24</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ11" t="n">
         <v>65</v>
@@ -2620,7 +2620,7 @@
         <v>13</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -2644,29 +2644,29 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
         <v>42</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG11" t="n">
         <v>17</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.84</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
@@ -2709,7 +2709,7 @@
         <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
@@ -2748,7 +2748,7 @@
         <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2805,7 +2805,7 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="AQ12" t="n">
         <v>3.9</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.34</v>
       </c>
       <c r="G13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H13" t="n">
         <v>6.8</v>
@@ -2903,10 +2903,10 @@
         <v>12.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.33</v>
@@ -2921,7 +2921,7 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
         <v>1.71</v>
@@ -2930,7 +2930,7 @@
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
         <v>2.12</v>
@@ -2942,13 +2942,13 @@
         <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
         <v>130</v>
@@ -2957,7 +2957,7 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
         <v>1000</v>
@@ -2972,10 +2972,10 @@
         <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
         <v>190</v>
@@ -2987,7 +2987,7 @@
         <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AV13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>6.6</v>
       </c>
-      <c r="AW13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.39</v>
@@ -3133,122 +3133,122 @@
         <v>1.77</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X14" t="n">
         <v>18</v>
       </c>
       <c r="Y14" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
         <v>28</v>
       </c>
-      <c r="Z14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>32</v>
-      </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX14" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="AY14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF14" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
         <v>1.59</v>
@@ -3333,7 +3333,7 @@
         <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Y15" t="n">
         <v>970</v>
@@ -3345,7 +3345,7 @@
         <v>970</v>
       </c>
       <c r="AB15" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
         <v>970</v>
@@ -3360,10 +3360,10 @@
         <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
         <v>36</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -3482,10 +3482,10 @@
         <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3497,7 +3497,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
@@ -3581,52 +3581,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
         <v>1.39</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>26</v>
       </c>
       <c r="I18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J18" t="n">
         <v>8.800000000000001</v>
@@ -3897,7 +3897,7 @@
         <v>1.34</v>
       </c>
       <c r="R18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S18" t="n">
         <v>1.85</v>
@@ -3906,19 +3906,19 @@
         <v>2.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="X18" t="n">
         <v>55</v>
       </c>
       <c r="Y18" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="Z18" t="n">
         <v>350</v>
@@ -3933,10 +3933,10 @@
         <v>29</v>
       </c>
       <c r="AD18" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AE18" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="AF18" t="n">
         <v>10.5</v>
@@ -3945,10 +3945,10 @@
         <v>17.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AJ18" t="n">
         <v>9.6</v>
@@ -3957,74 +3957,74 @@
         <v>17.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
         <v>310</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB18" t="n">
         <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF18" t="n">
         <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H20" t="n">
         <v>2.62</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.24</v>
@@ -4294,16 +4294,16 @@
         <v>1.53</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X20" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
         <v>20</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.34</v>
       </c>
       <c r="G21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H21" t="n">
         <v>7.8</v>
@@ -4455,7 +4455,7 @@
         <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K21" t="n">
         <v>7.8</v>
@@ -4494,13 +4494,13 @@
         <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="X21" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
         <v>110</v>
@@ -4527,7 +4527,7 @@
         <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
         <v>110</v>
@@ -4581,13 +4581,13 @@
         <v>8.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA21" t="n">
         <v>5.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>3.95</v>
       </c>
       <c r="BC21" t="n">
         <v>10.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4643,13 @@
         <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="J22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -4658,7 +4658,7 @@
         <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
         <v>4</v>
@@ -4670,7 +4670,7 @@
         <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R22" t="n">
         <v>1.4</v>
@@ -4694,13 +4694,13 @@
         <v>15.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22" t="n">
         <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB22" t="n">
         <v>17.5</v>
@@ -4712,13 +4712,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF22" t="n">
         <v>38</v>
       </c>
       <c r="AG22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH22" t="n">
         <v>19</v>
@@ -4730,7 +4730,7 @@
         <v>120</v>
       </c>
       <c r="AK22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL22" t="n">
         <v>65</v>
@@ -4748,25 +4748,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR22" t="n">
         <v>10.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT22" t="n">
         <v>16.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
         <v>9.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX22" t="n">
         <v>34</v>
@@ -4775,13 +4775,13 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA22" t="n">
         <v>30</v>
       </c>
       <c r="BB22" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="BC22" t="n">
         <v>55</v>
@@ -4790,7 +4790,7 @@
         <v>55</v>
       </c>
       <c r="BE22" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF22" t="n">
         <v>55</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>2.8</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I23" t="n">
         <v>3.05</v>
@@ -4855,31 +4855,31 @@
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U23" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
         <v>1.55</v>
@@ -4897,13 +4897,13 @@
         <v>55</v>
       </c>
       <c r="AB23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
         <v>7.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
         <v>38</v>
@@ -4915,7 +4915,7 @@
         <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>55</v>
@@ -4933,7 +4933,7 @@
         <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AO23" t="n">
         <v>38</v>
@@ -4942,13 +4942,13 @@
         <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR23" t="n">
         <v>16.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT23" t="n">
         <v>8.800000000000001</v>
@@ -4957,7 +4957,7 @@
         <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4969,13 +4969,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BC23" t="n">
         <v>21</v>
@@ -4987,14 +4987,14 @@
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BG23" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
         <v>1.36</v>
@@ -5073,13 +5073,13 @@
         <v>2.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W24" t="n">
         <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y24" t="n">
         <v>12.5</v>
@@ -5124,7 +5124,7 @@
         <v>40</v>
       </c>
       <c r="AM24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="n">
         <v>27</v>
@@ -5145,7 +5145,7 @@
         <v>28</v>
       </c>
       <c r="AT24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -5163,7 +5163,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
@@ -5178,17 +5178,17 @@
         <v>28</v>
       </c>
       <c r="BE24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF24" t="n">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="BG24" t="n">
         <v>14.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H25" t="n">
         <v>9.6</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K25" t="n">
         <v>6.6</v>
@@ -5243,7 +5243,7 @@
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.19</v>
@@ -5270,19 +5270,19 @@
         <v>1.1</v>
       </c>
       <c r="W25" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X25" t="n">
         <v>27</v>
       </c>
       <c r="Y25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z25" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA25" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
         <v>10.5</v>
@@ -5291,16 +5291,16 @@
         <v>14.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE25" t="n">
         <v>150</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>27</v>
@@ -5312,10 +5312,10 @@
         <v>11.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
         <v>140</v>
@@ -5327,31 +5327,31 @@
         <v>150</v>
       </c>
       <c r="AP25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ25" t="n">
         <v>30</v>
       </c>
       <c r="AR25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS25" t="n">
         <v>11</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>12</v>
       </c>
       <c r="AT25" t="n">
         <v>9</v>
       </c>
       <c r="AU25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY25" t="n">
         <v>9.199999999999999</v>
@@ -5360,7 +5360,7 @@
         <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB25" t="n">
         <v>10</v>
@@ -5372,17 +5372,17 @@
         <v>27</v>
       </c>
       <c r="BE25" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF25" t="n">
         <v>4.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -5440,13 +5440,13 @@
         <v>1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="R26" t="n">
         <v>1.65</v>
@@ -5458,7 +5458,7 @@
         <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -5482,7 +5482,7 @@
         <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD26" t="n">
         <v>1000</v>
@@ -5527,13 +5527,13 @@
         <v>4.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS26" t="n">
         <v>4.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AU26" t="n">
         <v>3.6</v>
@@ -5545,13 +5545,13 @@
         <v>4.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA26" t="n">
         <v>4.5</v>
@@ -5563,20 +5563,20 @@
         <v>4</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE26" t="n">
         <v>4.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG26" t="n">
         <v>4.3</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
         <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T27" t="n">
         <v>2.02</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>3.65</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I28" t="n">
         <v>2.24</v>
       </c>
       <c r="J28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
         <v>3.65</v>
@@ -5825,13 +5825,13 @@
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
         <v>1.96</v>
@@ -5846,37 +5846,37 @@
         <v>1.79</v>
       </c>
       <c r="U28" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V28" t="n">
         <v>1.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y28" t="n">
         <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AA28" t="n">
         <v>30</v>
       </c>
       <c r="AB28" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AC28" t="n">
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF28" t="n">
         <v>34</v>
@@ -5894,10 +5894,10 @@
         <v>75</v>
       </c>
       <c r="AK28" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -5906,19 +5906,19 @@
         <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP28" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR28" t="n">
         <v>12</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.4</v>
+        <v>17.5</v>
       </c>
       <c r="AT28" t="n">
         <v>13</v>
@@ -5933,7 +5933,7 @@
         <v>21</v>
       </c>
       <c r="AX28" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY28" t="n">
         <v>14</v>
@@ -5945,26 +5945,26 @@
         <v>32</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.7</v>
+        <v>24</v>
       </c>
       <c r="BD28" t="n">
         <v>44</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="BG28" t="n">
         <v>14.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -6025,22 +6025,22 @@
         <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
         <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V29" t="n">
         <v>1.47</v>
@@ -6112,7 +6112,7 @@
         <v>17</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AT29" t="n">
         <v>9.6</v>
@@ -6154,11 +6154,11 @@
         <v>21</v>
       </c>
       <c r="BG29" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I30" t="n">
         <v>2.48</v>
@@ -6225,16 +6225,16 @@
         <v>1.71</v>
       </c>
       <c r="R30" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S30" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T30" t="n">
         <v>1.61</v>
       </c>
       <c r="U30" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V30" t="n">
         <v>1.68</v>
@@ -6249,10 +6249,10 @@
         <v>14</v>
       </c>
       <c r="Z30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB30" t="n">
         <v>15.5</v>
@@ -6276,7 +6276,7 @@
         <v>16</v>
       </c>
       <c r="AI30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
         <v>1000</v>
@@ -6339,20 +6339,20 @@
         <v>25</v>
       </c>
       <c r="BD30" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BE30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF30" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BG30" t="n">
         <v>13</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O31" t="n">
         <v>1.31</v>
@@ -6425,7 +6425,7 @@
         <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U31" t="n">
         <v>1.94</v>
@@ -6452,7 +6452,7 @@
         <v>9.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD31" t="n">
         <v>29</v>
@@ -6503,7 +6503,7 @@
         <v>4.9</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
@@ -6512,7 +6512,7 @@
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX31" t="n">
         <v>7.4</v>
@@ -6527,16 +6527,16 @@
         <v>4.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD31" t="n">
         <v>26</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF31" t="n">
         <v>7.6</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -6577,19 +6577,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G32" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H32" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K32" t="n">
         <v>4.3</v>
@@ -6625,7 +6625,7 @@
         <v>1.94</v>
       </c>
       <c r="V32" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W32" t="n">
         <v>2.26</v>
@@ -6685,7 +6685,7 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AQ32" t="n">
         <v>3.65</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -6774,13 +6774,13 @@
         <v>1.93</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H33" t="n">
         <v>4.3</v>
       </c>
       <c r="I33" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
         <v>3.55</v>
@@ -6789,13 +6789,13 @@
         <v>3.85</v>
       </c>
       <c r="L33" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
         <v>1.37</v>
@@ -6807,7 +6807,7 @@
         <v>2.08</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
         <v>3.85</v>
@@ -6816,7 +6816,7 @@
         <v>1.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V33" t="n">
         <v>1.27</v>
@@ -6837,7 +6837,7 @@
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC33" t="n">
         <v>8.6</v>
@@ -6885,13 +6885,13 @@
         <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AU33" t="n">
         <v>7</v>
@@ -6900,19 +6900,19 @@
         <v>15.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX33" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ33" t="n">
         <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB33" t="n">
         <v>18.5</v>
@@ -6921,20 +6921,20 @@
         <v>18</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF33" t="n">
         <v>12</v>
       </c>
       <c r="BG33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
         <v>3.95</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L34" t="n">
         <v>1.23</v>
@@ -7079,10 +7079,10 @@
         <v>14.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT34" t="n">
         <v>10</v>
@@ -7094,7 +7094,7 @@
         <v>11.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX34" t="n">
         <v>11.5</v>
@@ -7106,7 +7106,7 @@
         <v>11</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB34" t="n">
         <v>18</v>
@@ -7118,7 +7118,7 @@
         <v>19</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF34" t="n">
         <v>7</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7159,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G35" t="n">
         <v>3.1</v>
       </c>
       <c r="H35" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I35" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K35" t="n">
         <v>3.35</v>
@@ -7201,13 +7201,13 @@
         <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U35" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V35" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W35" t="n">
         <v>1.47</v>
@@ -7219,13 +7219,13 @@
         <v>9.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA35" t="n">
         <v>48</v>
       </c>
       <c r="AB35" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC35" t="n">
         <v>7.4</v>
@@ -7237,10 +7237,10 @@
         <v>38</v>
       </c>
       <c r="AF35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH35" t="n">
         <v>21</v>
@@ -7276,13 +7276,13 @@
         <v>15.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV35" t="n">
         <v>11.5</v>
@@ -7300,29 +7300,29 @@
         <v>17</v>
       </c>
       <c r="BA35" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BC35" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD35" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF35" t="n">
         <v>29</v>
       </c>
       <c r="BG35" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
         <v>2.18</v>
       </c>
       <c r="T36" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U36" t="n">
         <v>1.93</v>
@@ -7407,7 +7407,7 @@
         <v>4.8</v>
       </c>
       <c r="X36" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Y36" t="n">
         <v>60</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.02</v>
       </c>
       <c r="G37" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H37" t="n">
         <v>3.95</v>
@@ -7559,10 +7559,10 @@
         <v>4.3</v>
       </c>
       <c r="J37" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K37" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L37" t="n">
         <v>1.34</v>
@@ -7598,7 +7598,7 @@
         <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X37" t="n">
         <v>15.5</v>
@@ -7631,7 +7631,7 @@
         <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI37" t="n">
         <v>75</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I38" t="n">
         <v>4.3</v>
@@ -7765,13 +7765,13 @@
         <v>1.03</v>
       </c>
       <c r="N38" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>1.16</v>
       </c>
       <c r="P38" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
         <v>1.49</v>
@@ -7795,7 +7795,7 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y38" t="n">
         <v>27</v>
@@ -7819,10 +7819,10 @@
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH38" t="n">
         <v>19</v>
@@ -7834,7 +7834,7 @@
         <v>28</v>
       </c>
       <c r="AK38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL38" t="n">
         <v>32</v>
@@ -7849,19 +7849,19 @@
         <v>30</v>
       </c>
       <c r="AP38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS38" t="n">
         <v>4.8</v>
       </c>
       <c r="AT38" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="AU38" t="n">
         <v>8.199999999999999</v>
@@ -7870,7 +7870,7 @@
         <v>12</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX38" t="n">
         <v>11.5</v>
@@ -7882,7 +7882,7 @@
         <v>11</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB38" t="n">
         <v>16.5</v>
@@ -7900,11 +7900,11 @@
         <v>6</v>
       </c>
       <c r="BG38" t="n">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -8010,16 +8010,16 @@
         <v>12</v>
       </c>
       <c r="AE39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF39" t="n">
         <v>38</v>
       </c>
       <c r="AG39" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AH39" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI39" t="n">
         <v>75</v>
@@ -8043,7 +8043,7 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ39" t="n">
         <v>5.6</v>
@@ -8061,7 +8061,7 @@
         <v>6.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW39" t="n">
         <v>6</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
         <v>5.9</v>
       </c>
       <c r="H40" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="I40" t="n">
         <v>1.74</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G41" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="H41" t="n">
         <v>4.5</v>
       </c>
       <c r="I41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K41" t="n">
         <v>6.2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K41" t="n">
-        <v>6.6</v>
       </c>
       <c r="L41" t="n">
         <v>1.12</v>
@@ -8347,28 +8347,28 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="O41" t="n">
         <v>1.06</v>
       </c>
       <c r="P41" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R41" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="S41" t="n">
         <v>1.53</v>
       </c>
       <c r="T41" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="U41" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
@@ -8392,7 +8392,7 @@
         <v>50</v>
       </c>
       <c r="AC41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD41" t="n">
         <v>28</v>
@@ -8401,61 +8401,61 @@
         <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG41" t="n">
         <v>15.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI41" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
         <v>26</v>
       </c>
       <c r="AK41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM41" t="n">
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AO41" t="n">
         <v>21</v>
       </c>
       <c r="AP41" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AQ41" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AR41" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AS41" t="n">
         <v>42</v>
       </c>
       <c r="AT41" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU41" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX41" t="n">
         <v>15</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>15.5</v>
       </c>
       <c r="AY41" t="n">
         <v>12.5</v>
@@ -8464,29 +8464,29 @@
         <v>12.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BB41" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD41" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BF41" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BG41" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -8523,16 +8523,16 @@
         <v>4.3</v>
       </c>
       <c r="H42" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I42" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J42" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L42" t="n">
         <v>1.45</v>
@@ -8547,7 +8547,7 @@
         <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q42" t="n">
         <v>2.2</v>
@@ -8559,13 +8559,13 @@
         <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U42" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V42" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W42" t="n">
         <v>1.3</v>
@@ -8577,7 +8577,7 @@
         <v>8.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA42" t="n">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>14</v>
       </c>
       <c r="AC42" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD42" t="n">
         <v>11</v>
@@ -8604,7 +8604,7 @@
         <v>19.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ42" t="n">
         <v>90</v>
@@ -8613,7 +8613,7 @@
         <v>60</v>
       </c>
       <c r="AL42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM42" t="n">
         <v>130</v>
@@ -8622,16 +8622,16 @@
         <v>70</v>
       </c>
       <c r="AO42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ42" t="n">
         <v>7.6</v>
       </c>
       <c r="AR42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS42" t="n">
         <v>23</v>
@@ -8655,32 +8655,32 @@
         <v>15.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC42" t="n">
         <v>12</v>
       </c>
-      <c r="BC42" t="n">
-        <v>48</v>
-      </c>
       <c r="BD42" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE42" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF42" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>11.5</v>
       </c>
       <c r="BG42" t="n">
         <v>17.5</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
         <v>3.45</v>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
@@ -8744,7 +8744,7 @@
         <v>1.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R43" t="n">
         <v>1.27</v>
@@ -8753,10 +8753,10 @@
         <v>4.2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U43" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>1.54</v>
@@ -8804,7 +8804,7 @@
         <v>55</v>
       </c>
       <c r="AK43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL43" t="n">
         <v>55</v>
@@ -8855,7 +8855,7 @@
         <v>40</v>
       </c>
       <c r="BB43" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC43" t="n">
         <v>30</v>
@@ -8864,7 +8864,7 @@
         <v>8.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF43" t="n">
         <v>6.8</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8941,7 @@
         <v>2.34</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S44" t="n">
         <v>4.5</v>
@@ -8962,7 +8962,7 @@
         <v>10.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z44" t="n">
         <v>29</v>
@@ -9016,7 +9016,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR44" t="n">
         <v>26</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -9102,13 +9102,13 @@
         <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H45" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I45" t="n">
         <v>4</v>
-      </c>
-      <c r="I45" t="n">
-        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>3.95</v>
@@ -9123,40 +9123,40 @@
         <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O45" t="n">
         <v>1.2</v>
       </c>
       <c r="P45" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R45" t="n">
         <v>1.62</v>
       </c>
       <c r="S45" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T45" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U45" t="n">
         <v>2.62</v>
       </c>
       <c r="V45" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W45" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z45" t="n">
         <v>32</v>
@@ -9165,7 +9165,7 @@
         <v>70</v>
       </c>
       <c r="AB45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC45" t="n">
         <v>9.199999999999999</v>
@@ -9189,7 +9189,7 @@
         <v>40</v>
       </c>
       <c r="AJ45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK45" t="n">
         <v>17.5</v>
@@ -9222,7 +9222,7 @@
         <v>12.5</v>
       </c>
       <c r="AU45" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV45" t="n">
         <v>15</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
         <v>2.14</v>
       </c>
       <c r="G46" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H46" t="n">
         <v>4</v>
@@ -9308,7 +9308,7 @@
         <v>3.4</v>
       </c>
       <c r="K46" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L46" t="n">
         <v>1.45</v>
@@ -9323,7 +9323,7 @@
         <v>1.38</v>
       </c>
       <c r="P46" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q46" t="n">
         <v>2.16</v>
@@ -9344,7 +9344,7 @@
         <v>1.32</v>
       </c>
       <c r="W46" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X46" t="n">
         <v>12</v>
@@ -9392,7 +9392,7 @@
         <v>42</v>
       </c>
       <c r="AM46" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>18</v>
@@ -9446,7 +9446,7 @@
         <v>38</v>
       </c>
       <c r="BE46" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF46" t="n">
         <v>16.5</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -9520,13 +9520,13 @@
         <v>1.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R47" t="n">
         <v>1.16</v>
       </c>
       <c r="S47" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T47" t="n">
         <v>1.11</v>
@@ -9595,52 +9595,52 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF47" t="n">
         <v>1.01</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G48" t="n">
         <v>1.82</v>
@@ -9690,16 +9690,16 @@
         <v>4.3</v>
       </c>
       <c r="I48" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K48" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M48" t="n">
         <v>1.02</v>
@@ -9708,28 +9708,28 @@
         <v>7.6</v>
       </c>
       <c r="O48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P48" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R48" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S48" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="T48" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U48" t="n">
         <v>3.2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W48" t="n">
         <v>2.22</v>
@@ -9789,62 +9789,62 @@
         <v>26</v>
       </c>
       <c r="AP48" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW48" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT48" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AX48" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="AY48" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ48" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB48" t="n">
         <v>16</v>
       </c>
       <c r="BC48" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="BD48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF48" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BG48" t="n">
-        <v>16</v>
+        <v>4.1</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G49" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H49" t="n">
         <v>5.5</v>
@@ -9887,7 +9887,7 @@
         <v>6.4</v>
       </c>
       <c r="J49" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K49" t="n">
         <v>6</v>
@@ -9899,7 +9899,7 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O49" t="n">
         <v>1.09</v>
@@ -9908,19 +9908,19 @@
         <v>3.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R49" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S49" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="T49" t="n">
         <v>1.47</v>
       </c>
       <c r="U49" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V49" t="n">
         <v>1.18</v>
@@ -9941,58 +9941,58 @@
         <v>1000</v>
       </c>
       <c r="AB49" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD49" t="n">
         <v>25</v>
       </c>
-      <c r="AC49" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>26</v>
-      </c>
       <c r="AE49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF49" t="n">
         <v>16.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH49" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI49" t="n">
         <v>55</v>
       </c>
       <c r="AJ49" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK49" t="n">
         <v>16</v>
       </c>
       <c r="AL49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM49" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN49" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AO49" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP49" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AR49" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT49" t="n">
         <v>17</v>
@@ -10004,22 +10004,22 @@
         <v>17.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="AX49" t="n">
         <v>11</v>
       </c>
       <c r="AY49" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ49" t="n">
         <v>13</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC49" t="n">
         <v>12</v>
@@ -10028,17 +10028,17 @@
         <v>17</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF49" t="n">
         <v>3.8</v>
       </c>
       <c r="BG49" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -10072,10 +10072,10 @@
         <v>1.36</v>
       </c>
       <c r="G50" t="n">
-        <v>110</v>
+        <v>1.68</v>
       </c>
       <c r="H50" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
@@ -10084,7 +10084,7 @@
         <v>4.5</v>
       </c>
       <c r="K50" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10102,127 +10102,127 @@
         <v>2.88</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="R50" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="S50" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T50" t="n">
-        <v>1.32</v>
+        <v>1.59</v>
       </c>
       <c r="U50" t="n">
         <v>1.87</v>
       </c>
       <c r="V50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W50" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP50" t="n">
         <v>1.01</v>
       </c>
-      <c r="X50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
         <v>1.01</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G51" t="n">
         <v>1.69</v>
@@ -10272,16 +10272,16 @@
         <v>6.2</v>
       </c>
       <c r="I51" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J51" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L51" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="M51" t="n">
         <v>1.08</v>
@@ -10305,7 +10305,7 @@
         <v>4</v>
       </c>
       <c r="T51" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U51" t="n">
         <v>1.86</v>
@@ -10326,7 +10326,7 @@
         <v>50</v>
       </c>
       <c r="AA51" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB51" t="n">
         <v>7</v>
@@ -10338,7 +10338,7 @@
         <v>25</v>
       </c>
       <c r="AE51" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF51" t="n">
         <v>9</v>
@@ -10347,7 +10347,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH51" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI51" t="n">
         <v>120</v>
@@ -10356,7 +10356,7 @@
         <v>18</v>
       </c>
       <c r="AK51" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL51" t="n">
         <v>44</v>
@@ -10368,25 +10368,25 @@
         <v>12.5</v>
       </c>
       <c r="AO51" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP51" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR51" t="n">
         <v>36</v>
       </c>
       <c r="AS51" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT51" t="n">
         <v>6.6</v>
       </c>
       <c r="AU51" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV51" t="n">
         <v>22</v>
@@ -10395,13 +10395,13 @@
         <v>15.5</v>
       </c>
       <c r="AX51" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY51" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA51" t="n">
         <v>15.5</v>
@@ -10410,7 +10410,7 @@
         <v>15.5</v>
       </c>
       <c r="BC51" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD51" t="n">
         <v>36</v>
@@ -10422,11 +10422,11 @@
         <v>11</v>
       </c>
       <c r="BG51" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
         <v>4.7</v>
       </c>
       <c r="G52" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H52" t="n">
         <v>1.87</v>
@@ -10475,7 +10475,7 @@
         <v>3.7</v>
       </c>
       <c r="L52" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
@@ -10487,10 +10487,10 @@
         <v>1.4</v>
       </c>
       <c r="P52" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R52" t="n">
         <v>1.26</v>
@@ -10535,7 +10535,7 @@
         <v>28</v>
       </c>
       <c r="AF52" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AG52" t="n">
         <v>25</v>
@@ -10544,7 +10544,7 @@
         <v>26</v>
       </c>
       <c r="AI52" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ52" t="n">
         <v>1000</v>
@@ -10589,7 +10589,7 @@
         <v>19</v>
       </c>
       <c r="AX52" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY52" t="n">
         <v>17</v>
@@ -10601,26 +10601,26 @@
         <v>36</v>
       </c>
       <c r="BB52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC52" t="n">
         <v>5</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>4.9</v>
       </c>
       <c r="BD52" t="n">
         <v>5</v>
       </c>
       <c r="BE52" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF52" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG52" t="n">
         <v>12</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -10651,58 +10651,58 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G53" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H53" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I53" t="n">
         <v>4.1</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K53" t="n">
         <v>3.3</v>
       </c>
       <c r="L53" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="M53" t="n">
         <v>1.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O53" t="n">
         <v>1.53</v>
       </c>
       <c r="P53" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="R53" t="n">
         <v>1.19</v>
       </c>
       <c r="S53" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T53" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U53" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V53" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W53" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X53" t="n">
         <v>9.199999999999999</v>
@@ -10711,7 +10711,7 @@
         <v>11</v>
       </c>
       <c r="Z53" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA53" t="n">
         <v>110</v>
@@ -10726,7 +10726,7 @@
         <v>18</v>
       </c>
       <c r="AE53" t="n">
-        <v>65</v>
+        <v>730</v>
       </c>
       <c r="AF53" t="n">
         <v>14</v>
@@ -10738,22 +10738,22 @@
         <v>25</v>
       </c>
       <c r="AI53" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AJ53" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK53" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AL53" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM53" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AN53" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AO53" t="n">
         <v>110</v>
@@ -10765,22 +10765,22 @@
         <v>9</v>
       </c>
       <c r="AR53" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AS53" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="AT53" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU53" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV53" t="n">
         <v>14.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AX53" t="n">
         <v>11</v>
@@ -10792,29 +10792,29 @@
         <v>20</v>
       </c>
       <c r="BA53" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BB53" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BC53" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BD53" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BE53" t="n">
-        <v>8.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BF53" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BG53" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
         <v>3.7</v>
       </c>
       <c r="H54" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I54" t="n">
         <v>2.62</v>
@@ -10869,13 +10869,13 @@
         <v>1.09</v>
       </c>
       <c r="N54" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
         <v>1.39</v>
       </c>
       <c r="P54" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q54" t="n">
         <v>2.16</v>
@@ -10884,7 +10884,7 @@
         <v>1.26</v>
       </c>
       <c r="S54" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T54" t="n">
         <v>1.86</v>
@@ -10962,7 +10962,7 @@
         <v>4</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT54" t="n">
         <v>3.8</v>
@@ -10974,41 +10974,41 @@
         <v>3.8</v>
       </c>
       <c r="AW54" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX54" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="AY54" t="n">
         <v>4</v>
       </c>
       <c r="AZ54" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="BA54" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB54" t="n">
         <v>4.9</v>
       </c>
       <c r="BC54" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE54" t="n">
         <v>5.1</v>
       </c>
       <c r="BF54" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BG54" t="n">
         <v>4.5</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -11042,13 +11042,13 @@
         <v>2.7</v>
       </c>
       <c r="G55" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="H55" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I55" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>3.1</v>
@@ -11057,22 +11057,22 @@
         <v>3.4</v>
       </c>
       <c r="L55" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M55" t="n">
         <v>1.1</v>
       </c>
       <c r="N55" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O55" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P55" t="n">
         <v>1.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R55" t="n">
         <v>1.24</v>
@@ -11081,16 +11081,16 @@
         <v>4.5</v>
       </c>
       <c r="T55" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U55" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V55" t="n">
         <v>1.47</v>
       </c>
       <c r="W55" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X55" t="n">
         <v>11.5</v>
@@ -11102,10 +11102,10 @@
         <v>970</v>
       </c>
       <c r="AA55" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC55" t="n">
         <v>970</v>
@@ -11114,7 +11114,7 @@
         <v>970</v>
       </c>
       <c r="AE55" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF55" t="n">
         <v>970</v>
@@ -11144,7 +11144,7 @@
         <v>48</v>
       </c>
       <c r="AO55" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP55" t="n">
         <v>4.8</v>
@@ -11153,10 +11153,10 @@
         <v>8.4</v>
       </c>
       <c r="AR55" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT55" t="n">
         <v>7.6</v>
@@ -11174,10 +11174,10 @@
         <v>14.5</v>
       </c>
       <c r="AY55" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AZ55" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA55" t="n">
         <v>7.2</v>
@@ -11189,10 +11189,10 @@
         <v>6.8</v>
       </c>
       <c r="BD55" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BE55" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF55" t="n">
         <v>6.8</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11248,7 @@
         <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L56" t="n">
         <v>1.55</v>
@@ -11353,16 +11353,16 @@
         <v>4.9</v>
       </c>
       <c r="AT56" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU56" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV56" t="n">
         <v>9</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX56" t="n">
         <v>15.5</v>
@@ -11374,29 +11374,29 @@
         <v>16.5</v>
       </c>
       <c r="BA56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB56" t="n">
         <v>5</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>4.9</v>
       </c>
       <c r="BC56" t="n">
         <v>4.9</v>
       </c>
       <c r="BD56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF56" t="n">
         <v>5</v>
       </c>
-      <c r="BE56" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF56" t="n">
+      <c r="BG56" t="n">
         <v>4.9</v>
       </c>
-      <c r="BG56" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -11427,25 +11427,25 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G57" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J57" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K57" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L57" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="M57" t="n">
         <v>1.09</v>
@@ -11463,10 +11463,10 @@
         <v>2.38</v>
       </c>
       <c r="R57" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S57" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T57" t="n">
         <v>2.08</v>
@@ -11478,7 +11478,7 @@
         <v>1.23</v>
       </c>
       <c r="W57" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X57" t="n">
         <v>12</v>
@@ -11535,22 +11535,22 @@
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>7.4</v>
+        <v>3.35</v>
       </c>
       <c r="AQ57" t="n">
         <v>3.55</v>
       </c>
       <c r="AR57" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS57" t="n">
         <v>4.3</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV57" t="n">
         <v>3.8</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -11630,22 +11630,22 @@
         <v>4.9</v>
       </c>
       <c r="I58" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J58" t="n">
         <v>2.96</v>
       </c>
       <c r="K58" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L58" t="n">
         <v>1.5</v>
       </c>
       <c r="M58" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N58" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O58" t="n">
         <v>1.56</v>
@@ -11660,7 +11660,7 @@
         <v>1.17</v>
       </c>
       <c r="S58" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T58" t="n">
         <v>2.1</v>
@@ -11669,7 +11669,7 @@
         <v>1.53</v>
       </c>
       <c r="V58" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W58" t="n">
         <v>1.9</v>
@@ -11687,7 +11687,7 @@
         <v>1000</v>
       </c>
       <c r="AB58" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC58" t="n">
         <v>9.199999999999999</v>
@@ -11699,10 +11699,10 @@
         <v>1000</v>
       </c>
       <c r="AF58" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG58" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH58" t="n">
         <v>1000</v>
@@ -11735,22 +11735,22 @@
         <v>9.4</v>
       </c>
       <c r="AR58" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AS58" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AT58" t="n">
         <v>4.6</v>
       </c>
       <c r="AU58" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV58" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AW58" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AX58" t="n">
         <v>7.6</v>
@@ -11759,32 +11759,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ58" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA58" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BB58" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC58" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE58" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF58" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BG58" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -11818,55 +11818,55 @@
         <v>3.2</v>
       </c>
       <c r="G59" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H59" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="I59" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="J59" t="n">
         <v>2.86</v>
       </c>
       <c r="K59" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L59" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M59" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N59" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O59" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P59" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R59" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S59" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T59" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U59" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V59" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W59" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X59" t="n">
         <v>10.5</v>
@@ -11881,22 +11881,22 @@
         <v>1000</v>
       </c>
       <c r="AB59" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC59" t="n">
         <v>8.6</v>
       </c>
       <c r="AD59" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE59" t="n">
         <v>1000</v>
       </c>
       <c r="AF59" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG59" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH59" t="n">
         <v>1000</v>
@@ -11923,62 +11923,62 @@
         <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AQ59" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.65</v>
+        <v>11</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT59" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AU59" t="n">
         <v>6</v>
       </c>
       <c r="AV59" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW59" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX59" t="n">
-        <v>3.9</v>
+        <v>16.5</v>
       </c>
       <c r="AY59" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AZ59" t="n">
-        <v>3.9</v>
+        <v>16.5</v>
       </c>
       <c r="BA59" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB59" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC59" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG59" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -12009,67 +12009,67 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G60" t="n">
-        <v>110</v>
+        <v>2.36</v>
       </c>
       <c r="H60" t="n">
-        <v>1.09</v>
+        <v>2.88</v>
       </c>
       <c r="I60" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K60" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L60" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M60" t="n">
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="O60" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="P60" t="n">
-        <v>1.58</v>
+        <v>3.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="R60" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="S60" t="n">
-        <v>1.05</v>
+        <v>1.71</v>
       </c>
       <c r="T60" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="U60" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="V60" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="W60" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
       </c>
       <c r="Y60" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z60" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA60" t="n">
         <v>1000</v>
@@ -12078,22 +12078,22 @@
         <v>1000</v>
       </c>
       <c r="AC60" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD60" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE60" t="n">
         <v>1000</v>
       </c>
       <c r="AF60" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG60" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH60" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI60" t="n">
         <v>1000</v>
@@ -12102,77 +12102,77 @@
         <v>1000</v>
       </c>
       <c r="AK60" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL60" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AM60" t="n">
         <v>1000</v>
       </c>
       <c r="AN60" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO60" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV60" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA60" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD60" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -12203,25 +12203,25 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G61" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H61" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I61" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K61" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L61" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M61" t="n">
         <v>1.06</v>
@@ -12236,13 +12236,13 @@
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R61" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S61" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T61" t="n">
         <v>1.71</v>
@@ -12251,19 +12251,19 @@
         <v>2.18</v>
       </c>
       <c r="V61" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W61" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="X61" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y61" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z61" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA61" t="n">
         <v>1000</v>
@@ -12275,10 +12275,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD61" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE61" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF61" t="n">
         <v>16</v>
@@ -12287,7 +12287,7 @@
         <v>12.5</v>
       </c>
       <c r="AH61" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI61" t="n">
         <v>60</v>
@@ -12308,7 +12308,7 @@
         <v>16.5</v>
       </c>
       <c r="AO61" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP61" t="n">
         <v>12.5</v>
@@ -12320,7 +12320,7 @@
         <v>21</v>
       </c>
       <c r="AS61" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT61" t="n">
         <v>8</v>
@@ -12332,7 +12332,7 @@
         <v>12</v>
       </c>
       <c r="AW61" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX61" t="n">
         <v>10.5</v>
@@ -12344,7 +12344,7 @@
         <v>13</v>
       </c>
       <c r="BA61" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB61" t="n">
         <v>19</v>
@@ -12353,20 +12353,20 @@
         <v>16</v>
       </c>
       <c r="BD61" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE61" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF61" t="n">
         <v>11.5</v>
       </c>
       <c r="BG61" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -12400,16 +12400,16 @@
         <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H62" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I62" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K62" t="n">
         <v>3.05</v>
@@ -12427,16 +12427,16 @@
         <v>1.69</v>
       </c>
       <c r="P62" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q62" t="n">
         <v>3.05</v>
       </c>
       <c r="R62" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S62" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="T62" t="n">
         <v>2.34</v>
@@ -12448,7 +12448,7 @@
         <v>1.5</v>
       </c>
       <c r="W62" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X62" t="n">
         <v>7.4</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
         <v>4.1</v>
       </c>
       <c r="L63" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M63" t="n">
         <v>1.09</v>
@@ -12663,7 +12663,7 @@
         <v>1000</v>
       </c>
       <c r="AD63" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE63" t="n">
         <v>1000</v>
@@ -12702,13 +12702,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ63" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AT63" t="n">
         <v>5.3</v>
@@ -12720,41 +12720,41 @@
         <v>2.4</v>
       </c>
       <c r="AW63" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AX63" t="n">
         <v>4</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>3.9</v>
       </c>
       <c r="AY63" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ63" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="BA63" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BB63" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC63" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD63" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BF63" t="n">
         <v>10</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -760,7 +760,7 @@
         <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
@@ -772,10 +772,10 @@
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -808,7 +808,7 @@
         <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
@@ -871,10 +871,10 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -886,31 +886,31 @@
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD2" t="n">
         <v>7.6</v>
       </c>
-      <c r="AX2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>1.89</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
         <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -969,7 +969,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -984,7 +984,7 @@
         <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.29</v>
@@ -999,10 +999,10 @@
         <v>1.93</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X3" t="n">
         <v>15</v>
@@ -1020,31 +1020,31 @@
         <v>9.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>85</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1053,7 +1053,7 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
         <v>110</v>
@@ -1065,10 +1065,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1080,7 +1080,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
@@ -1092,7 +1092,7 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>16.5</v>
@@ -1101,20 +1101,20 @@
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
         <v>4.3</v>
@@ -1160,7 +1160,7 @@
         <v>2.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.48</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.24</v>
+        <v>2.68</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="AS4" t="n">
         <v>1.76</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.08</v>
+        <v>5.4</v>
       </c>
       <c r="AU4" t="n">
         <v>3.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.87</v>
+        <v>2.98</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="AX4" t="n">
         <v>2.86</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.68</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="BE4" t="n">
         <v>1.77</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="BG4" t="n">
         <v>1.76</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
@@ -1351,10 +1351,10 @@
         <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.45</v>
@@ -1390,7 +1390,7 @@
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1414,7 +1414,7 @@
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF5" t="n">
         <v>9.4</v>
@@ -1438,7 +1438,7 @@
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
         <v>17.5</v>
@@ -1447,25 +1447,25 @@
         <v>250</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
         <v>8.6</v>
@@ -1483,13 +1483,13 @@
         <v>8.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
         <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
         <v>8.800000000000001</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I6" t="n">
         <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
         <v>3.05</v>
@@ -1560,7 +1560,7 @@
         <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
@@ -1575,7 +1575,7 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
         <v>1.74</v>
@@ -1656,7 +1656,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
@@ -1671,7 +1671,7 @@
         <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
         <v>7.8</v>
@@ -1680,7 +1680,7 @@
         <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BD6" t="n">
         <v>8</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>990</v>
+        <v>2.78</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>2.36</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.06</v>
+        <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
         <v>1.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,22 +1793,22 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1817,10 +1817,10 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1829,68 +1829,68 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
         <v>1.1</v>
@@ -1951,13 +1951,13 @@
         <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Q8" t="n">
         <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
         <v>1.05</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2145,10 +2145,10 @@
         <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
         <v>1.35</v>
@@ -2157,16 +2157,16 @@
         <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
@@ -2196,7 +2196,7 @@
         <v>15.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>16.5</v>
@@ -2205,7 +2205,7 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
@@ -2214,16 +2214,16 @@
         <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>50</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>12</v>
@@ -2232,53 +2232,53 @@
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BA9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>16</v>
-      </c>
       <c r="BF9" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG9" t="n">
         <v>34</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>3.25</v>
       </c>
       <c r="G11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H11" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I11" t="n">
         <v>2.48</v>
@@ -2521,7 +2521,7 @@
         <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
@@ -2533,7 +2533,7 @@
         <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
         <v>2.04</v>
@@ -2542,7 +2542,7 @@
         <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
         <v>1.79</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G12" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
         <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
@@ -2721,16 +2721,16 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
         <v>1.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R12" t="n">
         <v>1.31</v>
@@ -2739,7 +2739,7 @@
         <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
         <v>1.98</v>
@@ -2748,13 +2748,13 @@
         <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2766,7 +2766,7 @@
         <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2805,16 +2805,16 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
         <v>7.2</v>
@@ -2826,41 +2826,41 @@
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -2894,28 +2894,28 @@
         <v>1.34</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="H13" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
         <v>12.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="K13" t="n">
         <v>5.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
@@ -2924,13 +2924,13 @@
         <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T13" t="n">
         <v>2.12</v>
@@ -2942,7 +2942,7 @@
         <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X13" t="n">
         <v>24</v>
@@ -2969,7 +2969,7 @@
         <v>240</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG13" t="n">
         <v>11.5</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV13" t="n">
         <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
         <v>4.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
@@ -3109,34 +3109,34 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
         <v>1.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
         <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
         <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X14" t="n">
         <v>18</v>
@@ -3145,7 +3145,7 @@
         <v>24</v>
       </c>
       <c r="Z14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3181,7 +3181,7 @@
         <v>18.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3193,19 +3193,19 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="AR14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS14" t="n">
         <v>7.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
         <v>4.6</v>
@@ -3217,38 +3217,38 @@
         <v>7.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA14" t="n">
         <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
         <v>7.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>8.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I15" t="n">
         <v>1.59</v>
@@ -3294,7 +3294,7 @@
         <v>3.95</v>
       </c>
       <c r="K15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.26</v>
@@ -3315,10 +3315,10 @@
         <v>1.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
         <v>1.76</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -3482,10 +3482,10 @@
         <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="H17" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="I17" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
@@ -3691,13 +3691,13 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>1.83</v>
@@ -3709,28 +3709,28 @@
         <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U17" t="n">
         <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X17" t="n">
         <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB17" t="n">
         <v>14.5</v>
@@ -3739,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>36</v>
@@ -3772,22 +3772,22 @@
         <v>27</v>
       </c>
       <c r="AO17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP17" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR17" t="n">
         <v>14.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU17" t="n">
         <v>6.2</v>
@@ -3796,31 +3796,31 @@
         <v>9.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="n">
         <v>13.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC17" t="n">
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
         <v>15.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -3963,16 +3963,16 @@
         <v>310</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR18" t="n">
         <v>6.6</v>
@@ -3987,10 +3987,10 @@
         <v>20</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -4008,7 +4008,7 @@
         <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD18" t="n">
         <v>40</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
         <v>1.87</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
         <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R20" t="n">
         <v>1.56</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
         <v>7.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="AZ21" t="n">
         <v>18.5</v>
@@ -4590,7 +4590,7 @@
         <v>3.95</v>
       </c>
       <c r="BC21" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD21" t="n">
         <v>4.8</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -4640,16 +4640,16 @@
         <v>4.8</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I22" t="n">
         <v>1.86</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -4694,7 +4694,7 @@
         <v>15.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="n">
         <v>11</v>
@@ -4760,7 +4760,7 @@
         <v>16.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
         <v>9.4</v>
@@ -4790,7 +4790,7 @@
         <v>55</v>
       </c>
       <c r="BE22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF22" t="n">
         <v>55</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G23" t="n">
         <v>2.8</v>
       </c>
       <c r="H23" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I23" t="n">
         <v>3.05</v>
@@ -4864,7 +4864,7 @@
         <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R23" t="n">
         <v>1.27</v>
@@ -4930,13 +4930,13 @@
         <v>50</v>
       </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN23" t="n">
         <v>36</v>
       </c>
       <c r="AO23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         <v>2.36</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
         <v>3.85</v>
@@ -5061,7 +5061,7 @@
         <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
         <v>2.98</v>
@@ -5079,7 +5079,7 @@
         <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y24" t="n">
         <v>12.5</v>
@@ -5103,7 +5103,7 @@
         <v>24</v>
       </c>
       <c r="AF24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG24" t="n">
         <v>14</v>
@@ -5112,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ24" t="n">
         <v>55</v>
@@ -5130,7 +5130,7 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP24" t="n">
         <v>15.5</v>
@@ -5139,10 +5139,10 @@
         <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT24" t="n">
         <v>14</v>
@@ -5166,7 +5166,7 @@
         <v>14</v>
       </c>
       <c r="BA24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
         <v>40</v>
@@ -5178,17 +5178,17 @@
         <v>28</v>
       </c>
       <c r="BE24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG24" t="n">
         <v>14</v>
       </c>
-      <c r="BF24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>1.35</v>
       </c>
       <c r="H25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I25" t="n">
         <v>10.5</v>
@@ -5282,7 +5282,7 @@
         <v>100</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB25" t="n">
         <v>10.5</v>
@@ -5321,7 +5321,7 @@
         <v>140</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO25" t="n">
         <v>150</v>
@@ -5336,13 +5336,13 @@
         <v>12.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT25" t="n">
         <v>9</v>
       </c>
       <c r="AU25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
@@ -5351,13 +5351,13 @@
         <v>10.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA25" t="n">
         <v>12.5</v>
@@ -5372,7 +5372,7 @@
         <v>27</v>
       </c>
       <c r="BE25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF25" t="n">
         <v>4.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -5437,13 +5437,13 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q26" t="n">
         <v>1.43</v>
@@ -5452,13 +5452,13 @@
         <v>1.65</v>
       </c>
       <c r="S26" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="T26" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U26" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -5494,7 +5494,7 @@
         <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
         <v>1000</v>
@@ -5506,7 +5506,7 @@
         <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5521,62 +5521,62 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>4.2</v>
       </c>
       <c r="AR26" t="n">
         <v>4.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="AX26" t="n">
         <v>3.9</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC26" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC26" t="n">
-        <v>4</v>
-      </c>
       <c r="BD26" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>8.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K27" t="n">
         <v>4.9</v>
@@ -5640,7 +5640,7 @@
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
         <v>1.43</v>
@@ -5655,7 +5655,7 @@
         <v>1.91</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W27" t="n">
         <v>2.92</v>
@@ -5667,7 +5667,7 @@
         <v>29</v>
       </c>
       <c r="Z27" t="n">
-        <v>880</v>
+        <v>990</v>
       </c>
       <c r="AA27" t="n">
         <v>320</v>
@@ -5700,7 +5700,7 @@
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>46</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>3.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I28" t="n">
         <v>2.24</v>
@@ -5855,7 +5855,7 @@
         <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y28" t="n">
         <v>10</v>
@@ -5867,13 +5867,13 @@
         <v>30</v>
       </c>
       <c r="AB28" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC28" t="n">
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>24</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
         <v>2</v>
@@ -6034,13 +6034,13 @@
         <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T29" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V29" t="n">
         <v>1.47</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -6201,13 +6201,13 @@
         <v>2.48</v>
       </c>
       <c r="J30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K30" t="n">
         <v>3.85</v>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
@@ -6255,7 +6255,7 @@
         <v>55</v>
       </c>
       <c r="AB30" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC30" t="n">
         <v>8.800000000000001</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -6410,22 +6410,22 @@
         <v>3.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
         <v>1.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T31" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U31" t="n">
         <v>1.94</v>
@@ -6464,7 +6464,7 @@
         <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH31" t="n">
         <v>26</v>
@@ -6500,53 +6500,53 @@
         <v>34</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV31" t="n">
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY31" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD31" t="n">
         <v>26</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF31" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -6583,16 +6583,16 @@
         <v>1.79</v>
       </c>
       <c r="H32" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J32" t="n">
         <v>3.75</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L32" t="n">
         <v>1.38</v>
@@ -6601,7 +6601,7 @@
         <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
         <v>1.31</v>
@@ -6610,22 +6610,22 @@
         <v>1.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R32" t="n">
         <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>1.05</v>
+        <v>2.98</v>
       </c>
       <c r="T32" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U32" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W32" t="n">
         <v>2.26</v>
@@ -6643,7 +6643,7 @@
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC32" t="n">
         <v>1000</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT32" t="n">
         <v>3.1</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AV32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC32" t="n">
         <v>3.75</v>
       </c>
-      <c r="AW32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BD32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="G33" t="n">
         <v>1.99</v>
       </c>
       <c r="H33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
         <v>3.55</v>
@@ -6798,7 +6798,7 @@
         <v>3.4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P33" t="n">
         <v>1.82</v>
@@ -6807,7 +6807,7 @@
         <v>2.08</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
         <v>3.85</v>
@@ -6816,10 +6816,10 @@
         <v>1.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
         <v>2</v>
@@ -6852,7 +6852,7 @@
         <v>11.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH33" t="n">
         <v>21</v>
@@ -6885,10 +6885,10 @@
         <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT33" t="n">
         <v>7.2</v>
@@ -6900,7 +6900,7 @@
         <v>15.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX33" t="n">
         <v>9.4</v>
@@ -6912,7 +6912,7 @@
         <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB33" t="n">
         <v>18.5</v>
@@ -6921,20 +6921,20 @@
         <v>18</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF33" t="n">
         <v>12</v>
       </c>
       <c r="BG33" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>3.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
         <v>4.4</v>
@@ -7064,7 +7064,7 @@
         <v>32</v>
       </c>
       <c r="AM34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
         <v>10.5</v>
@@ -7094,7 +7094,7 @@
         <v>11.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX34" t="n">
         <v>11.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="G35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H35" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I35" t="n">
         <v>2.8</v>
       </c>
       <c r="J35" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K35" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L35" t="n">
         <v>1.5</v>
@@ -7183,25 +7183,25 @@
         <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O35" t="n">
         <v>1.44</v>
       </c>
       <c r="P35" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="R35" t="n">
         <v>1.24</v>
       </c>
       <c r="S35" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T35" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U35" t="n">
         <v>1.94</v>
@@ -7213,22 +7213,22 @@
         <v>1.47</v>
       </c>
       <c r="X35" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y35" t="n">
         <v>9.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA35" t="n">
         <v>48</v>
       </c>
       <c r="AB35" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD35" t="n">
         <v>13</v>
@@ -7255,7 +7255,7 @@
         <v>42</v>
       </c>
       <c r="AL35" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM35" t="n">
         <v>140</v>
@@ -7264,19 +7264,19 @@
         <v>46</v>
       </c>
       <c r="AO35" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP35" t="n">
         <v>9</v>
       </c>
       <c r="AQ35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR35" t="n">
         <v>15.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AT35" t="n">
         <v>9</v>
@@ -7288,41 +7288,41 @@
         <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX35" t="n">
         <v>16.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>17</v>
       </c>
       <c r="BA35" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BC35" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -7386,19 +7386,19 @@
         <v>2.88</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
         <v>1.77</v>
       </c>
       <c r="S36" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T36" t="n">
         <v>2.04</v>
       </c>
       <c r="U36" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="V36" t="n">
         <v>1.07</v>
@@ -7407,7 +7407,7 @@
         <v>4.8</v>
       </c>
       <c r="X36" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Y36" t="n">
         <v>60</v>
@@ -7416,7 +7416,7 @@
         <v>160</v>
       </c>
       <c r="AA36" t="n">
-        <v>740</v>
+        <v>710</v>
       </c>
       <c r="AB36" t="n">
         <v>11.5</v>
@@ -7428,10 +7428,10 @@
         <v>55</v>
       </c>
       <c r="AE36" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF36" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG36" t="n">
         <v>12.5</v>
@@ -7440,7 +7440,7 @@
         <v>34</v>
       </c>
       <c r="AI36" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AJ36" t="n">
         <v>10.5</v>
@@ -7455,22 +7455,22 @@
         <v>170</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AO36" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP36" t="n">
         <v>27</v>
       </c>
       <c r="AQ36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT36" t="n">
         <v>10</v>
@@ -7479,7 +7479,7 @@
         <v>14.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AW36" t="n">
         <v>13</v>
@@ -7494,7 +7494,7 @@
         <v>28</v>
       </c>
       <c r="BA36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB36" t="n">
         <v>9</v>
@@ -7503,7 +7503,7 @@
         <v>12</v>
       </c>
       <c r="BD36" t="n">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="BE36" t="n">
         <v>13</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -7547,19 +7547,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H37" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J37" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K37" t="n">
         <v>3.7</v>
@@ -7586,7 +7586,7 @@
         <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T37" t="n">
         <v>1.69</v>
@@ -7598,7 +7598,7 @@
         <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X37" t="n">
         <v>15.5</v>
@@ -7607,7 +7607,7 @@
         <v>970</v>
       </c>
       <c r="Z37" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA37" t="n">
         <v>110</v>
@@ -7625,7 +7625,7 @@
         <v>65</v>
       </c>
       <c r="AF37" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
         <v>970</v>
@@ -7643,7 +7643,7 @@
         <v>24</v>
       </c>
       <c r="AL37" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM37" t="n">
         <v>130</v>
@@ -7655,62 +7655,62 @@
         <v>65</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ37" t="n">
         <v>11.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AU37" t="n">
         <v>7</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY37" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD37" t="n">
         <v>27</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
@@ -7831,7 +7831,7 @@
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
         <v>22</v>
@@ -7852,16 +7852,16 @@
         <v>21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT38" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU38" t="n">
         <v>8.199999999999999</v>
@@ -7870,7 +7870,7 @@
         <v>12</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX38" t="n">
         <v>11.5</v>
@@ -7882,29 +7882,29 @@
         <v>11</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB38" t="n">
-        <v>16.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC38" t="n">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="BD38" t="n">
         <v>18</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
         <v>5.6</v>
       </c>
       <c r="H39" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="I39" t="n">
         <v>2.08</v>
@@ -7950,7 +7950,7 @@
         <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L39" t="n">
         <v>1.5</v>
@@ -8043,7 +8043,7 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ39" t="n">
         <v>5.6</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -8135,10 +8135,10 @@
         <v>5.9</v>
       </c>
       <c r="H40" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I40" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -8177,7 +8177,7 @@
         <v>2.02</v>
       </c>
       <c r="V40" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="W40" t="n">
         <v>1.2</v>
@@ -8261,7 +8261,7 @@
         <v>15.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="AY40" t="n">
         <v>19</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G41" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="H41" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I41" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K41" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L41" t="n">
         <v>1.12</v>
@@ -8407,16 +8407,16 @@
         <v>15.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL41" t="n">
         <v>21</v>
@@ -8446,10 +8446,10 @@
         <v>19</v>
       </c>
       <c r="AU41" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW41" t="n">
         <v>26</v>
@@ -8458,7 +8458,7 @@
         <v>15</v>
       </c>
       <c r="AY41" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ41" t="n">
         <v>12.5</v>
@@ -8467,7 +8467,7 @@
         <v>21</v>
       </c>
       <c r="BB41" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BC41" t="n">
         <v>11</v>
@@ -8476,17 +8476,17 @@
         <v>13.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BF41" t="n">
         <v>3.3</v>
       </c>
       <c r="BG41" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G42" t="n">
         <v>4.3</v>
       </c>
       <c r="H42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I42" t="n">
         <v>2.14</v>
       </c>
       <c r="J42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K42" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K42" t="n">
-        <v>3.45</v>
       </c>
       <c r="L42" t="n">
         <v>1.45</v>
@@ -8541,16 +8541,16 @@
         <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O42" t="n">
         <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R42" t="n">
         <v>1.29</v>
@@ -8559,10 +8559,10 @@
         <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U42" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V42" t="n">
         <v>1.87</v>
@@ -8574,13 +8574,13 @@
         <v>11.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA42" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB42" t="n">
         <v>14</v>
@@ -8592,13 +8592,13 @@
         <v>11</v>
       </c>
       <c r="AE42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF42" t="n">
         <v>30</v>
       </c>
       <c r="AG42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH42" t="n">
         <v>19.5</v>
@@ -8613,7 +8613,7 @@
         <v>60</v>
       </c>
       <c r="AL42" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM42" t="n">
         <v>130</v>
@@ -8646,41 +8646,41 @@
         <v>10</v>
       </c>
       <c r="AW42" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="AX42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY42" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BD42" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BE42" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BG42" t="n">
         <v>17.5</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
         <v>3.45</v>
       </c>
       <c r="L43" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
@@ -8753,7 +8753,7 @@
         <v>4.2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U43" t="n">
         <v>2</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>2.14</v>
       </c>
       <c r="G44" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H44" t="n">
         <v>4.1</v>
@@ -8956,7 +8956,7 @@
         <v>1.3</v>
       </c>
       <c r="W44" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X44" t="n">
         <v>10.5</v>
@@ -8998,7 +8998,7 @@
         <v>26</v>
       </c>
       <c r="AK44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL44" t="n">
         <v>48</v>
@@ -9031,10 +9031,10 @@
         <v>7</v>
       </c>
       <c r="AV44" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW44" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX44" t="n">
         <v>11</v>
@@ -9061,14 +9061,14 @@
         <v>44</v>
       </c>
       <c r="BF44" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG44" t="n">
         <v>70</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H45" t="n">
         <v>3.95</v>
@@ -9123,7 +9123,7 @@
         <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O45" t="n">
         <v>1.2</v>
@@ -9132,7 +9132,7 @@
         <v>2.54</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R45" t="n">
         <v>1.62</v>
@@ -9150,13 +9150,13 @@
         <v>1.33</v>
       </c>
       <c r="W45" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X45" t="n">
         <v>23</v>
       </c>
       <c r="Y45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z45" t="n">
         <v>32</v>
@@ -9165,7 +9165,7 @@
         <v>70</v>
       </c>
       <c r="AB45" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC45" t="n">
         <v>9.199999999999999</v>
@@ -9189,7 +9189,7 @@
         <v>40</v>
       </c>
       <c r="AJ45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK45" t="n">
         <v>17.5</v>
@@ -9201,7 +9201,7 @@
         <v>60</v>
       </c>
       <c r="AN45" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO45" t="n">
         <v>32</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G46" t="n">
         <v>2.14</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2.16</v>
       </c>
       <c r="H46" t="n">
         <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K46" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L46" t="n">
         <v>1.45</v>
@@ -9323,10 +9323,10 @@
         <v>1.38</v>
       </c>
       <c r="P46" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R46" t="n">
         <v>1.32</v>
@@ -9338,13 +9338,13 @@
         <v>1.9</v>
       </c>
       <c r="U46" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V46" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W46" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X46" t="n">
         <v>12</v>
@@ -9353,13 +9353,13 @@
         <v>13.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA46" t="n">
         <v>85</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC46" t="n">
         <v>7.4</v>
@@ -9416,7 +9416,7 @@
         <v>8.4</v>
       </c>
       <c r="AU46" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV46" t="n">
         <v>14.5</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I47" t="n">
         <v>1000</v>
@@ -9511,7 +9511,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G48" t="n">
         <v>1.82</v>
@@ -9690,10 +9690,10 @@
         <v>4.3</v>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J48" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K48" t="n">
         <v>5</v>
@@ -9705,10 +9705,10 @@
         <v>1.02</v>
       </c>
       <c r="N48" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="O48" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P48" t="n">
         <v>3.55</v>
@@ -9750,7 +9750,7 @@
         <v>25</v>
       </c>
       <c r="AC48" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD48" t="n">
         <v>25</v>
@@ -9789,10 +9789,10 @@
         <v>26</v>
       </c>
       <c r="AP48" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ48" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR48" t="n">
         <v>4.6</v>
@@ -9801,7 +9801,7 @@
         <v>4.6</v>
       </c>
       <c r="AT48" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AU48" t="n">
         <v>3.9</v>
@@ -9810,22 +9810,22 @@
         <v>4.1</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX48" t="n">
         <v>4.1</v>
       </c>
       <c r="AY48" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AZ48" t="n">
         <v>3.95</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC48" t="n">
         <v>4</v>
@@ -9834,7 +9834,7 @@
         <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF48" t="n">
         <v>4.7</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
         <v>1.49</v>
       </c>
       <c r="G49" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H49" t="n">
         <v>5.5</v>
@@ -9905,13 +9905,13 @@
         <v>1.09</v>
       </c>
       <c r="P49" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q49" t="n">
         <v>1.33</v>
       </c>
       <c r="R49" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S49" t="n">
         <v>1.83</v>
@@ -9980,19 +9980,19 @@
         <v>4.4</v>
       </c>
       <c r="AO49" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>7</v>
       </c>
       <c r="AR49" t="n">
         <v>7.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT49" t="n">
         <v>17</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>1.36</v>
       </c>
       <c r="G50" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H50" t="n">
         <v>5.4</v>
@@ -10093,7 +10093,7 @@
         <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="O50" t="n">
         <v>1.11</v>
@@ -10120,7 +10120,7 @@
         <v>1.1</v>
       </c>
       <c r="W50" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
         <v>4.1</v>
       </c>
       <c r="L51" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="M51" t="n">
         <v>1.08</v>
@@ -10308,7 +10308,7 @@
         <v>2.1</v>
       </c>
       <c r="U51" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V51" t="n">
         <v>1.17</v>
@@ -10350,7 +10350,7 @@
         <v>25</v>
       </c>
       <c r="AI51" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ51" t="n">
         <v>18</v>
@@ -10368,7 +10368,7 @@
         <v>12.5</v>
       </c>
       <c r="AO51" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AP51" t="n">
         <v>11.5</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
         <v>4.7</v>
       </c>
       <c r="G52" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H52" t="n">
         <v>1.87</v>
@@ -10490,7 +10490,7 @@
         <v>1.73</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R52" t="n">
         <v>1.26</v>
@@ -10514,7 +10514,7 @@
         <v>14</v>
       </c>
       <c r="Y52" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z52" t="n">
         <v>13.5</v>
@@ -10601,26 +10601,26 @@
         <v>36</v>
       </c>
       <c r="BB52" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC52" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC52" t="n">
-        <v>5</v>
-      </c>
       <c r="BD52" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG52" t="n">
         <v>12</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G53" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H53" t="n">
         <v>3.75</v>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>3.15</v>
@@ -10675,13 +10675,13 @@
         <v>1.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O53" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P53" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q53" t="n">
         <v>2.7</v>
@@ -10693,22 +10693,22 @@
         <v>5.3</v>
       </c>
       <c r="T53" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V53" t="n">
         <v>1.33</v>
       </c>
       <c r="W53" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X53" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y53" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z53" t="n">
         <v>27</v>
@@ -10717,16 +10717,16 @@
         <v>110</v>
       </c>
       <c r="AB53" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC53" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD53" t="n">
         <v>18</v>
       </c>
       <c r="AE53" t="n">
-        <v>730</v>
+        <v>900</v>
       </c>
       <c r="AF53" t="n">
         <v>14</v>
@@ -10735,13 +10735,13 @@
         <v>12.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AI53" t="n">
         <v>90</v>
       </c>
       <c r="AJ53" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AK53" t="n">
         <v>55</v>
@@ -10756,28 +10756,28 @@
         <v>55</v>
       </c>
       <c r="AO53" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP53" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ53" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR53" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AS53" t="n">
         <v>34</v>
       </c>
       <c r="AT53" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU53" t="n">
         <v>6.6</v>
       </c>
       <c r="AV53" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW53" t="n">
         <v>30</v>
@@ -10786,10 +10786,10 @@
         <v>11</v>
       </c>
       <c r="AY53" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA53" t="n">
         <v>38</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
         <v>1.95</v>
       </c>
       <c r="V54" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W54" t="n">
         <v>1.37</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -11042,10 +11042,10 @@
         <v>2.7</v>
       </c>
       <c r="G55" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H55" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I55" t="n">
         <v>3.1</v>
@@ -11054,7 +11054,7 @@
         <v>3.1</v>
       </c>
       <c r="K55" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L55" t="n">
         <v>1.52</v>
@@ -11069,7 +11069,7 @@
         <v>1.45</v>
       </c>
       <c r="P55" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q55" t="n">
         <v>2.34</v>
@@ -11078,7 +11078,7 @@
         <v>1.24</v>
       </c>
       <c r="S55" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T55" t="n">
         <v>1.94</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
         <v>3.15</v>
       </c>
       <c r="G56" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H56" t="n">
         <v>2.44</v>
@@ -11284,7 +11284,7 @@
         <v>1.58</v>
       </c>
       <c r="W56" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X56" t="n">
         <v>10.5</v>
@@ -11350,7 +11350,7 @@
         <v>11</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT56" t="n">
         <v>8.199999999999999</v>
@@ -11374,7 +11374,7 @@
         <v>16.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB56" t="n">
         <v>5</v>
@@ -11383,20 +11383,20 @@
         <v>4.9</v>
       </c>
       <c r="BD56" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE56" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF56" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG56" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -11430,10 +11430,10 @@
         <v>1.92</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H57" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I57" t="n">
         <v>5.4</v>
@@ -11442,19 +11442,19 @@
         <v>3.25</v>
       </c>
       <c r="K57" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L57" t="n">
         <v>1.43</v>
       </c>
       <c r="M57" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N57" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O57" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P57" t="n">
         <v>1.62</v>
@@ -11463,13 +11463,13 @@
         <v>2.38</v>
       </c>
       <c r="R57" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S57" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T57" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U57" t="n">
         <v>1.79</v>
@@ -11478,7 +11478,7 @@
         <v>1.23</v>
       </c>
       <c r="W57" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X57" t="n">
         <v>12</v>
@@ -11493,10 +11493,10 @@
         <v>1000</v>
       </c>
       <c r="AB57" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC57" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD57" t="n">
         <v>1000</v>
@@ -11535,16 +11535,16 @@
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS57" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>4.3</v>
       </c>
       <c r="AT57" t="n">
         <v>3.1</v>
@@ -11553,44 +11553,44 @@
         <v>3.25</v>
       </c>
       <c r="AV57" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX57" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AY57" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AZ57" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB57" t="n">
         <v>3.9</v>
       </c>
-      <c r="BA57" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB57" t="n">
+      <c r="BC57" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF57" t="n">
         <v>3.85</v>
       </c>
-      <c r="BC57" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BG57" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G58" t="n">
         <v>2.12</v>
@@ -11663,10 +11663,10 @@
         <v>5.5</v>
       </c>
       <c r="T58" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U58" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V58" t="n">
         <v>1.2</v>
@@ -11735,10 +11735,10 @@
         <v>9.4</v>
       </c>
       <c r="AR58" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS58" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT58" t="n">
         <v>4.6</v>
@@ -11747,10 +11747,10 @@
         <v>6.4</v>
       </c>
       <c r="AV58" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW58" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX58" t="n">
         <v>7.6</v>
@@ -11759,32 +11759,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ58" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA58" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD58" t="n">
         <v>6</v>
       </c>
-      <c r="BB58" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE58" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF58" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG58" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
         <v>2.44</v>
       </c>
       <c r="I59" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>2.86</v>
@@ -11836,7 +11836,7 @@
         <v>1.49</v>
       </c>
       <c r="M59" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N59" t="n">
         <v>2.48</v>
@@ -11854,7 +11854,7 @@
         <v>1.17</v>
       </c>
       <c r="S59" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="T59" t="n">
         <v>2.06</v>
@@ -11863,7 +11863,7 @@
         <v>1.74</v>
       </c>
       <c r="V59" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W59" t="n">
         <v>1.37</v>
@@ -11944,7 +11944,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW59" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX59" t="n">
         <v>16.5</v>
@@ -11953,10 +11953,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ59" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA59" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB59" t="n">
         <v>4.7</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="O60" t="n">
         <v>1.09</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -12245,10 +12245,10 @@
         <v>3.1</v>
       </c>
       <c r="T61" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U61" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V61" t="n">
         <v>1.33</v>
@@ -12311,34 +12311,34 @@
         <v>46</v>
       </c>
       <c r="AP61" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR61" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS61" t="n">
         <v>5.3</v>
       </c>
       <c r="AT61" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU61" t="n">
         <v>6.6</v>
       </c>
       <c r="AV61" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW61" t="n">
         <v>5.2</v>
       </c>
       <c r="AX61" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY61" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ61" t="n">
         <v>13</v>
@@ -12347,13 +12347,13 @@
         <v>5.3</v>
       </c>
       <c r="BB61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD61" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE61" t="n">
         <v>5.3</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -12400,13 +12400,13 @@
         <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H62" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J62" t="n">
         <v>2.84</v>
@@ -12427,7 +12427,7 @@
         <v>1.69</v>
       </c>
       <c r="P62" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q62" t="n">
         <v>3.05</v>
@@ -12439,7 +12439,7 @@
         <v>7.2</v>
       </c>
       <c r="T62" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U62" t="n">
         <v>1.63</v>
@@ -12463,7 +12463,7 @@
         <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC62" t="n">
         <v>7.4</v>
@@ -12511,10 +12511,10 @@
         <v>6.4</v>
       </c>
       <c r="AR62" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="AS62" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT62" t="n">
         <v>6.8</v>
@@ -12523,16 +12523,16 @@
         <v>6</v>
       </c>
       <c r="AV62" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW62" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AX62" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="AY62" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AZ62" t="n">
         <v>6.8</v>
@@ -12544,7 +12544,7 @@
         <v>7.8</v>
       </c>
       <c r="BC62" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD62" t="n">
         <v>8.199999999999999</v>
@@ -12556,11 +12556,11 @@
         <v>8</v>
       </c>
       <c r="BG62" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
         <v>3.75</v>
       </c>
       <c r="K63" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L63" t="n">
         <v>1.45</v>
@@ -12657,25 +12657,25 @@
         <v>1000</v>
       </c>
       <c r="AB63" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC63" t="n">
         <v>1000</v>
       </c>
       <c r="AD63" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH63" t="n">
         <v>38</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>1000</v>
       </c>
       <c r="AI63" t="n">
         <v>1000</v>
@@ -12702,13 +12702,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ63" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.94</v>
+        <v>3.75</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="AT63" t="n">
         <v>5.3</v>
@@ -12717,44 +12717,44 @@
         <v>7.8</v>
       </c>
       <c r="AV63" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="AW63" t="n">
-        <v>2.54</v>
+        <v>3.85</v>
       </c>
       <c r="AX63" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="AY63" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ63" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="BA63" t="n">
-        <v>2.54</v>
+        <v>3.85</v>
       </c>
       <c r="BB63" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BC63" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD63" t="n">
-        <v>2.48</v>
+        <v>8.4</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.98</v>
+        <v>3.9</v>
       </c>
       <c r="BF63" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-27.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>4.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
@@ -823,10 +823,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -871,7 +871,7 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>8.199999999999999</v>
@@ -880,47 +880,47 @@
         <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
         <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
         <v>1.93</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
         <v>42</v>
@@ -1020,10 +1020,10 @@
         <v>9.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>85</v>
@@ -1035,28 +1035,28 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP3" t="n">
         <v>9.199999999999999</v>
@@ -1065,10 +1065,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1080,7 +1080,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
@@ -1089,32 +1089,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="M4" t="n">
         <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
         <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1211,13 +1211,13 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC4" t="n">
         <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.68</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="AX4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>2.86</v>
       </c>
-      <c r="AY4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BA4" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.77</v>
+        <v>2.46</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1351,37 +1351,37 @@
         <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
         <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
         <v>1.71</v>
@@ -1393,7 +1393,7 @@
         <v>2.42</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
         <v>17.5</v>
@@ -1417,10 +1417,10 @@
         <v>150</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
@@ -1429,10 +1429,10 @@
         <v>140</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1441,37 +1441,37 @@
         <v>240</v>
       </c>
       <c r="AN5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>250</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
         <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
         <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>9</v>
@@ -1480,10 +1480,10 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
         <v>19</v>
@@ -1492,17 +1492,17 @@
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1539,40 +1539,40 @@
         <v>3.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="M6" t="n">
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T6" t="n">
         <v>2.18</v>
@@ -1581,7 +1581,7 @@
         <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W6" t="n">
         <v>1.36</v>
@@ -1590,7 +1590,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z6" t="n">
         <v>15.5</v>
@@ -1647,7 +1647,7 @@
         <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
         <v>30</v>
@@ -1671,32 +1671,32 @@
         <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
         <v>8.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
         <v>34</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.1</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.7</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="X7" t="n">
         <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,34 +1793,34 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1829,68 +1829,68 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AR7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW7" t="n">
         <v>6</v>
       </c>
-      <c r="AS7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE7" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>1.74</v>
       </c>
       <c r="G8" t="n">
-        <v>990</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X8" t="n">
         <v>950</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2115,46 +2115,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="n">
         <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
         <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
         <v>1.76</v>
@@ -2166,10 +2166,10 @@
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
         <v>13.5</v>
@@ -2184,7 +2184,7 @@
         <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
         <v>14.5</v>
@@ -2196,10 +2196,10 @@
         <v>15.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
@@ -2214,10 +2214,10 @@
         <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>50</v>
@@ -2226,19 +2226,19 @@
         <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR9" t="n">
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AT9" t="n">
         <v>9.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
@@ -2262,23 +2262,23 @@
         <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG9" t="n">
         <v>34</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
         <v>3.4</v>
@@ -2318,7 +2318,7 @@
         <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
@@ -2327,43 +2327,43 @@
         <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T10" t="n">
         <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
         <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Y10" t="n">
         <v>8.6</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ10" t="n">
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF10" t="n">
         <v>7</v>
       </c>
-      <c r="BF10" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
         <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
         <v>15</v>
@@ -2563,13 +2563,13 @@
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AA11" t="n">
         <v>36</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
@@ -2581,10 +2581,10 @@
         <v>29</v>
       </c>
       <c r="AF11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -2605,68 +2605,68 @@
         <v>130</v>
       </c>
       <c r="AN11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
         <v>13</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="n">
         <v>10</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
         <v>20</v>
       </c>
       <c r="AX11" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB11" t="n">
         <v>42</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD11" t="n">
         <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -2706,46 +2706,46 @@
         <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
         <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U12" t="n">
         <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
@@ -2754,7 +2754,7 @@
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2799,22 +2799,22 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT12" t="n">
         <v>7.2</v>
@@ -2823,44 +2823,44 @@
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC12" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>4.6</v>
       </c>
-      <c r="BE12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G13" t="n">
         <v>1.4</v>
@@ -2903,37 +2903,37 @@
         <v>12.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K13" t="n">
         <v>5.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
         <v>1.72</v>
@@ -2981,10 +2981,10 @@
         <v>190</v>
       </c>
       <c r="AJ13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="n">
         <v>50</v>
@@ -2993,68 +2993,68 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>19</v>
+        <v>3.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="AT13" t="n">
         <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
         <v>6.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="BF13" t="n">
         <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -3088,37 +3088,37 @@
         <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H14" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
         <v>4.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
         <v>1.34</v>
@@ -3130,16 +3130,16 @@
         <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
         <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y14" t="n">
         <v>24</v>
@@ -3154,7 +3154,7 @@
         <v>7.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
         <v>32</v>
@@ -3187,7 +3187,7 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3199,22 +3199,22 @@
         <v>19</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>7.2</v>
@@ -3223,10 +3223,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>11.5</v>
@@ -3238,17 +3238,17 @@
         <v>34</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
         <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I15" t="n">
         <v>1.59</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -3351,13 +3351,13 @@
         <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE15" t="n">
         <v>970</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG15" t="n">
         <v>950</v>
@@ -3366,16 +3366,16 @@
         <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -3387,19 +3387,19 @@
         <v>970</v>
       </c>
       <c r="AP15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
         <v>8.6</v>
@@ -3408,41 +3408,41 @@
         <v>8</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.9</v>
+        <v>2.88</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.2</v>
+        <v>2.48</v>
       </c>
       <c r="BC15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG15" t="n">
         <v>5</v>
       </c>
-      <c r="BD15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G16" t="n">
         <v>990</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="n">
         <v>990</v>
@@ -3491,40 +3491,40 @@
         <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>1.37</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -3670,22 +3670,22 @@
         <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H17" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="I17" t="n">
         <v>2.86</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3694,34 +3694,34 @@
         <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R17" t="n">
         <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V17" t="n">
         <v>1.53</v>
       </c>
       <c r="W17" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="X17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="n">
         <v>14.5</v>
@@ -3754,7 +3754,7 @@
         <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>48</v>
@@ -3769,7 +3769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO17" t="n">
         <v>29</v>
@@ -3778,59 +3778,59 @@
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12</v>
-      </c>
       <c r="BA17" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC17" t="n">
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF17" t="n">
         <v>15.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H18" t="n">
         <v>26</v>
@@ -3873,46 +3873,46 @@
         <v>34</v>
       </c>
       <c r="J18" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M18" t="n">
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="X18" t="n">
         <v>55</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AD18" t="n">
         <v>950</v>
@@ -3942,7 +3942,7 @@
         <v>10.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
         <v>950</v>
@@ -3951,7 +3951,7 @@
         <v>360</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK18" t="n">
         <v>17.5</v>
@@ -3963,46 +3963,46 @@
         <v>310</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>38</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
         <v>7</v>
@@ -4011,20 +4011,20 @@
         <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G19" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
         <v>5</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
@@ -4267,46 +4267,46 @@
         <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.53</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z20" t="n">
         <v>27</v>
@@ -4315,16 +4315,16 @@
         <v>50</v>
       </c>
       <c r="AB20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
         <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
         <v>24</v>
@@ -4354,7 +4354,7 @@
         <v>17</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
@@ -4366,7 +4366,7 @@
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -4378,22 +4378,22 @@
         <v>9.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="AX20" t="n">
         <v>14.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
         <v>11</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BC20" t="n">
         <v>17</v>
@@ -4402,17 +4402,17 @@
         <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="BG20" t="n">
         <v>12</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -4443,28 +4443,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H21" t="n">
         <v>7.8</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="K21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
         <v>6</v>
@@ -4473,19 +4473,19 @@
         <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T21" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
@@ -4494,7 +4494,7 @@
         <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
@@ -4503,7 +4503,7 @@
         <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
@@ -4548,22 +4548,22 @@
         <v>5</v>
       </c>
       <c r="AO21" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP21" t="n">
         <v>4.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU21" t="n">
         <v>10.5</v>
@@ -4572,41 +4572,41 @@
         <v>4.9</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX21" t="n">
         <v>7.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ21" t="n">
         <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.95</v>
+        <v>9</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BG21" t="n">
         <v>5.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="I22" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="J22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -4670,7 +4670,7 @@
         <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R22" t="n">
         <v>1.4</v>
@@ -4679,25 +4679,25 @@
         <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U22" t="n">
         <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
         <v>15.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA22" t="n">
         <v>19</v>
@@ -4706,10 +4706,10 @@
         <v>17.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE22" t="n">
         <v>18.5</v>
@@ -4718,7 +4718,7 @@
         <v>38</v>
       </c>
       <c r="AG22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH22" t="n">
         <v>19</v>
@@ -4730,19 +4730,19 @@
         <v>120</v>
       </c>
       <c r="AK22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL22" t="n">
         <v>65</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP22" t="n">
         <v>14.5</v>
@@ -4757,31 +4757,31 @@
         <v>17.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
         <v>34</v>
       </c>
       <c r="AY22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>17</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC22" t="n">
         <v>55</v>
@@ -4790,17 +4790,17 @@
         <v>55</v>
       </c>
       <c r="BE22" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF22" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>2.8</v>
       </c>
       <c r="H23" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I23" t="n">
         <v>3.05</v>
@@ -4846,22 +4846,22 @@
         <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.43</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q23" t="n">
         <v>2.32</v>
@@ -4870,10 +4870,10 @@
         <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U23" t="n">
         <v>2</v>
@@ -4888,7 +4888,7 @@
         <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
         <v>19</v>
@@ -4903,19 +4903,19 @@
         <v>7.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>55</v>
@@ -4930,7 +4930,7 @@
         <v>50</v>
       </c>
       <c r="AM23" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN23" t="n">
         <v>36</v>
@@ -4948,13 +4948,13 @@
         <v>16.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4969,22 +4969,22 @@
         <v>11.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BB23" t="n">
         <v>36</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BD23" t="n">
         <v>40</v>
       </c>
       <c r="BE23" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BF23" t="n">
         <v>27</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
         <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.36</v>
@@ -5049,22 +5049,22 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
         <v>1.64</v>
@@ -5082,7 +5082,7 @@
         <v>17</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
         <v>16</v>
@@ -5094,7 +5094,7 @@
         <v>15.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
         <v>11</v>
@@ -5121,22 +5121,22 @@
         <v>34</v>
       </c>
       <c r="AL24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM24" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO24" t="n">
         <v>15.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
         <v>14.5</v>
@@ -5157,7 +5157,7 @@
         <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY24" t="n">
         <v>12.5</v>
@@ -5169,26 +5169,26 @@
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
       </c>
       <c r="BD24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BF24" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BG24" t="n">
         <v>14</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H25" t="n">
         <v>9.4</v>
@@ -5237,55 +5237,55 @@
         <v>6.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R25" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S25" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U25" t="n">
         <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="X25" t="n">
         <v>27</v>
       </c>
       <c r="Y25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z25" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA25" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>14.5</v>
@@ -5297,22 +5297,22 @@
         <v>150</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI25" t="n">
         <v>120</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL25" t="n">
         <v>34</v>
@@ -5321,68 +5321,68 @@
         <v>140</v>
       </c>
       <c r="AN25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ25" t="n">
         <v>30</v>
       </c>
       <c r="AR25" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
         <v>10</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I26" t="n">
         <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
@@ -5443,16 +5443,16 @@
         <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S26" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="T26" t="n">
         <v>1.54</v>
@@ -5524,10 +5524,10 @@
         <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS26" t="n">
         <v>4.8</v>
@@ -5542,16 +5542,16 @@
         <v>4.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AY26" t="n">
         <v>3.85</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BA26" t="n">
         <v>4.6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G27" t="n">
         <v>1.52</v>
       </c>
       <c r="H27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I27" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K27" t="n">
         <v>4.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
@@ -5637,10 +5637,10 @@
         <v>1.28</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R27" t="n">
         <v>1.43</v>
@@ -5652,19 +5652,19 @@
         <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="X27" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z27" t="n">
         <v>990</v>
@@ -5679,16 +5679,16 @@
         <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE27" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF27" t="n">
         <v>8.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH27" t="n">
         <v>25</v>
@@ -5703,16 +5703,16 @@
         <v>16</v>
       </c>
       <c r="AL27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM27" t="n">
         <v>180</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP27" t="n">
         <v>15.5</v>
@@ -5721,13 +5721,13 @@
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS27" t="n">
         <v>48</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU27" t="n">
         <v>9.6</v>
@@ -5742,13 +5742,13 @@
         <v>8</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB27" t="n">
         <v>11.5</v>
@@ -5757,10 +5757,10 @@
         <v>14</v>
       </c>
       <c r="BD27" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BE27" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BF27" t="n">
         <v>6.8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -5801,61 +5801,61 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G28" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H28" t="n">
         <v>2.18</v>
       </c>
       <c r="I28" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.31</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
         <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
         <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U28" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V28" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y28" t="n">
         <v>10</v>
@@ -5870,31 +5870,31 @@
         <v>17.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE28" t="n">
         <v>24</v>
       </c>
       <c r="AF28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG28" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ28" t="n">
         <v>75</v>
       </c>
       <c r="AK28" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AL28" t="n">
         <v>55</v>
@@ -5906,7 +5906,7 @@
         <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP28" t="n">
         <v>13.5</v>
@@ -5918,7 +5918,7 @@
         <v>12</v>
       </c>
       <c r="AS28" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AT28" t="n">
         <v>13</v>
@@ -5930,41 +5930,41 @@
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY28" t="n">
         <v>14</v>
       </c>
       <c r="AZ28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BC28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BD28" t="n">
         <v>44</v>
       </c>
       <c r="BE28" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG28" t="n">
         <v>14.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -5995,58 +5995,58 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G29" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H29" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
         <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O29" t="n">
         <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R29" t="n">
         <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T29" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U29" t="n">
         <v>2.14</v>
       </c>
       <c r="V29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
@@ -6058,7 +6058,7 @@
         <v>21</v>
       </c>
       <c r="AA29" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB29" t="n">
         <v>11</v>
@@ -6070,7 +6070,7 @@
         <v>14</v>
       </c>
       <c r="AE29" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF29" t="n">
         <v>18</v>
@@ -6079,10 +6079,10 @@
         <v>13</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ29" t="n">
         <v>44</v>
@@ -6094,13 +6094,13 @@
         <v>44</v>
       </c>
       <c r="AM29" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP29" t="n">
         <v>11.5</v>
@@ -6136,7 +6136,7 @@
         <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29" t="n">
         <v>32</v>
@@ -6148,7 +6148,7 @@
         <v>34</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF29" t="n">
         <v>21</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G30" t="n">
         <v>3.2</v>
@@ -6201,67 +6201,67 @@
         <v>2.48</v>
       </c>
       <c r="J30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.7</v>
       </c>
-      <c r="K30" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S30" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T30" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U30" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V30" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W30" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y30" t="n">
         <v>14</v>
       </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AA30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
         <v>16.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
@@ -6270,67 +6270,67 @@
         <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK30" t="n">
         <v>32</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
         <v>15.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU30" t="n">
         <v>7.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX30" t="n">
         <v>20</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>19.5</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BB30" t="n">
         <v>38</v>
@@ -6339,20 +6339,20 @@
         <v>25</v>
       </c>
       <c r="BD30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE30" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BF30" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BG30" t="n">
         <v>13</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G31" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H31" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
         <v>6.8</v>
@@ -6398,31 +6398,31 @@
         <v>3.85</v>
       </c>
       <c r="K31" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T31" t="n">
         <v>1.92</v>
@@ -6431,10 +6431,10 @@
         <v>1.94</v>
       </c>
       <c r="V31" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X31" t="n">
         <v>17.5</v>
@@ -6461,10 +6461,10 @@
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH31" t="n">
         <v>26</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AR31" t="n">
         <v>34</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="AV31" t="n">
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>4.6</v>
       </c>
       <c r="BA31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD31" t="n">
         <v>5</v>
       </c>
-      <c r="BB31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>26</v>
-      </c>
       <c r="BE31" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -6577,46 +6577,46 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G32" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H32" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K32" t="n">
         <v>4.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M32" t="n">
         <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O32" t="n">
         <v>1.31</v>
       </c>
       <c r="P32" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="T32" t="n">
         <v>1.87</v>
@@ -6625,10 +6625,10 @@
         <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6646,7 +6646,7 @@
         <v>10</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD32" t="n">
         <v>1000</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AW32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD32" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE32" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
         <v>4.9</v>
@@ -6786,28 +6786,28 @@
         <v>3.55</v>
       </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O33" t="n">
         <v>1.36</v>
       </c>
       <c r="P33" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
         <v>3.85</v>
@@ -6816,13 +6816,13 @@
         <v>1.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
         <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X33" t="n">
         <v>15.5</v>
@@ -6849,7 +6849,7 @@
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG33" t="n">
         <v>9.800000000000001</v>
@@ -6873,7 +6873,7 @@
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
@@ -6885,25 +6885,25 @@
         <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT33" t="n">
         <v>7.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV33" t="n">
         <v>15.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX33" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY33" t="n">
         <v>8.800000000000001</v>
@@ -6912,7 +6912,7 @@
         <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BB33" t="n">
         <v>18.5</v>
@@ -6921,20 +6921,20 @@
         <v>18</v>
       </c>
       <c r="BD33" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF33" t="n">
         <v>12</v>
       </c>
       <c r="BG33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -6968,10 +6968,10 @@
         <v>2.02</v>
       </c>
       <c r="G34" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H34" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I34" t="n">
         <v>3.8</v>
@@ -6980,34 +6980,34 @@
         <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L34" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="M34" t="n">
         <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O34" t="n">
         <v>1.19</v>
       </c>
       <c r="P34" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R34" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S34" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T34" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U34" t="n">
         <v>2.58</v>
@@ -7016,7 +7016,7 @@
         <v>1.35</v>
       </c>
       <c r="W34" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X34" t="n">
         <v>30</v>
@@ -7037,16 +7037,16 @@
         <v>11.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE34" t="n">
         <v>44</v>
       </c>
       <c r="AF34" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH34" t="n">
         <v>18</v>
@@ -7070,7 +7070,7 @@
         <v>10.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP34" t="n">
         <v>18</v>
@@ -7079,10 +7079,10 @@
         <v>14.5</v>
       </c>
       <c r="AR34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS34" t="n">
         <v>5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>4.8</v>
       </c>
       <c r="AT34" t="n">
         <v>10</v>
@@ -7094,7 +7094,7 @@
         <v>11.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX34" t="n">
         <v>11.5</v>
@@ -7106,7 +7106,7 @@
         <v>11</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB34" t="n">
         <v>18</v>
@@ -7118,7 +7118,7 @@
         <v>19</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
         <v>7</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H35" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J35" t="n">
         <v>3.05</v>
@@ -7177,19 +7177,19 @@
         <v>3.15</v>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M35" t="n">
         <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P35" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q35" t="n">
         <v>2.48</v>
@@ -7198,22 +7198,22 @@
         <v>1.24</v>
       </c>
       <c r="S35" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T35" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U35" t="n">
         <v>1.94</v>
       </c>
       <c r="V35" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W35" t="n">
         <v>1.47</v>
       </c>
       <c r="X35" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y35" t="n">
         <v>9.6</v>
@@ -7249,13 +7249,13 @@
         <v>60</v>
       </c>
       <c r="AJ35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK35" t="n">
         <v>42</v>
       </c>
       <c r="AL35" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM35" t="n">
         <v>140</v>
@@ -7276,13 +7276,13 @@
         <v>15.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AT35" t="n">
         <v>9</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV35" t="n">
         <v>11.5</v>
@@ -7309,7 +7309,7 @@
         <v>13.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BE35" t="n">
         <v>15.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -7359,46 +7359,46 @@
         <v>1.26</v>
       </c>
       <c r="H36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I36" t="n">
         <v>15</v>
       </c>
       <c r="J36" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K36" t="n">
         <v>8</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
         <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O36" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P36" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="Q36" t="n">
         <v>1.48</v>
       </c>
       <c r="R36" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S36" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U36" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V36" t="n">
         <v>1.07</v>
@@ -7407,7 +7407,7 @@
         <v>4.8</v>
       </c>
       <c r="X36" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y36" t="n">
         <v>60</v>
@@ -7416,10 +7416,10 @@
         <v>160</v>
       </c>
       <c r="AA36" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="AB36" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC36" t="n">
         <v>16.5</v>
@@ -7458,19 +7458,19 @@
         <v>3.7</v>
       </c>
       <c r="AO36" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP36" t="n">
         <v>27</v>
       </c>
       <c r="AQ36" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AR36" t="n">
         <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT36" t="n">
         <v>10</v>
@@ -7482,7 +7482,7 @@
         <v>44</v>
       </c>
       <c r="AW36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX36" t="n">
         <v>7.8</v>
@@ -7497,26 +7497,26 @@
         <v>13</v>
       </c>
       <c r="BB36" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC36" t="n">
         <v>12</v>
       </c>
       <c r="BD36" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF36" t="n">
         <v>3.45</v>
       </c>
       <c r="BG36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -7547,58 +7547,58 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G37" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H37" t="n">
         <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K37" t="n">
         <v>3.7</v>
       </c>
       <c r="L37" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O37" t="n">
         <v>1.34</v>
       </c>
       <c r="P37" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T37" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="U37" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W37" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="X37" t="n">
         <v>15.5</v>
@@ -7613,10 +7613,10 @@
         <v>110</v>
       </c>
       <c r="AB37" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD37" t="n">
         <v>20</v>
@@ -7628,7 +7628,7 @@
         <v>970</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH37" t="n">
         <v>950</v>
@@ -7655,62 +7655,62 @@
         <v>65</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>11.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT37" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AU37" t="n">
         <v>7</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AY37" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BD37" t="n">
         <v>27</v>
       </c>
       <c r="BE37" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -7741,58 +7741,58 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H38" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K38" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M38" t="n">
         <v>1.03</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O38" t="n">
         <v>1.16</v>
       </c>
       <c r="P38" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R38" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="S38" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="T38" t="n">
         <v>1.52</v>
       </c>
       <c r="U38" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V38" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X38" t="n">
         <v>950</v>
@@ -7813,7 +7813,7 @@
         <v>11.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
         <v>1000</v>
@@ -7822,19 +7822,19 @@
         <v>19.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH38" t="n">
         <v>19</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL38" t="n">
         <v>32</v>
@@ -7846,34 +7846,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO38" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
         <v>21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT38" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AU38" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV38" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AX38" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY38" t="n">
         <v>9.6</v>
@@ -7882,29 +7882,29 @@
         <v>11</v>
       </c>
       <c r="BA38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC38" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD38" t="n">
-        <v>18</v>
+        <v>5.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF38" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -7935,82 +7935,82 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="G39" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H39" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I39" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K39" t="n">
         <v>3.35</v>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="M39" t="n">
         <v>1.12</v>
       </c>
       <c r="N39" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O39" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P39" t="n">
         <v>1.53</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="R39" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S39" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U39" t="n">
         <v>1.68</v>
       </c>
       <c r="V39" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="W39" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X39" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA39" t="n">
         <v>26</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC39" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD39" t="n">
         <v>12</v>
       </c>
       <c r="AE39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF39" t="n">
         <v>38</v>
@@ -8043,28 +8043,28 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ39" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="AR39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="AW39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX39" t="n">
         <v>30</v>
@@ -8073,32 +8073,32 @@
         <v>18</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BA39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC39" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC39" t="n">
-        <v>7</v>
-      </c>
       <c r="BD39" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG39" t="n">
         <v>20</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -8129,25 +8129,25 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G40" t="n">
         <v>5.9</v>
       </c>
       <c r="H40" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I40" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M40" t="n">
         <v>1.06</v>
@@ -8162,25 +8162,25 @@
         <v>2.02</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R40" t="n">
         <v>1.39</v>
       </c>
       <c r="S40" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T40" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U40" t="n">
         <v>2.02</v>
       </c>
       <c r="V40" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="W40" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X40" t="n">
         <v>17</v>
@@ -8195,7 +8195,7 @@
         <v>18</v>
       </c>
       <c r="AB40" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC40" t="n">
         <v>9.6</v>
@@ -8207,7 +8207,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AG40" t="n">
         <v>22</v>
@@ -8222,7 +8222,7 @@
         <v>160</v>
       </c>
       <c r="AK40" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL40" t="n">
         <v>85</v>
@@ -8231,25 +8231,25 @@
         <v>120</v>
       </c>
       <c r="AN40" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO40" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP40" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ40" t="n">
         <v>7.8</v>
       </c>
       <c r="AR40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS40" t="n">
         <v>13.5</v>
       </c>
       <c r="AT40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU40" t="n">
         <v>8.4</v>
@@ -8270,29 +8270,29 @@
         <v>18</v>
       </c>
       <c r="BA40" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC40" t="n">
         <v>11</v>
       </c>
-      <c r="BC40" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD40" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF40" t="n">
         <v>11</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>10.5</v>
       </c>
       <c r="BG40" t="n">
         <v>8</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -8323,25 +8323,25 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G41" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J41" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K41" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="M41" t="n">
         <v>1.01</v>
@@ -8350,19 +8350,19 @@
         <v>13.5</v>
       </c>
       <c r="O41" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R41" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="S41" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T41" t="n">
         <v>1.33</v>
@@ -8389,7 +8389,7 @@
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AC41" t="n">
         <v>20</v>
@@ -8416,7 +8416,7 @@
         <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL41" t="n">
         <v>21</v>
@@ -8425,7 +8425,7 @@
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AO41" t="n">
         <v>21</v>
@@ -8458,10 +8458,10 @@
         <v>15</v>
       </c>
       <c r="AY41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ41" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA41" t="n">
         <v>21</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G42" t="n">
         <v>4.2</v>
-      </c>
-      <c r="G42" t="n">
-        <v>4.3</v>
       </c>
       <c r="H42" t="n">
         <v>2.12</v>
@@ -8529,52 +8529,52 @@
         <v>2.14</v>
       </c>
       <c r="J42" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L42" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M42" t="n">
         <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O42" t="n">
         <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R42" t="n">
         <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T42" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U42" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>1.87</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X42" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Y42" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z42" t="n">
         <v>12</v>
@@ -8589,13 +8589,13 @@
         <v>7.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE42" t="n">
         <v>24</v>
       </c>
       <c r="AF42" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG42" t="n">
         <v>17</v>
@@ -8613,7 +8613,7 @@
         <v>60</v>
       </c>
       <c r="AL42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM42" t="n">
         <v>130</v>
@@ -8637,7 +8637,7 @@
         <v>23</v>
       </c>
       <c r="AT42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU42" t="n">
         <v>7</v>
@@ -8646,7 +8646,7 @@
         <v>10</v>
       </c>
       <c r="AW42" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AX42" t="n">
         <v>26</v>
@@ -8655,32 +8655,32 @@
         <v>15.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="BB42" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BC42" t="n">
         <v>48</v>
       </c>
       <c r="BD42" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE42" t="n">
         <v>15</v>
       </c>
-      <c r="BE42" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BF42" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="BG42" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G43" t="n">
         <v>3.05</v>
       </c>
       <c r="H43" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I43" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J43" t="n">
         <v>3.25</v>
@@ -8729,31 +8729,31 @@
         <v>3.45</v>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O43" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P43" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T43" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U43" t="n">
         <v>2</v>
@@ -8762,10 +8762,10 @@
         <v>1.54</v>
       </c>
       <c r="W43" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X43" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y43" t="n">
         <v>10.5</v>
@@ -8789,10 +8789,10 @@
         <v>36</v>
       </c>
       <c r="AF43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG43" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH43" t="n">
         <v>19.5</v>
@@ -8828,7 +8828,7 @@
         <v>14.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT43" t="n">
         <v>9</v>
@@ -8840,7 +8840,7 @@
         <v>10.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="AX43" t="n">
         <v>16</v>
@@ -8855,26 +8855,26 @@
         <v>40</v>
       </c>
       <c r="BB43" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC43" t="n">
         <v>30</v>
       </c>
       <c r="BD43" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF43" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG43" t="n">
         <v>6.8</v>
       </c>
-      <c r="BG43" t="n">
-        <v>23</v>
-      </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -8911,19 +8911,19 @@
         <v>2.16</v>
       </c>
       <c r="H44" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I44" t="n">
         <v>4.3</v>
       </c>
       <c r="J44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K44" t="n">
         <v>3.35</v>
       </c>
-      <c r="K44" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L44" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M44" t="n">
         <v>1.1</v>
@@ -8938,7 +8938,7 @@
         <v>1.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R44" t="n">
         <v>1.26</v>
@@ -9013,10 +9013,10 @@
         <v>80</v>
       </c>
       <c r="AP44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR44" t="n">
         <v>26</v>
@@ -9028,7 +9028,7 @@
         <v>7.4</v>
       </c>
       <c r="AU44" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV44" t="n">
         <v>16</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H45" t="n">
         <v>3.95</v>
@@ -9111,10 +9111,10 @@
         <v>4</v>
       </c>
       <c r="J45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K45" t="n">
         <v>3.95</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4</v>
       </c>
       <c r="L45" t="n">
         <v>1.31</v>
@@ -9129,16 +9129,16 @@
         <v>1.2</v>
       </c>
       <c r="P45" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q45" t="n">
         <v>1.63</v>
       </c>
       <c r="R45" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S45" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T45" t="n">
         <v>1.58</v>
@@ -9168,7 +9168,7 @@
         <v>13.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD45" t="n">
         <v>16</v>
@@ -9189,7 +9189,7 @@
         <v>40</v>
       </c>
       <c r="AJ45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK45" t="n">
         <v>17.5</v>
@@ -9243,7 +9243,7 @@
         <v>38</v>
       </c>
       <c r="BB45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC45" t="n">
         <v>16.5</v>
@@ -9255,14 +9255,14 @@
         <v>50</v>
       </c>
       <c r="BF45" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG45" t="n">
         <v>29</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G46" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H46" t="n">
         <v>4</v>
@@ -9311,7 +9311,7 @@
         <v>3.5</v>
       </c>
       <c r="L46" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M46" t="n">
         <v>1.09</v>
@@ -9323,7 +9323,7 @@
         <v>1.38</v>
       </c>
       <c r="P46" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q46" t="n">
         <v>2.14</v>
@@ -9341,10 +9341,10 @@
         <v>2.06</v>
       </c>
       <c r="V46" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W46" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X46" t="n">
         <v>12</v>
@@ -9353,19 +9353,19 @@
         <v>13.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA46" t="n">
         <v>85</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC46" t="n">
         <v>7.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE46" t="n">
         <v>55</v>
@@ -9407,7 +9407,7 @@
         <v>12.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS46" t="n">
         <v>70</v>
@@ -9416,10 +9416,10 @@
         <v>8.4</v>
       </c>
       <c r="AU46" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV46" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW46" t="n">
         <v>46</v>
@@ -9431,7 +9431,7 @@
         <v>10</v>
       </c>
       <c r="AZ46" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA46" t="n">
         <v>55</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -9681,58 +9681,58 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="G48" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H48" t="n">
         <v>4.3</v>
       </c>
       <c r="I48" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J48" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K48" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L48" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M48" t="n">
         <v>1.02</v>
       </c>
       <c r="N48" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P48" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R48" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S48" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="T48" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="U48" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V48" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W48" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9765,7 +9765,7 @@
         <v>14</v>
       </c>
       <c r="AH48" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI48" t="n">
         <v>1000</v>
@@ -9795,13 +9795,13 @@
         <v>4.6</v>
       </c>
       <c r="AR48" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU48" t="n">
         <v>3.9</v>
@@ -9816,7 +9816,7 @@
         <v>4.1</v>
       </c>
       <c r="AY48" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ48" t="n">
         <v>3.95</v>
@@ -9825,13 +9825,13 @@
         <v>4.6</v>
       </c>
       <c r="BB48" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC48" t="n">
         <v>4</v>
       </c>
       <c r="BD48" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE48" t="n">
         <v>4.6</v>
@@ -9840,11 +9840,11 @@
         <v>4.7</v>
       </c>
       <c r="BG48" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -9875,67 +9875,67 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G49" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H49" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I49" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J49" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M49" t="n">
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P49" t="n">
         <v>3.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R49" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S49" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="T49" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="U49" t="n">
         <v>2.82</v>
       </c>
       <c r="V49" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W49" t="n">
         <v>2.78</v>
       </c>
       <c r="X49" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Y49" t="n">
         <v>55</v>
       </c>
       <c r="Z49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
@@ -9950,7 +9950,7 @@
         <v>25</v>
       </c>
       <c r="AE49" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
         <v>16.5</v>
@@ -9986,16 +9986,16 @@
         <v>7.4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS49" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT49" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU49" t="n">
         <v>10.5</v>
@@ -10016,7 +10016,7 @@
         <v>13</v>
       </c>
       <c r="BA49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB49" t="n">
         <v>14</v>
@@ -10028,7 +10028,7 @@
         <v>17</v>
       </c>
       <c r="BE49" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF49" t="n">
         <v>3.8</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -10069,170 +10069,170 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="G50" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="H50" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="K50" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M50" t="n">
         <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="O50" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P50" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R50" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="S50" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="T50" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="U50" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="V50" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="W50" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="n">
         <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC50" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE50" t="n">
         <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI50" t="n">
         <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK50" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
         <v>6.2</v>
       </c>
       <c r="I51" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J51" t="n">
         <v>4</v>
@@ -10287,7 +10287,7 @@
         <v>1.08</v>
       </c>
       <c r="N51" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O51" t="n">
         <v>1.39</v>
@@ -10299,7 +10299,7 @@
         <v>2.14</v>
       </c>
       <c r="R51" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -10308,7 +10308,7 @@
         <v>2.1</v>
       </c>
       <c r="U51" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V51" t="n">
         <v>1.17</v>
@@ -10326,7 +10326,7 @@
         <v>50</v>
       </c>
       <c r="AA51" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB51" t="n">
         <v>7</v>
@@ -10347,28 +10347,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI51" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK51" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL51" t="n">
         <v>44</v>
       </c>
       <c r="AM51" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN51" t="n">
         <v>12.5</v>
       </c>
       <c r="AO51" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AP51" t="n">
         <v>11.5</v>
@@ -10377,13 +10377,13 @@
         <v>15.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT51" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU51" t="n">
         <v>8.199999999999999</v>
@@ -10392,41 +10392,41 @@
         <v>22</v>
       </c>
       <c r="AW51" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AX51" t="n">
         <v>8.4</v>
       </c>
       <c r="AY51" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA51" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BB51" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC51" t="n">
         <v>17.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE51" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BF51" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -10463,40 +10463,40 @@
         <v>5.1</v>
       </c>
       <c r="H52" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I52" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J52" t="n">
         <v>3.45</v>
       </c>
       <c r="K52" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L52" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
       </c>
       <c r="N52" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P52" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R52" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S52" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T52" t="n">
         <v>1.96</v>
@@ -10511,7 +10511,7 @@
         <v>1.24</v>
       </c>
       <c r="X52" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y52" t="n">
         <v>7.8</v>
@@ -10523,7 +10523,7 @@
         <v>26</v>
       </c>
       <c r="AB52" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC52" t="n">
         <v>8.4</v>
@@ -10532,10 +10532,10 @@
         <v>12.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG52" t="n">
         <v>25</v>
@@ -10589,7 +10589,7 @@
         <v>19</v>
       </c>
       <c r="AX52" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY52" t="n">
         <v>17</v>
@@ -10601,26 +10601,26 @@
         <v>36</v>
       </c>
       <c r="BB52" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC52" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE52" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG52" t="n">
         <v>12</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -10669,31 +10669,31 @@
         <v>3.3</v>
       </c>
       <c r="L53" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M53" t="n">
         <v>1.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O53" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P53" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q53" t="n">
         <v>2.7</v>
       </c>
       <c r="R53" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S53" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T53" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U53" t="n">
         <v>1.78</v>
@@ -10723,7 +10723,7 @@
         <v>7.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE53" t="n">
         <v>900</v>
@@ -10738,7 +10738,7 @@
         <v>40</v>
       </c>
       <c r="AI53" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ53" t="n">
         <v>50</v>
@@ -10750,7 +10750,7 @@
         <v>1000</v>
       </c>
       <c r="AM53" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN53" t="n">
         <v>55</v>
@@ -10789,7 +10789,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA53" t="n">
         <v>38</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -10845,58 +10845,58 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G54" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H54" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I54" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="J54" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K54" t="n">
         <v>3.6</v>
       </c>
       <c r="L54" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M54" t="n">
         <v>1.09</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O54" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P54" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R54" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T54" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U54" t="n">
         <v>1.95</v>
       </c>
       <c r="V54" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W54" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X54" t="n">
         <v>13</v>
@@ -10905,10 +10905,10 @@
         <v>10.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA54" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB54" t="n">
         <v>13</v>
@@ -10920,7 +10920,7 @@
         <v>13.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF54" t="n">
         <v>27</v>
@@ -10950,46 +10950,46 @@
         <v>60</v>
       </c>
       <c r="AO54" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP54" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ54" t="n">
         <v>3.6</v>
       </c>
       <c r="AR54" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW54" t="n">
         <v>5.1</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>5.2</v>
       </c>
       <c r="AX54" t="n">
         <v>19</v>
       </c>
       <c r="AY54" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ54" t="n">
         <v>16</v>
       </c>
       <c r="BA54" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB54" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC54" t="n">
         <v>4.9</v>
@@ -10998,17 +10998,17 @@
         <v>5</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF54" t="n">
         <v>5</v>
       </c>
       <c r="BG54" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -11039,58 +11039,58 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G55" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H55" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J55" t="n">
         <v>3.1</v>
       </c>
       <c r="K55" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L55" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M55" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N55" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P55" t="n">
         <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="R55" t="n">
         <v>1.24</v>
       </c>
       <c r="S55" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T55" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U55" t="n">
         <v>1.94</v>
       </c>
-      <c r="U55" t="n">
-        <v>1.95</v>
-      </c>
       <c r="V55" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W55" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X55" t="n">
         <v>11.5</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -11233,55 +11233,55 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G56" t="n">
         <v>3.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I56" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K56" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L56" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M56" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N56" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O56" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P56" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R56" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S56" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T56" t="n">
         <v>2.04</v>
       </c>
       <c r="U56" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V56" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W56" t="n">
         <v>1.4</v>
@@ -11290,13 +11290,13 @@
         <v>10.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB56" t="n">
         <v>10.5</v>
@@ -11305,10 +11305,10 @@
         <v>8.4</v>
       </c>
       <c r="AD56" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF56" t="n">
         <v>23</v>
@@ -11338,7 +11338,7 @@
         <v>65</v>
       </c>
       <c r="AO56" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP56" t="n">
         <v>7.8</v>
@@ -11350,19 +11350,19 @@
         <v>11</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT56" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU56" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV56" t="n">
         <v>9</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX56" t="n">
         <v>15.5</v>
@@ -11374,29 +11374,29 @@
         <v>16.5</v>
       </c>
       <c r="BA56" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG56" t="n">
         <v>5</v>
       </c>
-      <c r="BB56" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -11427,16 +11427,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G57" t="n">
         <v>2.02</v>
       </c>
       <c r="H57" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I57" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>3.25</v>
@@ -11445,13 +11445,13 @@
         <v>3.5</v>
       </c>
       <c r="L57" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="M57" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N57" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="O57" t="n">
         <v>1.48</v>
@@ -11460,13 +11460,13 @@
         <v>1.62</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R57" t="n">
         <v>1.22</v>
       </c>
       <c r="S57" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T57" t="n">
         <v>2.1</v>
@@ -11475,7 +11475,7 @@
         <v>1.79</v>
       </c>
       <c r="V57" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W57" t="n">
         <v>1.98</v>
@@ -11511,7 +11511,7 @@
         <v>13</v>
       </c>
       <c r="AH57" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI57" t="n">
         <v>1000</v>
@@ -11529,68 +11529,68 @@
         <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO57" t="n">
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR57" t="n">
         <v>4.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT57" t="n">
         <v>3.1</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV57" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX57" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AY57" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ57" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA57" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB57" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BC57" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD57" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE57" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF57" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BG57" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -11621,58 +11621,58 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G58" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H58" t="n">
         <v>4.9</v>
       </c>
       <c r="I58" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J58" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L58" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M58" t="n">
         <v>1.13</v>
       </c>
       <c r="N58" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="O58" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P58" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R58" t="n">
         <v>1.17</v>
       </c>
       <c r="S58" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="T58" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="U58" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="V58" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W58" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="X58" t="n">
         <v>9.6</v>
@@ -11735,22 +11735,22 @@
         <v>9.4</v>
       </c>
       <c r="AR58" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS58" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT58" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AU58" t="n">
         <v>6.4</v>
       </c>
       <c r="AV58" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX58" t="n">
         <v>7.6</v>
@@ -11762,29 +11762,29 @@
         <v>5.6</v>
       </c>
       <c r="BA58" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB58" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC58" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF58" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD58" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF58" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG58" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -11818,58 +11818,58 @@
         <v>3.2</v>
       </c>
       <c r="G59" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H59" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J59" t="n">
         <v>2.86</v>
       </c>
       <c r="K59" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="L59" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="M59" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N59" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O59" t="n">
         <v>1.54</v>
       </c>
       <c r="P59" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="R59" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S59" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T59" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U59" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V59" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W59" t="n">
         <v>1.37</v>
       </c>
       <c r="X59" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y59" t="n">
         <v>9.199999999999999</v>
@@ -11881,10 +11881,10 @@
         <v>1000</v>
       </c>
       <c r="AB59" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC59" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD59" t="n">
         <v>14</v>
@@ -11893,7 +11893,7 @@
         <v>1000</v>
       </c>
       <c r="AF59" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG59" t="n">
         <v>1000</v>
@@ -11932,19 +11932,19 @@
         <v>11</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT59" t="n">
         <v>7.2</v>
       </c>
       <c r="AU59" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV59" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW59" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AX59" t="n">
         <v>16.5</v>
@@ -11953,32 +11953,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ59" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BA59" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BB59" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC59" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG59" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -12009,67 +12009,67 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G60" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H60" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I60" t="n">
         <v>3.3</v>
       </c>
       <c r="J60" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="K60" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L60" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="M60" t="n">
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="O60" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P60" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R60" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S60" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="T60" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U60" t="n">
         <v>3.35</v>
       </c>
       <c r="V60" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W60" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
       </c>
       <c r="Y60" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z60" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA60" t="n">
         <v>1000</v>
@@ -12078,101 +12078,101 @@
         <v>1000</v>
       </c>
       <c r="AC60" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AD60" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH60" t="n">
         <v>17</v>
       </c>
-      <c r="AE60" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF60" t="n">
+      <c r="AI60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL60" t="n">
         <v>26</v>
       </c>
-      <c r="AG60" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>22</v>
-      </c>
       <c r="AM60" t="n">
         <v>1000</v>
       </c>
       <c r="AN60" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO60" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="AQ60" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="AR60" t="n">
-        <v>7.4</v>
+        <v>3.65</v>
       </c>
       <c r="AS60" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="AT60" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="AU60" t="n">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="AV60" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="AW60" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AX60" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="AY60" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="AZ60" t="n">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="BA60" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="BB60" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC60" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="BD60" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="BE60" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BF60" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="BG60" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -12203,55 +12203,55 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G61" t="n">
         <v>2.3</v>
       </c>
       <c r="H61" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>3.5</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L61" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M61" t="n">
         <v>1.06</v>
       </c>
       <c r="N61" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O61" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R61" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S61" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T61" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U61" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V61" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W61" t="n">
         <v>1.78</v>
@@ -12263,7 +12263,7 @@
         <v>17</v>
       </c>
       <c r="Z61" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA61" t="n">
         <v>1000</v>
@@ -12272,7 +12272,7 @@
         <v>12</v>
       </c>
       <c r="AC61" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD61" t="n">
         <v>17.5</v>
@@ -12290,7 +12290,7 @@
         <v>19.5</v>
       </c>
       <c r="AI61" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ61" t="n">
         <v>29</v>
@@ -12308,7 +12308,7 @@
         <v>16.5</v>
       </c>
       <c r="AO61" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP61" t="n">
         <v>12</v>
@@ -12320,7 +12320,7 @@
         <v>20</v>
       </c>
       <c r="AS61" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT61" t="n">
         <v>8.199999999999999</v>
@@ -12332,7 +12332,7 @@
         <v>11.5</v>
       </c>
       <c r="AW61" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX61" t="n">
         <v>11</v>
@@ -12344,7 +12344,7 @@
         <v>13</v>
       </c>
       <c r="BA61" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB61" t="n">
         <v>20</v>
@@ -12353,20 +12353,20 @@
         <v>17</v>
       </c>
       <c r="BD61" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE61" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF61" t="n">
         <v>11.5</v>
       </c>
       <c r="BG61" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -12400,55 +12400,55 @@
         <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H62" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I62" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K62" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L62" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="M62" t="n">
         <v>1.16</v>
       </c>
       <c r="N62" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O62" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="P62" t="n">
         <v>1.42</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
         <v>1.14</v>
       </c>
       <c r="S62" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T62" t="n">
         <v>2.38</v>
       </c>
       <c r="U62" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V62" t="n">
         <v>1.5</v>
       </c>
       <c r="W62" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X62" t="n">
         <v>7.4</v>
@@ -12520,7 +12520,7 @@
         <v>6.8</v>
       </c>
       <c r="AU62" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV62" t="n">
         <v>5.7</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -12591,64 +12591,64 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G63" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H63" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I63" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J63" t="n">
         <v>3.75</v>
       </c>
       <c r="K63" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L63" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M63" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N63" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P63" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R63" t="n">
         <v>1.24</v>
       </c>
       <c r="S63" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T63" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="U63" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W63" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X63" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y63" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z63" t="n">
         <v>1000</v>
@@ -12657,34 +12657,34 @@
         <v>1000</v>
       </c>
       <c r="AB63" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AC63" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD63" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE63" t="n">
         <v>1000</v>
       </c>
       <c r="AF63" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG63" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH63" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI63" t="n">
         <v>1000</v>
       </c>
       <c r="AJ63" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK63" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL63" t="n">
         <v>1000</v>
@@ -12693,22 +12693,22 @@
         <v>1000</v>
       </c>
       <c r="AN63" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO63" t="n">
         <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AQ63" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AR63" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AT63" t="n">
         <v>5.3</v>
@@ -12717,44 +12717,44 @@
         <v>7.8</v>
       </c>
       <c r="AV63" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AW63" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="AX63" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY63" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ63" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BA63" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="BB63" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE63" t="n">
         <v>5</v>
       </c>
-      <c r="BC63" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BF63" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG63" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
